--- a/2026/ITALIA/Marzo/Marzo ITALIA.xlsx
+++ b/2026/ITALIA/Marzo/Marzo ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D2314F-E32A-433C-AF19-3A54F04969E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFCFEF-EE74-45D5-B649-A92DEB239590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,19 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$129</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$137</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="247">
   <si>
     <t>TOTAL</t>
   </si>
@@ -769,7 +764,19 @@
     <t>Doartero julio  - Adelanto cambio tablero bombas</t>
   </si>
   <si>
-    <t>Efectivo -  Debe abonar la cuota 5 de 24 - Hasta ahora solo abono 4/24</t>
+    <t xml:space="preserve">Plan de pago de 6C: Consta de 6 cuotas de $300.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aun no abono cuotas - Consta de 3 cuotas de $300.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efectivo - 123300-   Debe abonar la cuota 5 de 24 - Hasta ahora solo abono 4/24 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aun no abono cuotas - Consta de 24 cuotas de $33.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan de pago de 6B: Consta de 24 cuotas de $33.000 + expensas en curso </t>
   </si>
 </sst>
 </file>
@@ -1535,11 +1542,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1667,7 +1675,6 @@
     <xf numFmtId="44" fontId="19" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1681,7 +1688,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1737,7 +1743,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1765,7 +1770,6 @@
     </xf>
     <xf numFmtId="44" fontId="19" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="18" fillId="13" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1815,147 +1819,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="18" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1965,7 +1829,7 @@
     <xf numFmtId="44" fontId="12" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1976,12 +1840,6 @@
     <xf numFmtId="167" fontId="18" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="13" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="18" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1999,17 +1857,154 @@
     <xf numFmtId="44" fontId="16" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="13" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2091,9 +2086,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2131,9 +2126,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2166,26 +2161,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2218,26 +2196,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2411,32 +2372,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M138"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="181" t="s">
+      <c r="B1" s="200" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="182"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="201"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>152</v>
@@ -2445,16 +2406,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="185" t="s">
+      <c r="B3" s="202" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="186"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="203"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>102</v>
       </c>
@@ -2465,7 +2426,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>151</v>
       </c>
@@ -2478,8 +2439,8 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="94" t="s">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="93" t="s">
         <v>140</v>
       </c>
       <c r="B6" s="8"/>
@@ -2489,57 +2450,57 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="187" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="204" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="187"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="187"/>
-      <c r="C9" s="187"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="187"/>
-      <c r="C10" s="187"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="188" t="s">
+      <c r="C8" s="204"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="205" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="188"/>
-      <c r="C13" s="188"/>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="188"/>
-      <c r="B14" s="188"/>
-      <c r="C14" s="188"/>
-      <c r="D14" s="188"/>
-      <c r="E14" s="188"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="188"/>
-      <c r="B15" s="188"/>
-      <c r="C15" s="188"/>
-      <c r="D15" s="188"/>
-      <c r="E15" s="188"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="188"/>
-      <c r="B16" s="188"/>
-      <c r="C16" s="188"/>
-      <c r="D16" s="188"/>
-      <c r="E16" s="188"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="205"/>
+      <c r="C13" s="205"/>
+      <c r="D13" s="205"/>
+      <c r="E13" s="205"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="205"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="205"/>
+      <c r="B15" s="205"/>
+      <c r="C15" s="205"/>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="205"/>
+      <c r="B16" s="205"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="205"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>106</v>
       </c>
@@ -2548,73 +2509,73 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>141</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="235"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="183" t="s">
+      <c r="D21" s="129"/>
+      <c r="E21" s="181"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="196" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="184"/>
+      <c r="B22" s="197"/>
       <c r="C22" s="21"/>
-      <c r="D22" s="143">
+      <c r="D22" s="139">
         <v>2109818.7799999998</v>
       </c>
-      <c r="E22" s="236"/>
+      <c r="E22" s="182"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="183" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="196" t="s">
         <v>171</v>
       </c>
-      <c r="B23" s="184"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="21"/>
-      <c r="D23" s="143">
+      <c r="D23" s="139">
         <v>-458885.59</v>
       </c>
       <c r="E23" s="23"/>
       <c r="H23" s="22"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="183" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="184"/>
+      <c r="B24" s="197"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="144">
+      <c r="D24" s="140">
         <v>0.81</v>
       </c>
       <c r="E24" s="23"/>
       <c r="H24" s="22"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="237">
+      <c r="E25" s="183">
         <f>SUM(D22:D24)</f>
         <v>1650933.9999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
         <v>207</v>
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="238"/>
-    </row>
-    <row r="27" spans="1:8" s="178" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="184"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>178</v>
       </c>
@@ -2623,9 +2584,9 @@
       <c r="D27" s="38">
         <v>370000</v>
       </c>
-      <c r="E27" s="239"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E27" s="185"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>192</v>
       </c>
@@ -2634,104 +2595,104 @@
       <c r="D28" s="38">
         <v>5842.51</v>
       </c>
-      <c r="E28" s="240" t="s">
+      <c r="E28" s="186" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
         <v>107</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="241">
+      <c r="D29" s="118"/>
+      <c r="E29" s="187">
         <f>D27+D28</f>
         <v>375842.51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>142</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="238"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="184"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="95"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="94"/>
       <c r="D31" s="38"/>
-      <c r="E31" s="240"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E31" s="186"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="95"/>
-      <c r="C32" s="95"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
       <c r="D32" s="38">
         <v>960321.67</v>
       </c>
-      <c r="E32" s="240" t="s">
+      <c r="E32" s="186" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="95"/>
-      <c r="C33" s="95"/>
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
       <c r="D33" s="38">
         <v>166275.49</v>
       </c>
-      <c r="E33" s="240" t="s">
+      <c r="E33" s="186" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="95"/>
+      <c r="B34" s="94"/>
+      <c r="C34" s="94"/>
       <c r="D34" s="38">
         <v>86923.04</v>
       </c>
-      <c r="E34" s="240" t="str">
+      <c r="E34" s="186" t="str">
         <f>E33</f>
         <v>Debito 12/03</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="95"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="94"/>
       <c r="D35" s="38">
         <v>9658.1200000000008</v>
       </c>
-      <c r="E35" s="240" t="str">
+      <c r="E35" s="186" t="str">
         <f>E33</f>
         <v>Debito 12/03</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="240"/>
-    </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="186"/>
+    </row>
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
         <v>143</v>
       </c>
@@ -2743,29 +2704,29 @@
         <v>1223178.3200000003</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>108</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
       <c r="D38" s="26"/>
-      <c r="E38" s="241"/>
-    </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="179" t="s">
+      <c r="E38" s="187"/>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="206" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="180"/>
+      <c r="B39" s="207"/>
       <c r="C39" s="29"/>
-      <c r="D39" s="145">
+      <c r="D39" s="141">
         <v>214164</v>
       </c>
       <c r="E39" s="23" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
         <v>109</v>
       </c>
@@ -2777,16 +2738,16 @@
         <v>214164</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
         <v>110</v>
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
       <c r="D41" s="31"/>
-      <c r="E41" s="242"/>
-    </row>
-    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="188"/>
+    </row>
+    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="32" t="s">
         <v>111</v>
       </c>
@@ -2799,7 +2760,7 @@
       </c>
       <c r="E42" s="23"/>
     </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>111</v>
       </c>
@@ -2812,7 +2773,7 @@
       </c>
       <c r="E43" s="23"/>
     </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
         <v>222</v>
       </c>
@@ -2827,7 +2788,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
         <v>224</v>
       </c>
@@ -2840,20 +2801,20 @@
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="179" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="206" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="180"/>
+      <c r="B46" s="207"/>
       <c r="C46" s="32"/>
       <c r="D46" s="33">
         <v>4890986.6399999997</v>
       </c>
-      <c r="E46" s="133" t="s">
+      <c r="E46" s="130" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>113</v>
       </c>
@@ -2862,30 +2823,30 @@
       <c r="D47" s="33"/>
       <c r="E47" s="23"/>
     </row>
-    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="24" t="s">
         <v>114</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
       <c r="D48" s="36"/>
-      <c r="E48" s="243">
+      <c r="E48" s="189">
         <f>SUM(D42:D47)</f>
         <v>4943792.54</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="17"/>
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
       <c r="D49" s="25"/>
-      <c r="E49" s="244"/>
-    </row>
-    <row r="50" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="183" t="s">
+      <c r="E49" s="190"/>
+    </row>
+    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="196" t="s">
         <v>173</v>
       </c>
-      <c r="B50" s="184"/>
+      <c r="B50" s="197"/>
       <c r="C50" s="32"/>
       <c r="D50" s="33">
         <v>285000</v>
@@ -2894,37 +2855,37 @@
         <v>203</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="183" t="s">
+    <row r="51" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="196" t="s">
         <v>240</v>
       </c>
-      <c r="B51" s="184"/>
+      <c r="B51" s="197"/>
       <c r="C51" s="32"/>
       <c r="D51" s="33">
         <v>1300000</v>
       </c>
-      <c r="E51" s="130" t="s">
+      <c r="E51" s="127" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="183" t="s">
+    <row r="52" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="196" t="s">
         <v>241</v>
       </c>
-      <c r="B52" s="184"/>
+      <c r="B52" s="197"/>
       <c r="C52" s="32"/>
       <c r="D52" s="33">
         <v>380000</v>
       </c>
-      <c r="E52" s="130" t="s">
+      <c r="E52" s="127" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="183" t="s">
+    <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="196" t="s">
         <v>204</v>
       </c>
-      <c r="B53" s="184"/>
+      <c r="B53" s="197"/>
       <c r="C53" s="32"/>
       <c r="D53" s="33">
         <v>170000</v>
@@ -2934,8 +2895,8 @@
       </c>
       <c r="F53" s="53"/>
     </row>
-    <row r="54" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="105" t="s">
+    <row r="54" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="103" t="s">
         <v>219</v>
       </c>
       <c r="B54" s="20"/>
@@ -2948,21 +2909,21 @@
       </c>
       <c r="F54" s="53"/>
     </row>
-    <row r="55" spans="1:6" ht="85.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="183" t="s">
+    <row r="55" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="196" t="s">
         <v>189</v>
       </c>
-      <c r="B55" s="184"/>
+      <c r="B55" s="197"/>
       <c r="C55" s="32"/>
       <c r="D55" s="33">
         <v>1400000</v>
       </c>
-      <c r="E55" s="236" t="s">
+      <c r="E55" s="182" t="s">
         <v>205</v>
       </c>
       <c r="F55" s="53"/>
     </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
         <v>179</v>
       </c>
@@ -2976,8 +2937,8 @@
       </c>
       <c r="F56" s="53"/>
     </row>
-    <row r="57" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="105" t="s">
+    <row r="57" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="103" t="s">
         <v>174</v>
       </c>
       <c r="B57" s="20"/>
@@ -2990,22 +2951,22 @@
       </c>
       <c r="F57" s="53"/>
     </row>
-    <row r="58" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="183" t="s">
+    <row r="58" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="196" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="184"/>
+      <c r="B58" s="197"/>
       <c r="C58" s="32"/>
       <c r="D58" s="33">
         <v>2550520.2599999998</v>
       </c>
-      <c r="E58" s="236" t="s">
+      <c r="E58" s="182" t="s">
         <v>213</v>
       </c>
       <c r="F58" s="53"/>
     </row>
-    <row r="59" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="105" t="s">
+    <row r="59" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="103" t="s">
         <v>200</v>
       </c>
       <c r="B59" s="20"/>
@@ -3013,26 +2974,26 @@
       <c r="D59" s="33">
         <v>137300</v>
       </c>
-      <c r="E59" s="236" t="s">
+      <c r="E59" s="182" t="s">
         <v>202</v>
       </c>
       <c r="F59" s="53"/>
     </row>
-    <row r="60" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="183" t="s">
+    <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="196" t="s">
         <v>211</v>
       </c>
-      <c r="B60" s="184"/>
+      <c r="B60" s="197"/>
       <c r="C60" s="32"/>
       <c r="D60" s="33">
         <v>105602.65</v>
       </c>
-      <c r="E60" s="236" t="s">
+      <c r="E60" s="182" t="s">
         <v>202</v>
       </c>
       <c r="F60" s="53"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
         <v>0</v>
       </c>
@@ -3044,76 +3005,76 @@
         <v>7533872.9100000001</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="17" t="s">
         <v>115</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
       <c r="D62" s="18"/>
-      <c r="E62" s="235"/>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="183" t="s">
+      <c r="E62" s="181"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="196" t="s">
         <v>208</v>
       </c>
-      <c r="B63" s="184"/>
+      <c r="B63" s="197"/>
       <c r="C63" s="21"/>
-      <c r="D63" s="146"/>
-      <c r="E63" s="236"/>
-    </row>
-    <row r="64" spans="1:6" s="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="176" t="s">
+      <c r="D63" s="142"/>
+      <c r="E63" s="182"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="B64" s="177"/>
+      <c r="B64" s="20"/>
       <c r="C64" s="21"/>
-      <c r="D64" s="147">
+      <c r="D64" s="143">
         <v>100000</v>
       </c>
-      <c r="E64" s="236" t="s">
+      <c r="E64" s="182" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
         <v>172</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="21"/>
-      <c r="D65" s="147">
+      <c r="D65" s="143">
         <v>125000</v>
       </c>
-      <c r="E65" s="236" t="s">
+      <c r="E65" s="182" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="105" t="s">
+    <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="103" t="s">
         <v>201</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="21"/>
-      <c r="D66" s="147">
+      <c r="D66" s="143">
         <v>45000</v>
       </c>
-      <c r="E66" s="236" t="s">
+      <c r="E66" s="182" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
         <v>107</v>
       </c>
       <c r="B67" s="24"/>
       <c r="C67" s="24"/>
       <c r="D67" s="25"/>
-      <c r="E67" s="237">
+      <c r="E67" s="183">
         <f>SUM(D63:D66)</f>
         <v>270000</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>116</v>
       </c>
@@ -3122,29 +3083,29 @@
       <c r="D68" s="41"/>
       <c r="E68" s="44"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="B69" s="96"/>
-      <c r="C69" s="96"/>
-      <c r="D69" s="148">
+      <c r="B69" s="95"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="144">
         <v>52000</v>
       </c>
-      <c r="E69" s="245"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E69" s="191"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="B70" s="96"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="148">
+      <c r="B70" s="95"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="144">
         <v>227782.42</v>
       </c>
-      <c r="E70" s="245"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E70" s="191"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="42" t="s">
         <v>107</v>
       </c>
@@ -3156,14 +3117,14 @@
         <v>279782.42000000004</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="32"/>
       <c r="B72" s="32"/>
       <c r="C72" s="32"/>
       <c r="D72" s="45"/>
       <c r="E72" s="46"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="47" t="s">
         <v>117</v>
       </c>
@@ -3172,13 +3133,13 @@
       <c r="D73" s="48"/>
       <c r="E73" s="49"/>
     </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="50"/>
       <c r="D74" s="51"/>
       <c r="E74" s="52"/>
       <c r="F74" s="53"/>
     </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="54" t="s">
         <v>118</v>
       </c>
@@ -3192,16 +3153,16 @@
       <c r="F75" s="59"/>
       <c r="G75" s="53"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D76" s="51"/>
       <c r="E76" s="51"/>
     </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D77" s="51"/>
       <c r="E77" s="51"/>
       <c r="H77" s="60"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>119</v>
       </c>
@@ -3210,65 +3171,67 @@
       <c r="D78" s="61"/>
       <c r="E78" s="62"/>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="27"/>
       <c r="B79" s="28"/>
       <c r="C79" s="32"/>
       <c r="D79" s="38"/>
       <c r="E79" s="63"/>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="183"/>
-      <c r="B80" s="184"/>
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="196"/>
+      <c r="B80" s="197"/>
       <c r="C80" s="32"/>
       <c r="D80" s="38"/>
       <c r="E80" s="63"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="45"/>
       <c r="E81" s="45"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="B82" s="64"/>
       <c r="C82" s="32"/>
       <c r="D82" s="38"/>
       <c r="E82" s="63"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="65" t="s">
         <v>148</v>
       </c>
       <c r="B83" s="66"/>
       <c r="C83" s="66"/>
-      <c r="D83" s="131"/>
-      <c r="E83" s="246">
+      <c r="D83" s="128"/>
+      <c r="E83" s="192">
         <f>SUM(D79:D82)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D84" s="51"/>
       <c r="E84" s="51"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D85" s="51"/>
       <c r="E85" s="51"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="47" t="s">
         <v>120</v>
       </c>
       <c r="B86" s="47"/>
       <c r="C86" s="47"/>
       <c r="D86" s="48"/>
-      <c r="E86" s="247"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E86" s="241">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D87" s="51"/>
       <c r="E87" s="51"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="54" t="s">
         <v>121</v>
       </c>
@@ -3277,14 +3240,14 @@
       <c r="D88" s="57"/>
       <c r="E88" s="58">
         <f>E83+E86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D89" s="51"/>
       <c r="E89" s="51"/>
     </row>
-    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="67" t="s">
         <v>122</v>
       </c>
@@ -3295,7 +3258,7 @@
       <c r="D90" s="51"/>
       <c r="E90" s="51"/>
     </row>
-    <row r="91" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="67" t="s">
         <v>123</v>
       </c>
@@ -3306,7 +3269,7 @@
       <c r="D91" s="51"/>
       <c r="E91" s="51"/>
     </row>
-    <row r="92" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="67" t="s">
         <v>124</v>
       </c>
@@ -3317,324 +3280,360 @@
       <c r="D92" s="51"/>
       <c r="E92" s="51"/>
     </row>
-    <row r="93" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="67" t="s">
         <v>125</v>
       </c>
       <c r="B93" s="68">
         <f>E88</f>
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="D93" s="51"/>
       <c r="E93" s="51"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D94" s="51"/>
       <c r="E94" s="51"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D95" s="51"/>
       <c r="E95" s="51"/>
     </row>
-    <row r="96" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="191" t="s">
+    <row r="96" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="195" t="s">
         <v>185</v>
       </c>
-      <c r="B96" s="191"/>
+      <c r="B96" s="195"/>
       <c r="D96" s="51"/>
       <c r="E96" s="51"/>
     </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="191"/>
-      <c r="B97" s="191"/>
+    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="195"/>
+      <c r="B97" s="195"/>
       <c r="D97" s="51"/>
       <c r="E97" s="51"/>
     </row>
-    <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="191"/>
-      <c r="B98" s="191"/>
+    <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="195"/>
+      <c r="B98" s="195"/>
       <c r="D98" s="51"/>
       <c r="E98" s="51"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D99" s="51"/>
       <c r="E99" s="51"/>
     </row>
-    <row r="100" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="191" t="s">
+    <row r="100" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="195" t="s">
         <v>186</v>
       </c>
-      <c r="B100" s="191"/>
+      <c r="B100" s="195"/>
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
     </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="191"/>
-      <c r="B101" s="191"/>
+    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="195"/>
+      <c r="B101" s="195"/>
       <c r="D101" s="51"/>
       <c r="E101" s="51"/>
     </row>
-    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="191"/>
-      <c r="B102" s="191"/>
+    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="195"/>
+      <c r="B102" s="195"/>
       <c r="D102" s="51"/>
       <c r="E102" s="51"/>
     </row>
-    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D103" s="51"/>
       <c r="E103" s="51"/>
     </row>
-    <row r="104" spans="1:5" s="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="191" t="s">
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="195" t="s">
         <v>233</v>
       </c>
-      <c r="B104" s="191"/>
+      <c r="B104" s="195"/>
       <c r="D104" s="51"/>
       <c r="E104" s="51"/>
     </row>
-    <row r="105" spans="1:5" s="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="191"/>
-      <c r="B105" s="191"/>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="195"/>
+      <c r="B105" s="195"/>
       <c r="D105" s="51"/>
       <c r="E105" s="51"/>
     </row>
-    <row r="106" spans="1:5" s="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="191"/>
-      <c r="B106" s="191"/>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="195"/>
+      <c r="B106" s="195"/>
       <c r="D106" s="51"/>
       <c r="E106" s="51"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D107" s="51"/>
       <c r="E107" s="51"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="190" t="s">
-        <v>191</v>
-      </c>
-      <c r="B108" s="190"/>
+    <row r="108" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="195" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" s="195"/>
       <c r="D108" s="51"/>
       <c r="E108" s="51"/>
     </row>
-    <row r="109" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="190"/>
-      <c r="B109" s="190"/>
+    <row r="109" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="195"/>
+      <c r="B109" s="195"/>
       <c r="D109" s="51"/>
       <c r="E109" s="51"/>
     </row>
-    <row r="110" spans="1:5" s="71" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110" s="69"/>
-      <c r="C110" s="70"/>
-      <c r="D110" s="248"/>
-      <c r="E110" s="248"/>
-    </row>
-    <row r="111" spans="1:5" s="71" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="104" t="s">
+    <row r="110" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="195"/>
+      <c r="B110" s="195"/>
+      <c r="D110" s="51"/>
+      <c r="E110" s="51"/>
+    </row>
+    <row r="111" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D111" s="51"/>
+      <c r="E111" s="51"/>
+    </row>
+    <row r="112" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="195" t="s">
+        <v>242</v>
+      </c>
+      <c r="B112" s="195"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="51"/>
+    </row>
+    <row r="113" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="195"/>
+      <c r="B113" s="195"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="195"/>
+      <c r="B114" s="195"/>
+      <c r="D114" s="51"/>
+      <c r="E114" s="51"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D115" s="51"/>
+      <c r="E115" s="51"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="199" t="s">
+        <v>191</v>
+      </c>
+      <c r="B116" s="199"/>
+      <c r="D116" s="51"/>
+      <c r="E116" s="51"/>
+    </row>
+    <row r="117" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="199"/>
+      <c r="B117" s="199"/>
+      <c r="D117" s="51"/>
+      <c r="E117" s="51"/>
+    </row>
+    <row r="118" spans="1:6" s="71" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="70"/>
+      <c r="D118" s="193"/>
+      <c r="E118" s="193"/>
+    </row>
+    <row r="119" spans="1:6" s="71" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="102" t="s">
         <v>168</v>
       </c>
-      <c r="B111" s="72">
+      <c r="B119" s="72">
         <v>1066133.5837450363</v>
       </c>
-      <c r="C111" s="70"/>
-      <c r="D111" s="249"/>
-      <c r="E111" s="249"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="29" t="s">
+      <c r="C119" s="70"/>
+      <c r="D119" s="194"/>
+      <c r="E119" s="194"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="B112" s="73">
+      <c r="B120" s="73">
         <f>-B91-B92</f>
         <v>-16491566.700000001</v>
       </c>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B113" s="73">
-        <f>B129</f>
-        <v>364781.9</v>
-      </c>
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="69"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B114" s="74">
-        <f>PRORRATEO!F117</f>
-        <v>14068443.220000001</v>
-      </c>
-      <c r="D114" s="51"/>
-      <c r="E114" s="51"/>
-      <c r="F114" s="69"/>
-    </row>
-    <row r="115" spans="1:6" s="178" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" s="222">
-        <v>-110000</v>
-      </c>
-      <c r="D115" s="51"/>
-      <c r="E115" s="51"/>
-      <c r="F115" s="69"/>
-    </row>
-    <row r="116" spans="1:6" s="178" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B116" s="222">
-        <v>-6066</v>
-      </c>
-      <c r="D116" s="51"/>
-      <c r="E116" s="51"/>
-      <c r="F116" s="69"/>
-    </row>
-    <row r="117" spans="1:6" s="178" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="B117" s="222">
-        <v>-20610</v>
-      </c>
-      <c r="D117" s="51"/>
-      <c r="E117" s="51"/>
-      <c r="F117" s="69"/>
-    </row>
-    <row r="118" spans="1:6" s="178" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="B118" s="222">
-        <v>-50000</v>
-      </c>
-      <c r="D118" s="51"/>
-      <c r="E118" s="51"/>
-      <c r="F118" s="69"/>
-    </row>
-    <row r="119" spans="1:6" s="178" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="223" t="s">
-        <v>235</v>
-      </c>
-      <c r="B119" s="226">
-        <f>300000+B120</f>
-        <v>168000</v>
-      </c>
-      <c r="D119" s="51"/>
-      <c r="E119" s="51"/>
-      <c r="F119" s="69"/>
-    </row>
-    <row r="120" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="223" t="s">
-        <v>225</v>
-      </c>
-      <c r="B120" s="141">
-        <v>-132000</v>
-      </c>
       <c r="D120" s="51"/>
       <c r="E120" s="51"/>
-      <c r="F120" s="69"/>
-    </row>
-    <row r="121" spans="1:6" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="223" t="s">
-        <v>232</v>
-      </c>
-      <c r="B121" s="224">
-        <f>150000+B120</f>
-        <v>18000</v>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="73">
+        <f>B137</f>
+        <v>364781.9</v>
       </c>
       <c r="D121" s="51"/>
       <c r="E121" s="51"/>
       <c r="F121" s="69"/>
     </row>
-    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="223" t="s">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B122" s="74">
+        <f>PRORRATEO!F117</f>
+        <v>14192055.65</v>
+      </c>
+      <c r="D122" s="51"/>
+      <c r="E122" s="51"/>
+      <c r="F122" s="69"/>
+    </row>
+    <row r="123" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B123" s="170">
+        <v>-110000</v>
+      </c>
+      <c r="D123" s="51"/>
+      <c r="E123" s="51"/>
+      <c r="F123" s="69"/>
+    </row>
+    <row r="124" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="B124" s="170">
+        <v>-6066</v>
+      </c>
+      <c r="D124" s="51"/>
+      <c r="E124" s="51"/>
+      <c r="F124" s="69"/>
+    </row>
+    <row r="125" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="B125" s="170">
+        <v>-20610</v>
+      </c>
+      <c r="D125" s="51"/>
+      <c r="E125" s="51"/>
+      <c r="F125" s="69"/>
+    </row>
+    <row r="126" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B126" s="170">
+        <v>-50000</v>
+      </c>
+      <c r="D126" s="51"/>
+      <c r="E126" s="51"/>
+      <c r="F126" s="69"/>
+    </row>
+    <row r="127" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="171" t="s">
+        <v>235</v>
+      </c>
+      <c r="B127" s="174">
+        <f>300000+B128-123612</f>
+        <v>44388</v>
+      </c>
+      <c r="D127" s="51"/>
+      <c r="E127" s="51"/>
+      <c r="F127" s="69"/>
+    </row>
+    <row r="128" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="171" t="s">
+        <v>225</v>
+      </c>
+      <c r="B128" s="137">
+        <v>-132000</v>
+      </c>
+      <c r="D128" s="51"/>
+      <c r="E128" s="51"/>
+      <c r="F128" s="69"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="171" t="s">
+        <v>232</v>
+      </c>
+      <c r="B129" s="172">
+        <f>150000+B128</f>
+        <v>18000</v>
+      </c>
+      <c r="D129" s="51"/>
+      <c r="E129" s="51"/>
+      <c r="F129" s="69"/>
+    </row>
+    <row r="130" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="171" t="s">
         <v>228</v>
       </c>
-      <c r="B122" s="141">
+      <c r="B130" s="137">
         <v>-132000</v>
       </c>
-      <c r="F122" s="69"/>
-    </row>
-    <row r="123" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="75" t="s">
+      <c r="F130" s="69"/>
+    </row>
+    <row r="131" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="B123" s="76">
-        <f>SUM(B111:C122)</f>
-        <v>-1256883.9962549638</v>
-      </c>
-      <c r="D123" s="69"/>
-      <c r="E123" s="53"/>
-      <c r="F123" s="53"/>
-    </row>
-    <row r="124" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="189" t="s">
+      <c r="B131" s="76">
+        <f>SUM(B119:C130)</f>
+        <v>-1256883.5662549641</v>
+      </c>
+      <c r="D131" s="69"/>
+      <c r="E131" s="53"/>
+      <c r="F131" s="53"/>
+    </row>
+    <row r="132" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="198" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="189"/>
-      <c r="C125" s="189"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="189"/>
-      <c r="B126" s="189"/>
-      <c r="C126" s="189"/>
-    </row>
-    <row r="127" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="77" t="s">
+      <c r="B133" s="198"/>
+      <c r="C133" s="198"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="198"/>
+      <c r="B134" s="198"/>
+      <c r="C134" s="198"/>
+    </row>
+    <row r="135" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="77" t="s">
         <v>231</v>
       </c>
-      <c r="B127" s="129">
+      <c r="B135" s="126">
         <v>195940.3</v>
       </c>
-      <c r="C127" s="78"/>
-      <c r="D127" s="59"/>
-    </row>
-    <row r="128" spans="1:6" s="178" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="225" t="s">
+      <c r="C135" s="78"/>
+      <c r="D135" s="59"/>
+    </row>
+    <row r="136" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="173" t="s">
         <v>234</v>
       </c>
-      <c r="B128" s="129">
+      <c r="B136" s="126">
         <v>168841.60000000001</v>
       </c>
-      <c r="C128" s="78"/>
-      <c r="D128" s="59"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B129" s="80">
-        <f>SUM(B127:B128)</f>
+      <c r="C136" s="78"/>
+      <c r="D136" s="59"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" s="80">
+        <f>SUM(B135:B136)</f>
         <v>364781.9</v>
       </c>
-      <c r="C129" s="81"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M130" s="82"/>
+      <c r="C137" s="81"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M138" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A104:B106"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A125:C126"/>
-    <mergeCell ref="A108:B109"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A96:B98"/>
-    <mergeCell ref="A100:B102"/>
+  <mergeCells count="25">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A63:B63"/>
@@ -3646,6 +3645,20 @@
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A104:B106"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A133:C134"/>
+    <mergeCell ref="A116:B117"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A96:B98"/>
+    <mergeCell ref="A100:B102"/>
+    <mergeCell ref="A112:B114"/>
+    <mergeCell ref="A108:B110"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3656,272 +3669,272 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" style="178" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="106"/>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="108"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="109"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111" t="s">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="104"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="106"/>
+    </row>
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="219">
+      <c r="E2" s="208">
         <v>3000000</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="J2" s="112">
-        <v>12074625</v>
-      </c>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="114"/>
+      <c r="J2" s="110">
+        <f>12074625+(12074625*5%)</f>
+        <v>12678356.25</v>
+      </c>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="112"/>
       <c r="O2" s="83"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="115"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="119"/>
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="113"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="117"/>
       <c r="O3" s="83"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="198" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="219" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="199"/>
-      <c r="C4" s="199"/>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
-      <c r="F4" s="199"/>
-      <c r="G4" s="199"/>
-      <c r="H4" s="199"/>
-      <c r="I4" s="199"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="199"/>
-      <c r="L4" s="199"/>
-      <c r="M4" s="199"/>
-      <c r="N4" s="200"/>
+      <c r="B4" s="220"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="221"/>
       <c r="O4" s="83"/>
     </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="201"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="202"/>
-      <c r="N5" s="203"/>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="224"/>
       <c r="O5" s="83"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="201"/>
-      <c r="B6" s="202"/>
-      <c r="C6" s="202"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="M6" s="202"/>
-      <c r="N6" s="203"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="222"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="224"/>
       <c r="O6" s="83"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="201"/>
-      <c r="B7" s="202"/>
-      <c r="C7" s="202"/>
-      <c r="D7" s="202"/>
-      <c r="E7" s="202"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="202"/>
-      <c r="J7" s="202"/>
-      <c r="K7" s="202"/>
-      <c r="L7" s="202"/>
-      <c r="M7" s="202"/>
-      <c r="N7" s="203"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="222"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="224"/>
       <c r="O7" s="83"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="204"/>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="205"/>
-      <c r="E8" s="205"/>
-      <c r="F8" s="205"/>
-      <c r="G8" s="205"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="205"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="205"/>
-      <c r="M8" s="205"/>
-      <c r="N8" s="206"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="213" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="225"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="226"/>
+      <c r="N8" s="227"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="234" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="214"/>
-      <c r="C9" s="214"/>
-      <c r="D9" s="214"/>
-      <c r="E9" s="214"/>
-      <c r="F9" s="214"/>
-      <c r="G9" s="214"/>
-      <c r="H9" s="214"/>
-      <c r="I9" s="214"/>
-      <c r="J9" s="214"/>
-      <c r="K9" s="214"/>
-      <c r="L9" s="214"/>
-      <c r="M9" s="214"/>
-      <c r="N9" s="215"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="216" t="s">
+      <c r="B9" s="235"/>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
+      <c r="N9" s="236"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="237" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
-      <c r="D10" s="217"/>
-      <c r="E10" s="217"/>
-      <c r="F10" s="217"/>
-      <c r="G10" s="217"/>
-      <c r="H10" s="217"/>
-      <c r="I10" s="217"/>
-      <c r="J10" s="217"/>
-      <c r="K10" s="217"/>
-      <c r="L10" s="217"/>
-      <c r="M10" s="217"/>
-      <c r="N10" s="218"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="207" t="s">
+      <c r="B10" s="238"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="239"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="228" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="209" t="s">
+      <c r="B11" s="230" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="209" t="s">
+      <c r="C11" s="230" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="209" t="s">
+      <c r="D11" s="230" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="192" t="s">
+      <c r="E11" s="209" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="209" t="s">
+      <c r="F11" s="230" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="211" t="s">
+      <c r="G11" s="232" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="192" t="s">
+      <c r="H11" s="209" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="192" t="s">
+      <c r="I11" s="209" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="192" t="s">
+      <c r="J11" s="209" t="s">
         <v>128</v>
       </c>
-      <c r="K11" s="220" t="s">
+      <c r="K11" s="211" t="s">
         <v>188</v>
       </c>
-      <c r="L11" s="232" t="s">
+      <c r="L11" s="213" t="s">
         <v>236</v>
       </c>
-      <c r="M11" s="170" t="s">
+      <c r="M11" s="166" t="s">
         <v>138</v>
       </c>
-      <c r="N11" s="194" t="s">
+      <c r="N11" s="215" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="208"/>
-      <c r="B12" s="210"/>
-      <c r="C12" s="210"/>
-      <c r="D12" s="210"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="210"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="193"/>
-      <c r="J12" s="193"/>
-      <c r="K12" s="221"/>
-      <c r="L12" s="233"/>
-      <c r="M12" s="171" t="str">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="229"/>
+      <c r="B12" s="231"/>
+      <c r="C12" s="231"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="210"/>
+      <c r="F12" s="231"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="210"/>
+      <c r="I12" s="210"/>
+      <c r="J12" s="210"/>
+      <c r="K12" s="212"/>
+      <c r="L12" s="214"/>
+      <c r="M12" s="167" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="195"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="154">
+      <c r="N12" s="216"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="150">
         <v>1</v>
       </c>
       <c r="B13" s="84" t="s">
@@ -3946,71 +3959,71 @@
         <f>IF(G13&gt;0,G13*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="145">
         <f t="shared" ref="I13:I44" si="1">J$2*D13/100</f>
-        <v>165422.36250000002</v>
-      </c>
-      <c r="J13" s="149">
+        <v>173693.480625</v>
+      </c>
+      <c r="J13" s="145">
         <f t="shared" ref="J13:J44" si="2">E$2*D13/100</f>
         <v>41100.000000000007</v>
       </c>
-      <c r="K13" s="89"/>
-      <c r="L13" s="227"/>
-      <c r="M13" s="90">
+      <c r="K13" s="145"/>
+      <c r="L13" s="175"/>
+      <c r="M13" s="89">
         <f>ROUND(SUM(G13:L13),0) + O13</f>
-        <v>206522.01</v>
-      </c>
-      <c r="N13" s="165">
+        <v>214793.01</v>
+      </c>
+      <c r="N13" s="161">
         <f t="shared" ref="N13:N33" si="3">ROUND(M13*3%,0) + M13</f>
-        <v>212718.01</v>
+        <v>221237.01</v>
       </c>
       <c r="O13" s="53">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="151">
         <v>2</v>
       </c>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="98">
+      <c r="C14" s="101"/>
+      <c r="D14" s="96">
         <v>1.18</v>
       </c>
-      <c r="E14" s="99">
+      <c r="E14" s="97">
         <v>2734782.02</v>
       </c>
-      <c r="F14" s="99">
+      <c r="F14" s="97">
         <f>10111.62+8904.75+9529.66</f>
         <v>28546.030000000002</v>
       </c>
-      <c r="G14" s="100">
+      <c r="G14" s="98">
         <f t="shared" si="0"/>
         <v>2706235.99</v>
       </c>
-      <c r="H14" s="100">
+      <c r="H14" s="98">
         <f t="shared" ref="H14:H77" si="4">IF(G14&gt;0,G14*3%,0)</f>
         <v>81187.079700000002</v>
       </c>
-      <c r="I14" s="150">
+      <c r="I14" s="146">
         <f t="shared" si="1"/>
-        <v>142480.57500000001</v>
-      </c>
-      <c r="J14" s="150">
+        <v>149604.60375000001</v>
+      </c>
+      <c r="J14" s="146">
         <f t="shared" si="2"/>
         <v>35400</v>
       </c>
-      <c r="K14" s="97"/>
-      <c r="L14" s="228"/>
-      <c r="M14" s="101">
+      <c r="K14" s="146"/>
+      <c r="L14" s="176"/>
+      <c r="M14" s="99">
         <f>ROUND(SUM(G14:L14),0) + O14</f>
-        <v>2965304.02</v>
-      </c>
-      <c r="N14" s="166">
+        <v>2972428.02</v>
+      </c>
+      <c r="N14" s="162">
         <f t="shared" si="3"/>
-        <v>3054263.02</v>
+        <v>3061601.02</v>
       </c>
       <c r="O14" s="53">
         <f>O13+0.01</f>
@@ -4020,14 +4033,14 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="154">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="150">
         <v>3</v>
       </c>
       <c r="B15" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="91"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="85">
         <v>0.74</v>
       </c>
@@ -4046,38 +4059,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I15" s="149">
+      <c r="I15" s="145">
         <f t="shared" si="1"/>
-        <v>89352.225000000006</v>
-      </c>
-      <c r="J15" s="149">
+        <v>93819.836249999993</v>
+      </c>
+      <c r="J15" s="145">
         <f t="shared" si="2"/>
         <v>22200</v>
       </c>
-      <c r="K15" s="89"/>
-      <c r="L15" s="227"/>
-      <c r="M15" s="90">
+      <c r="K15" s="145"/>
+      <c r="L15" s="175"/>
+      <c r="M15" s="89">
         <f t="shared" ref="M15:M78" si="5">ROUND(SUM(G15:L15),0) + O15</f>
-        <v>111552.03</v>
-      </c>
-      <c r="N15" s="165">
+        <v>116020.03</v>
+      </c>
+      <c r="N15" s="161">
         <f t="shared" si="3"/>
-        <v>114899.03</v>
+        <v>119501.03</v>
       </c>
       <c r="O15" s="53">
         <f t="shared" ref="O15:O30" si="6">O14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="156">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="152">
         <v>4</v>
       </c>
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="127"/>
-      <c r="D16" s="123">
+      <c r="C16" s="124"/>
+      <c r="D16" s="121">
         <v>1.47</v>
       </c>
       <c r="E16" s="87">
@@ -4087,39 +4100,39 @@
         <f>E16</f>
         <v>221597.04</v>
       </c>
-      <c r="G16" s="124">
+      <c r="G16" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="124">
+      <c r="H16" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I16" s="151">
+      <c r="I16" s="147">
         <f t="shared" si="1"/>
-        <v>177496.98749999999</v>
-      </c>
-      <c r="J16" s="151">
+        <v>186371.83687500001</v>
+      </c>
+      <c r="J16" s="147">
         <f t="shared" si="2"/>
         <v>44100</v>
       </c>
-      <c r="K16" s="125"/>
-      <c r="L16" s="229"/>
-      <c r="M16" s="90">
+      <c r="K16" s="147"/>
+      <c r="L16" s="177"/>
+      <c r="M16" s="89">
         <f t="shared" si="5"/>
-        <v>221597.04</v>
-      </c>
-      <c r="N16" s="167">
+        <v>230472.04</v>
+      </c>
+      <c r="N16" s="163">
         <f t="shared" si="3"/>
-        <v>228245.04</v>
+        <v>237386.04</v>
       </c>
       <c r="O16" s="53">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="154">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="150">
         <v>5</v>
       </c>
       <c r="B17" s="84" t="s">
@@ -4144,31 +4157,31 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I17" s="149">
+      <c r="I17" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J17" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J17" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K17" s="89"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="90">
+      <c r="K17" s="145"/>
+      <c r="L17" s="175"/>
+      <c r="M17" s="89">
         <f t="shared" si="5"/>
-        <v>168836.05</v>
-      </c>
-      <c r="N17" s="165">
+        <v>175598.05</v>
+      </c>
+      <c r="N17" s="161">
         <f t="shared" si="3"/>
-        <v>173901.05</v>
+        <v>180866.05</v>
       </c>
       <c r="O17" s="53">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="154">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="150">
         <v>6</v>
       </c>
       <c r="B18" s="84" t="s">
@@ -4192,31 +4205,31 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I18" s="149">
+      <c r="I18" s="145">
         <f t="shared" si="1"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J18" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J18" s="145">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K18" s="89"/>
-      <c r="L18" s="227"/>
-      <c r="M18" s="90">
+      <c r="K18" s="145"/>
+      <c r="L18" s="175"/>
+      <c r="M18" s="89">
         <f t="shared" si="5"/>
-        <v>197014.06</v>
-      </c>
-      <c r="N18" s="165">
+        <v>205165.06</v>
+      </c>
+      <c r="N18" s="161">
         <f t="shared" si="3"/>
-        <v>202924.06</v>
+        <v>211320.06</v>
       </c>
       <c r="O18" s="53">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="154">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="150">
         <v>7</v>
       </c>
       <c r="B19" s="84" t="s">
@@ -4241,37 +4254,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I19" s="149">
+      <c r="I19" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J19" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J19" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K19" s="89"/>
-      <c r="L19" s="227"/>
-      <c r="M19" s="90">
+      <c r="K19" s="145"/>
+      <c r="L19" s="175"/>
+      <c r="M19" s="89">
         <f t="shared" si="5"/>
-        <v>168836.07</v>
-      </c>
-      <c r="N19" s="165">
+        <v>175598.07</v>
+      </c>
+      <c r="N19" s="161">
         <f t="shared" si="3"/>
-        <v>173901.07</v>
+        <v>180866.07</v>
       </c>
       <c r="O19" s="53">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="154">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="150">
         <v>8</v>
       </c>
       <c r="B20" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="91"/>
+      <c r="C20" s="90"/>
       <c r="D20" s="85">
         <v>0.82</v>
       </c>
@@ -4290,37 +4303,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I20" s="149">
+      <c r="I20" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J20" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J20" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K20" s="89"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="90">
+      <c r="K20" s="145"/>
+      <c r="L20" s="175"/>
+      <c r="M20" s="89">
         <f t="shared" si="5"/>
-        <v>123612.08</v>
-      </c>
-      <c r="N20" s="165">
+        <v>128563.08</v>
+      </c>
+      <c r="N20" s="161">
         <f t="shared" si="3"/>
-        <v>127320.08</v>
+        <v>132420.08000000002</v>
       </c>
       <c r="O20" s="53">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="154">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="150">
         <v>9</v>
       </c>
       <c r="B21" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="91"/>
+      <c r="C21" s="90"/>
       <c r="D21" s="85">
         <v>0.82</v>
       </c>
@@ -4338,37 +4351,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I21" s="149">
+      <c r="I21" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J21" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J21" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K21" s="89"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="90">
+      <c r="K21" s="145"/>
+      <c r="L21" s="175"/>
+      <c r="M21" s="89">
         <f t="shared" si="5"/>
-        <v>120012.09</v>
-      </c>
-      <c r="N21" s="165">
+        <v>124963.09</v>
+      </c>
+      <c r="N21" s="161">
         <f t="shared" si="3"/>
-        <v>123612.09</v>
+        <v>128712.09</v>
       </c>
       <c r="O21" s="53">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="154">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="150">
         <v>10</v>
       </c>
       <c r="B22" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="91"/>
+      <c r="C22" s="90"/>
       <c r="D22" s="85">
         <v>1.34</v>
       </c>
@@ -4386,37 +4399,37 @@
         <f t="shared" si="4"/>
         <v>181.79999999999998</v>
       </c>
-      <c r="I22" s="149">
+      <c r="I22" s="145">
         <f t="shared" si="1"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J22" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J22" s="145">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K22" s="89"/>
-      <c r="L22" s="227"/>
-      <c r="M22" s="90">
+      <c r="K22" s="145"/>
+      <c r="L22" s="175"/>
+      <c r="M22" s="89">
         <f t="shared" si="5"/>
-        <v>208242.1</v>
-      </c>
-      <c r="N22" s="165">
+        <v>216332.1</v>
+      </c>
+      <c r="N22" s="161">
         <f t="shared" si="3"/>
-        <v>214489.1</v>
+        <v>222822.1</v>
       </c>
       <c r="O22" s="53">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="154">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="150">
         <v>11</v>
       </c>
       <c r="B23" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="91"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -4435,37 +4448,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I23" s="149">
+      <c r="I23" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J23" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J23" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K23" s="89"/>
-      <c r="L23" s="227"/>
-      <c r="M23" s="90">
+      <c r="K23" s="145"/>
+      <c r="L23" s="175"/>
+      <c r="M23" s="89">
         <f t="shared" si="5"/>
-        <v>168836.11</v>
-      </c>
-      <c r="N23" s="165">
+        <v>175598.11</v>
+      </c>
+      <c r="N23" s="161">
         <f t="shared" si="3"/>
-        <v>173901.11</v>
+        <v>180866.11</v>
       </c>
       <c r="O23" s="53">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="154">
+    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="150">
         <v>12</v>
       </c>
       <c r="B24" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="91"/>
+      <c r="C24" s="90"/>
       <c r="D24" s="85">
         <v>1.17</v>
       </c>
@@ -4483,37 +4496,37 @@
         <f t="shared" si="4"/>
         <v>106644.2436</v>
       </c>
-      <c r="I24" s="149">
+      <c r="I24" s="145">
         <f t="shared" si="1"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J24" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J24" s="145">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
-      <c r="K24" s="89"/>
-      <c r="L24" s="227"/>
-      <c r="M24" s="90">
+      <c r="K24" s="145"/>
+      <c r="L24" s="175"/>
+      <c r="M24" s="89">
         <f t="shared" si="5"/>
-        <v>3837825.12</v>
-      </c>
-      <c r="N24" s="165">
+        <v>3844889.12</v>
+      </c>
+      <c r="N24" s="161">
         <f t="shared" si="3"/>
-        <v>3952960.12</v>
+        <v>3960236.12</v>
       </c>
       <c r="O24" s="53">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="154">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="150">
         <v>13</v>
       </c>
       <c r="B25" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="91"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="85">
         <v>1.35</v>
       </c>
@@ -4532,37 +4545,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I25" s="149">
+      <c r="I25" s="145">
         <f t="shared" si="1"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J25" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J25" s="145">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K25" s="89"/>
-      <c r="L25" s="227"/>
-      <c r="M25" s="90">
+      <c r="K25" s="145"/>
+      <c r="L25" s="175"/>
+      <c r="M25" s="89">
         <f t="shared" si="5"/>
-        <v>203507.13</v>
-      </c>
-      <c r="N25" s="165">
+        <v>211658.13</v>
+      </c>
+      <c r="N25" s="161">
         <f t="shared" si="3"/>
-        <v>209612.13</v>
+        <v>218008.13</v>
       </c>
       <c r="O25" s="53">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="154">
+    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="150">
         <v>14</v>
       </c>
       <c r="B26" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="90"/>
       <c r="D26" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -4578,38 +4591,38 @@
         <f t="shared" si="4"/>
         <v>5065.0842000000002</v>
       </c>
-      <c r="I26" s="149">
+      <c r="I26" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J26" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J26" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K26" s="89"/>
-      <c r="L26" s="227"/>
-      <c r="M26" s="90">
+      <c r="K26" s="145"/>
+      <c r="L26" s="175"/>
+      <c r="M26" s="89">
         <f t="shared" si="5"/>
-        <v>342737.14</v>
-      </c>
-      <c r="N26" s="165">
+        <v>349499.14</v>
+      </c>
+      <c r="N26" s="161">
         <f t="shared" si="3"/>
-        <v>353019.14</v>
+        <v>359984.14</v>
       </c>
       <c r="O26" s="53">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="156">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="152">
         <v>15</v>
       </c>
-      <c r="B27" s="121" t="s">
+      <c r="B27" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="127"/>
-      <c r="D27" s="123">
+      <c r="C27" s="124"/>
+      <c r="D27" s="121">
         <v>0.82</v>
       </c>
       <c r="E27" s="87">
@@ -4627,31 +4640,31 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I27" s="149">
+      <c r="I27" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J27" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J27" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K27" s="89"/>
-      <c r="L27" s="227"/>
-      <c r="M27" s="90">
+      <c r="K27" s="145"/>
+      <c r="L27" s="175"/>
+      <c r="M27" s="89">
         <f t="shared" si="5"/>
-        <v>123612.15</v>
-      </c>
-      <c r="N27" s="165">
+        <v>128563.15</v>
+      </c>
+      <c r="N27" s="161">
         <f t="shared" si="3"/>
-        <v>127320.15</v>
+        <v>132420.15</v>
       </c>
       <c r="O27" s="53">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="154">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="150">
         <v>16</v>
       </c>
       <c r="B28" s="84" t="s">
@@ -4675,37 +4688,37 @@
         <f t="shared" si="4"/>
         <v>6386.94</v>
       </c>
-      <c r="I28" s="149">
+      <c r="I28" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J28" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J28" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K28" s="89"/>
-      <c r="L28" s="227"/>
-      <c r="M28" s="90">
+      <c r="K28" s="145"/>
+      <c r="L28" s="175"/>
+      <c r="M28" s="89">
         <f t="shared" si="5"/>
-        <v>342897.16</v>
-      </c>
-      <c r="N28" s="165">
+        <v>347847.16</v>
+      </c>
+      <c r="N28" s="161">
         <f t="shared" si="3"/>
-        <v>353184.16</v>
+        <v>358282.16</v>
       </c>
       <c r="O28" s="53">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="154">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="150">
         <v>17</v>
       </c>
       <c r="B29" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="91"/>
+      <c r="C29" s="90"/>
       <c r="D29" s="85">
         <v>1.34</v>
       </c>
@@ -4724,38 +4737,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I29" s="149">
+      <c r="I29" s="145">
         <f t="shared" si="1"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J29" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J29" s="145">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K29" s="89"/>
-      <c r="L29" s="227"/>
-      <c r="M29" s="90">
+      <c r="K29" s="145"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="89">
         <f t="shared" si="5"/>
-        <v>202000.17</v>
-      </c>
-      <c r="N29" s="165">
+        <v>210090.17</v>
+      </c>
+      <c r="N29" s="161">
         <f t="shared" si="3"/>
-        <v>208060.17</v>
+        <v>216393.17</v>
       </c>
       <c r="O29" s="53">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="156">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="152">
         <v>18</v>
       </c>
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="122"/>
-      <c r="D30" s="123">
+      <c r="C30" s="120"/>
+      <c r="D30" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E30" s="87">
@@ -4765,45 +4778,45 @@
         <f>E30</f>
         <v>163771.18</v>
       </c>
-      <c r="G30" s="124">
+      <c r="G30" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H30" s="124">
+      <c r="H30" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="151">
+      <c r="I30" s="147">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J30" s="151">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J30" s="147">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K30" s="125"/>
-      <c r="L30" s="229"/>
-      <c r="M30" s="90">
+      <c r="K30" s="147"/>
+      <c r="L30" s="177"/>
+      <c r="M30" s="89">
         <f t="shared" si="5"/>
-        <v>168836.18</v>
-      </c>
-      <c r="N30" s="167">
+        <v>175598.18</v>
+      </c>
+      <c r="N30" s="163">
         <f t="shared" si="3"/>
-        <v>173901.18</v>
+        <v>180866.18</v>
       </c>
       <c r="O30" s="53">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="154">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="150">
         <v>19</v>
       </c>
       <c r="B31" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="91"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="85">
         <v>1.17</v>
       </c>
@@ -4821,23 +4834,23 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I31" s="149">
+      <c r="I31" s="145">
         <f t="shared" si="1"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J31" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J31" s="145">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
-      <c r="K31" s="89"/>
-      <c r="L31" s="227"/>
-      <c r="M31" s="90">
+      <c r="K31" s="145"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="89">
         <f t="shared" si="5"/>
-        <v>161299.19</v>
-      </c>
-      <c r="N31" s="165">
+        <v>168363.19</v>
+      </c>
+      <c r="N31" s="161">
         <f t="shared" si="3"/>
-        <v>166138.19</v>
+        <v>173414.19</v>
       </c>
       <c r="O31" s="53">
         <f>O30+0.01</f>
@@ -4847,63 +4860,63 @@
         <v>162</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="157">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="153">
         <v>20</v>
       </c>
-      <c r="B32" s="152" t="s">
+      <c r="B32" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="135"/>
-      <c r="D32" s="136">
+      <c r="C32" s="132"/>
+      <c r="D32" s="133">
         <v>1.35</v>
       </c>
-      <c r="E32" s="137">
+      <c r="E32" s="134">
         <v>413120.2</v>
       </c>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138">
+      <c r="F32" s="134"/>
+      <c r="G32" s="135">
         <f t="shared" si="0"/>
         <v>413120.2</v>
       </c>
-      <c r="H32" s="138"/>
-      <c r="I32" s="153">
+      <c r="H32" s="135"/>
+      <c r="I32" s="149">
         <f t="shared" si="1"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J32" s="153">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J32" s="149">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K32" s="139"/>
-      <c r="L32" s="230">
+      <c r="K32" s="149"/>
+      <c r="L32" s="178">
         <v>123300</v>
       </c>
-      <c r="M32" s="140">
+      <c r="M32" s="136">
         <f t="shared" si="5"/>
-        <v>739928.2</v>
-      </c>
-      <c r="N32" s="168">
+        <v>748078.2</v>
+      </c>
+      <c r="N32" s="164">
         <f t="shared" si="3"/>
-        <v>762126.2</v>
+        <v>770520.2</v>
       </c>
       <c r="O32" s="53">
         <f t="shared" ref="O32:O95" si="7">O31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="156">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="152">
         <v>21</v>
       </c>
-      <c r="B33" s="128" t="s">
+      <c r="B33" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="127"/>
-      <c r="D33" s="123">
+      <c r="C33" s="124"/>
+      <c r="D33" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E33" s="87">
@@ -4913,46 +4926,46 @@
         <f>E33</f>
         <v>168836.21</v>
       </c>
-      <c r="G33" s="124">
+      <c r="G33" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="124">
+      <c r="H33" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I33" s="151">
+      <c r="I33" s="147">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J33" s="151">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J33" s="147">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K33" s="125"/>
-      <c r="L33" s="229"/>
-      <c r="M33" s="90">
+      <c r="K33" s="147"/>
+      <c r="L33" s="177"/>
+      <c r="M33" s="89">
         <f t="shared" si="5"/>
-        <v>168836.21</v>
-      </c>
-      <c r="N33" s="167">
+        <v>175598.21</v>
+      </c>
+      <c r="N33" s="163">
         <f t="shared" si="3"/>
-        <v>173901.21</v>
+        <v>180866.21</v>
       </c>
       <c r="O33" s="53">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="173">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="152">
         <f>A33+1</f>
         <v>22</v>
       </c>
-      <c r="B34" s="174" t="s">
+      <c r="B34" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="C34" s="91"/>
+      <c r="C34" s="90"/>
       <c r="D34" s="85">
         <v>0.82</v>
       </c>
@@ -4970,38 +4983,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I34" s="149">
+      <c r="I34" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J34" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J34" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K34" s="89"/>
-      <c r="L34" s="227"/>
-      <c r="M34" s="90">
+      <c r="K34" s="145"/>
+      <c r="L34" s="175"/>
+      <c r="M34" s="89">
         <f t="shared" si="5"/>
-        <v>120015.22</v>
-      </c>
-      <c r="N34" s="165">
+        <v>124966.22</v>
+      </c>
+      <c r="N34" s="161">
         <f t="shared" ref="N34:N97" si="8">ROUND(M34*3%,0) + M34</f>
-        <v>123615.22</v>
+        <v>128715.22</v>
       </c>
       <c r="O34" s="53">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="154">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="150">
         <f t="shared" ref="A35:A98" si="9">A34+1</f>
         <v>23</v>
       </c>
-      <c r="B35" s="92" t="s">
+      <c r="B35" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="91"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="85">
         <v>0.82</v>
       </c>
@@ -5019,38 +5032,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I35" s="149">
+      <c r="I35" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J35" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J35" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K35" s="89"/>
-      <c r="L35" s="227"/>
-      <c r="M35" s="90">
+      <c r="K35" s="145"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="89">
         <f t="shared" si="5"/>
-        <v>119904.23</v>
-      </c>
-      <c r="N35" s="165">
+        <v>124855.23</v>
+      </c>
+      <c r="N35" s="161">
         <f t="shared" si="8"/>
-        <v>123501.23</v>
+        <v>128601.23</v>
       </c>
       <c r="O35" s="53">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="154">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="150">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="B36" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="91"/>
+      <c r="C36" s="90"/>
       <c r="D36" s="85">
         <v>1.34</v>
       </c>
@@ -5069,38 +5082,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I36" s="149">
+      <c r="I36" s="145">
         <f t="shared" si="1"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J36" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J36" s="145">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K36" s="89"/>
-      <c r="L36" s="227"/>
-      <c r="M36" s="90">
+      <c r="K36" s="145"/>
+      <c r="L36" s="175"/>
+      <c r="M36" s="89">
         <f t="shared" si="5"/>
-        <v>202000.24</v>
-      </c>
-      <c r="N36" s="165">
+        <v>210090.23999999999</v>
+      </c>
+      <c r="N36" s="161">
         <f t="shared" si="8"/>
-        <v>208060.24</v>
+        <v>216393.24</v>
       </c>
       <c r="O36" s="53">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="154">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="150">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="B37" s="92" t="s">
+      <c r="B37" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="91"/>
+      <c r="C37" s="90"/>
       <c r="D37" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -5116,38 +5129,38 @@
         <f t="shared" si="4"/>
         <v>9720.1574999999993</v>
       </c>
-      <c r="I37" s="149">
+      <c r="I37" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J37" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J37" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K37" s="89"/>
-      <c r="L37" s="227"/>
-      <c r="M37" s="90">
+      <c r="K37" s="145"/>
+      <c r="L37" s="175"/>
+      <c r="M37" s="89">
         <f t="shared" si="5"/>
-        <v>502561.25</v>
-      </c>
-      <c r="N37" s="165">
+        <v>509323.25</v>
+      </c>
+      <c r="N37" s="161">
         <f t="shared" si="8"/>
-        <v>517638.25</v>
+        <v>524603.25</v>
       </c>
       <c r="O37" s="53">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="154">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="150">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="B38" s="92" t="s">
+      <c r="B38" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="91"/>
+      <c r="C38" s="90"/>
       <c r="D38" s="85">
         <v>1.17</v>
       </c>
@@ -5165,38 +5178,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I38" s="149">
+      <c r="I38" s="145">
         <f t="shared" si="1"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J38" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J38" s="145">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
-      <c r="K38" s="89"/>
-      <c r="L38" s="227"/>
-      <c r="M38" s="90">
+      <c r="K38" s="145"/>
+      <c r="L38" s="175"/>
+      <c r="M38" s="89">
         <f t="shared" si="5"/>
-        <v>171082.26</v>
-      </c>
-      <c r="N38" s="165">
+        <v>178146.26</v>
+      </c>
+      <c r="N38" s="161">
         <f t="shared" si="8"/>
-        <v>176214.26</v>
+        <v>183490.26</v>
       </c>
       <c r="O38" s="53">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="154">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="150">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="B39" s="92" t="s">
+      <c r="B39" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="91"/>
+      <c r="C39" s="90"/>
       <c r="D39" s="85">
         <v>1.35</v>
       </c>
@@ -5215,38 +5228,40 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I39" s="149">
+      <c r="I39" s="145">
         <f t="shared" si="1"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J39" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J39" s="145">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K39" s="89"/>
-      <c r="L39" s="227"/>
-      <c r="M39" s="90">
+      <c r="K39" s="145">
+        <v>50000</v>
+      </c>
+      <c r="L39" s="175"/>
+      <c r="M39" s="89">
         <f t="shared" si="5"/>
-        <v>203507.27</v>
-      </c>
-      <c r="N39" s="165">
+        <v>261658.27</v>
+      </c>
+      <c r="N39" s="161">
         <f t="shared" si="8"/>
-        <v>209612.27</v>
+        <v>269508.27</v>
       </c>
       <c r="O39" s="53">
         <f t="shared" si="7"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="154">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="150">
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="B40" s="92" t="s">
+      <c r="B40" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="91"/>
+      <c r="C40" s="90"/>
       <c r="D40" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -5264,39 +5279,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="149">
+      <c r="I40" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J40" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J40" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K40" s="89"/>
-      <c r="L40" s="227"/>
-      <c r="M40" s="90">
+      <c r="K40" s="145"/>
+      <c r="L40" s="175"/>
+      <c r="M40" s="89">
         <f t="shared" si="5"/>
-        <v>163918.28</v>
-      </c>
-      <c r="N40" s="165">
+        <v>170680.28</v>
+      </c>
+      <c r="N40" s="161">
         <f t="shared" si="8"/>
-        <v>168836.28</v>
+        <v>175800.28</v>
       </c>
       <c r="O40" s="53">
         <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="156">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="152">
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
-      <c r="B41" s="128" t="s">
+      <c r="B41" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="127"/>
-      <c r="D41" s="123">
+      <c r="C41" s="124"/>
+      <c r="D41" s="121">
         <v>0.82</v>
       </c>
       <c r="E41" s="87">
@@ -5306,31 +5321,31 @@
         <f>E41</f>
         <v>243961.29</v>
       </c>
-      <c r="G41" s="124">
+      <c r="G41" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H41" s="124">
+      <c r="H41" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="151">
+      <c r="I41" s="147">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J41" s="151">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J41" s="147">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K41" s="125"/>
-      <c r="L41" s="229"/>
-      <c r="M41" s="90">
+      <c r="K41" s="147"/>
+      <c r="L41" s="177"/>
+      <c r="M41" s="89">
         <f t="shared" si="5"/>
-        <v>123612.29</v>
-      </c>
-      <c r="N41" s="167">
+        <v>128563.29</v>
+      </c>
+      <c r="N41" s="163">
         <f t="shared" si="8"/>
-        <v>127320.29</v>
+        <v>132420.28999999998</v>
       </c>
       <c r="O41" s="53">
         <f t="shared" si="7"/>
@@ -5340,15 +5355,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="156">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="152">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="B42" s="128" t="s">
+      <c r="B42" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="91"/>
+      <c r="C42" s="90"/>
       <c r="D42" s="85">
         <v>0.82</v>
       </c>
@@ -5366,38 +5381,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I42" s="149">
+      <c r="I42" s="145">
         <f t="shared" si="1"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J42" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J42" s="145">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K42" s="89"/>
-      <c r="L42" s="227"/>
-      <c r="M42" s="90">
+      <c r="K42" s="145"/>
+      <c r="L42" s="175"/>
+      <c r="M42" s="89">
         <f t="shared" si="5"/>
-        <v>123480.3</v>
-      </c>
-      <c r="N42" s="165">
+        <v>128431.3</v>
+      </c>
+      <c r="N42" s="161">
         <f t="shared" si="8"/>
-        <v>127184.3</v>
+        <v>132284.29999999999</v>
       </c>
       <c r="O42" s="53">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="154">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" s="150">
         <f t="shared" si="9"/>
         <v>31</v>
       </c>
-      <c r="B43" s="92" t="s">
+      <c r="B43" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="91"/>
+      <c r="C43" s="90"/>
       <c r="D43" s="85">
         <v>1.34</v>
       </c>
@@ -5416,38 +5431,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I43" s="149">
+      <c r="I43" s="145">
         <f t="shared" si="1"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J43" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J43" s="145">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K43" s="89"/>
-      <c r="L43" s="227"/>
-      <c r="M43" s="90">
+      <c r="K43" s="145"/>
+      <c r="L43" s="175"/>
+      <c r="M43" s="89">
         <f t="shared" si="5"/>
-        <v>202000.31</v>
-      </c>
-      <c r="N43" s="165">
+        <v>210090.31</v>
+      </c>
+      <c r="N43" s="161">
         <f t="shared" si="8"/>
-        <v>208060.31</v>
+        <v>216393.31</v>
       </c>
       <c r="O43" s="53">
         <f t="shared" si="7"/>
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="154">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="150">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
-      <c r="B44" s="92" t="s">
+      <c r="B44" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="91"/>
+      <c r="C44" s="90"/>
       <c r="D44" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -5465,72 +5480,72 @@
         <f t="shared" si="4"/>
         <v>5019.09</v>
       </c>
-      <c r="I44" s="149">
+      <c r="I44" s="145">
         <f t="shared" si="1"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J44" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J44" s="145">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K44" s="89"/>
-      <c r="L44" s="227"/>
-      <c r="M44" s="90">
+      <c r="K44" s="145"/>
+      <c r="L44" s="175"/>
+      <c r="M44" s="89">
         <f t="shared" si="5"/>
-        <v>341158.32</v>
-      </c>
-      <c r="N44" s="165">
+        <v>347920.32</v>
+      </c>
+      <c r="N44" s="161">
         <f t="shared" si="8"/>
-        <v>351393.32</v>
+        <v>358358.32</v>
       </c>
       <c r="O44" s="53">
         <f t="shared" si="7"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="157">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="153">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
-      <c r="B45" s="134" t="s">
+      <c r="B45" s="131" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="135"/>
-      <c r="D45" s="136">
+      <c r="C45" s="132"/>
+      <c r="D45" s="133">
         <v>1.17</v>
       </c>
-      <c r="E45" s="137">
+      <c r="E45" s="134">
         <v>358037.33</v>
       </c>
-      <c r="F45" s="137">
+      <c r="F45" s="134">
         <f>E45</f>
         <v>358037.33</v>
       </c>
-      <c r="G45" s="138">
+      <c r="G45" s="135">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H45" s="138"/>
-      <c r="I45" s="153">
+      <c r="H45" s="135"/>
+      <c r="I45" s="149">
         <f t="shared" ref="I45:I76" si="10">J$2*D45/100</f>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J45" s="153">
+        <v>148336.768125</v>
+      </c>
+      <c r="J45" s="149">
         <f t="shared" ref="J45:J76" si="11">E$2*D45/100</f>
         <v>35100</v>
       </c>
-      <c r="K45" s="139"/>
-      <c r="L45" s="230">
+      <c r="K45" s="149"/>
+      <c r="L45" s="178">
         <v>170000</v>
       </c>
-      <c r="M45" s="140">
+      <c r="M45" s="136">
         <f t="shared" si="5"/>
-        <v>346373.33</v>
-      </c>
-      <c r="N45" s="168">
+        <v>353437.33</v>
+      </c>
+      <c r="N45" s="164">
         <f t="shared" si="8"/>
-        <v>356764.33</v>
+        <v>364040.33</v>
       </c>
       <c r="O45" s="53">
         <f t="shared" si="7"/>
@@ -5540,15 +5555,15 @@
         <v>237</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="154">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="150">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
-      <c r="B46" s="92" t="s">
+      <c r="B46" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="91"/>
+      <c r="C46" s="90"/>
       <c r="D46" s="85">
         <v>1.35</v>
       </c>
@@ -5567,39 +5582,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I46" s="149">
+      <c r="I46" s="145">
         <f t="shared" si="10"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J46" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J46" s="145">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K46" s="89"/>
-      <c r="L46" s="227"/>
-      <c r="M46" s="90">
+      <c r="K46" s="145"/>
+      <c r="L46" s="175"/>
+      <c r="M46" s="89">
         <f t="shared" si="5"/>
-        <v>203507.34</v>
-      </c>
-      <c r="N46" s="165">
+        <v>211658.34</v>
+      </c>
+      <c r="N46" s="161">
         <f t="shared" si="8"/>
-        <v>209612.34</v>
+        <v>218008.34</v>
       </c>
       <c r="O46" s="53">
         <f t="shared" si="7"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="156">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="152">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="B47" s="128" t="s">
+      <c r="B47" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="127"/>
-      <c r="D47" s="123">
+      <c r="C47" s="124"/>
+      <c r="D47" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E47" s="87">
@@ -5608,31 +5623,31 @@
       <c r="F47" s="87">
         <v>342000</v>
       </c>
-      <c r="G47" s="124">
+      <c r="G47" s="122">
         <f t="shared" si="0"/>
         <v>-27147.650000000023</v>
       </c>
-      <c r="H47" s="124">
+      <c r="H47" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I47" s="151">
+      <c r="I47" s="147">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J47" s="151">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J47" s="147">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K47" s="125"/>
-      <c r="L47" s="229"/>
-      <c r="M47" s="90">
+      <c r="K47" s="147"/>
+      <c r="L47" s="177"/>
+      <c r="M47" s="89">
         <f t="shared" si="5"/>
-        <v>141688.35</v>
-      </c>
-      <c r="N47" s="167">
+        <v>148450.35</v>
+      </c>
+      <c r="N47" s="163">
         <f t="shared" si="8"/>
-        <v>145939.35</v>
+        <v>152904.35</v>
       </c>
       <c r="O47" s="53">
         <f t="shared" si="7"/>
@@ -5642,15 +5657,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="154">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="150">
         <f t="shared" si="9"/>
         <v>36</v>
       </c>
-      <c r="B48" s="92" t="s">
+      <c r="B48" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="91"/>
+      <c r="C48" s="90"/>
       <c r="D48" s="85">
         <v>0.82</v>
       </c>
@@ -5669,23 +5684,23 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I48" s="149">
+      <c r="I48" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J48" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J48" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K48" s="89"/>
-      <c r="L48" s="227"/>
-      <c r="M48" s="90">
+      <c r="K48" s="145"/>
+      <c r="L48" s="175"/>
+      <c r="M48" s="89">
         <f t="shared" si="5"/>
-        <v>123612.36</v>
-      </c>
-      <c r="N48" s="165">
+        <v>128563.36</v>
+      </c>
+      <c r="N48" s="161">
         <f t="shared" si="8"/>
-        <v>127320.36</v>
+        <v>132420.35999999999</v>
       </c>
       <c r="O48" s="53">
         <f t="shared" si="7"/>
@@ -5695,15 +5710,15 @@
         <v>163</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="154">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" s="150">
         <f t="shared" si="9"/>
         <v>37</v>
       </c>
-      <c r="B49" s="92" t="s">
+      <c r="B49" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="91"/>
+      <c r="C49" s="90"/>
       <c r="D49" s="85">
         <v>0.82</v>
       </c>
@@ -5722,38 +5737,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I49" s="149">
+      <c r="I49" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J49" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J49" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K49" s="89"/>
-      <c r="L49" s="227"/>
-      <c r="M49" s="90">
+      <c r="K49" s="145"/>
+      <c r="L49" s="175"/>
+      <c r="M49" s="89">
         <f t="shared" si="5"/>
-        <v>123612.37</v>
-      </c>
-      <c r="N49" s="165">
+        <v>128563.37</v>
+      </c>
+      <c r="N49" s="161">
         <f t="shared" si="8"/>
-        <v>127320.37</v>
+        <v>132420.37</v>
       </c>
       <c r="O49" s="53">
         <f t="shared" si="7"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="154">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50" s="150">
         <f t="shared" si="9"/>
         <v>38</v>
       </c>
-      <c r="B50" s="92" t="s">
+      <c r="B50" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="91"/>
+      <c r="C50" s="90"/>
       <c r="D50" s="85">
         <v>1.34</v>
       </c>
@@ -5769,38 +5784,38 @@
         <f t="shared" si="4"/>
         <v>12114.581399999999</v>
       </c>
-      <c r="I50" s="149">
+      <c r="I50" s="145">
         <f t="shared" si="10"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J50" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J50" s="145">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K50" s="89"/>
-      <c r="L50" s="227"/>
-      <c r="M50" s="90">
+      <c r="K50" s="145"/>
+      <c r="L50" s="175"/>
+      <c r="M50" s="89">
         <f t="shared" si="5"/>
-        <v>617934.38</v>
-      </c>
-      <c r="N50" s="165">
+        <v>626024.38</v>
+      </c>
+      <c r="N50" s="161">
         <f t="shared" si="8"/>
-        <v>636472.38</v>
+        <v>644805.38</v>
       </c>
       <c r="O50" s="53">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="154">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="150">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
-      <c r="B51" s="92" t="s">
+      <c r="B51" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="91"/>
+      <c r="C51" s="90"/>
       <c r="D51" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -5819,38 +5834,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I51" s="149">
+      <c r="I51" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J51" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J51" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K51" s="89"/>
-      <c r="L51" s="227"/>
-      <c r="M51" s="90">
+      <c r="K51" s="145"/>
+      <c r="L51" s="175"/>
+      <c r="M51" s="89">
         <f t="shared" si="5"/>
-        <v>168836.39</v>
-      </c>
-      <c r="N51" s="165">
+        <v>175598.39</v>
+      </c>
+      <c r="N51" s="161">
         <f t="shared" si="8"/>
-        <v>173901.39</v>
+        <v>180866.39</v>
       </c>
       <c r="O51" s="53">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="154">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="150">
         <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="B52" s="92" t="s">
+      <c r="B52" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="91"/>
+      <c r="C52" s="90"/>
       <c r="D52" s="85">
         <v>1.17</v>
       </c>
@@ -5866,38 +5881,38 @@
         <f t="shared" si="4"/>
         <v>16354.602000000001</v>
       </c>
-      <c r="I52" s="149">
+      <c r="I52" s="145">
         <f t="shared" si="10"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J52" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J52" s="145">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
-      <c r="K52" s="89"/>
-      <c r="L52" s="227"/>
-      <c r="M52" s="90">
+      <c r="K52" s="145"/>
+      <c r="L52" s="175"/>
+      <c r="M52" s="89">
         <f t="shared" si="5"/>
-        <v>737881.4</v>
-      </c>
-      <c r="N52" s="165">
+        <v>744945.4</v>
+      </c>
+      <c r="N52" s="161">
         <f t="shared" si="8"/>
-        <v>760017.4</v>
+        <v>767293.4</v>
       </c>
       <c r="O52" s="53">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="154">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="150">
         <f t="shared" si="9"/>
         <v>41</v>
       </c>
-      <c r="B53" s="92" t="s">
+      <c r="B53" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="91"/>
+      <c r="C53" s="90"/>
       <c r="D53" s="85">
         <v>1.35</v>
       </c>
@@ -5915,134 +5930,145 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I53" s="149">
+      <c r="I53" s="145">
         <f t="shared" si="10"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J53" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J53" s="145">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K53" s="89"/>
-      <c r="L53" s="227"/>
-      <c r="M53" s="90">
+      <c r="K53" s="145"/>
+      <c r="L53" s="175"/>
+      <c r="M53" s="89">
         <f t="shared" si="5"/>
-        <v>197585.41</v>
-      </c>
-      <c r="N53" s="165">
+        <v>205736.41</v>
+      </c>
+      <c r="N53" s="161">
         <f t="shared" si="8"/>
-        <v>203513.41</v>
+        <v>211908.41</v>
       </c>
       <c r="O53" s="53">
         <f t="shared" si="7"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="157">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="153">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="135"/>
-      <c r="D54" s="136">
+      <c r="C54" s="132"/>
+      <c r="D54" s="133">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E54" s="137">
+      <c r="E54" s="134">
         <v>201845.42</v>
       </c>
-      <c r="F54" s="137">
+      <c r="F54" s="134">
         <f>E54</f>
         <v>201845.42</v>
       </c>
-      <c r="G54" s="138">
+      <c r="G54" s="135">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H54" s="138"/>
-      <c r="I54" s="153">
+      <c r="H54" s="135"/>
+      <c r="I54" s="149">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J54" s="153">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J54" s="149">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K54" s="139"/>
-      <c r="L54" s="230"/>
-      <c r="M54" s="140">
+      <c r="K54" s="149"/>
+      <c r="L54" s="178">
+        <v>33000</v>
+      </c>
+      <c r="M54" s="136">
         <f t="shared" si="5"/>
-        <v>168836.42</v>
-      </c>
-      <c r="N54" s="168">
+        <v>208598.42</v>
+      </c>
+      <c r="N54" s="164">
         <f t="shared" si="8"/>
-        <v>173901.42</v>
+        <v>214856.42</v>
       </c>
       <c r="O54" s="53">
         <f t="shared" si="7"/>
         <v>0.42000000000000021</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="154">
+      <c r="P54" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="153">
         <f t="shared" si="9"/>
         <v>43</v>
       </c>
-      <c r="B55" s="92" t="s">
+      <c r="B55" s="131" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="91"/>
-      <c r="D55" s="85">
+      <c r="C55" s="132"/>
+      <c r="D55" s="133">
         <v>0.82</v>
       </c>
-      <c r="E55" s="86">
-        <v>1858968.43</v>
-      </c>
-      <c r="F55" s="87">
-        <v>0</v>
-      </c>
-      <c r="G55" s="88">
+      <c r="E55" s="240">
+        <v>123612.43</v>
+      </c>
+      <c r="F55" s="134">
+        <f>E55</f>
+        <v>123612.43</v>
+      </c>
+      <c r="G55" s="135">
         <f t="shared" si="0"/>
-        <v>1858968.43</v>
-      </c>
-      <c r="H55" s="88">
+        <v>0</v>
+      </c>
+      <c r="H55" s="135">
         <f t="shared" si="4"/>
-        <v>55769.052899999995</v>
+        <v>0</v>
       </c>
       <c r="I55" s="149">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
+        <v>103962.52125000001</v>
       </c>
       <c r="J55" s="149">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K55" s="89"/>
-      <c r="L55" s="227"/>
-      <c r="M55" s="90">
-        <f t="shared" si="5"/>
-        <v>2038349.43</v>
-      </c>
-      <c r="N55" s="165">
+      <c r="K55" s="149"/>
+      <c r="L55" s="178">
+        <v>300000</v>
+      </c>
+      <c r="M55" s="136">
+        <f>ROUND(SUM(G55:L55),0) + O55</f>
+        <v>428563.43</v>
+      </c>
+      <c r="N55" s="164">
         <f t="shared" si="8"/>
-        <v>2099499.4299999997</v>
+        <v>441420.43</v>
       </c>
       <c r="O55" s="53">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="154">
+      <c r="P55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="150">
         <f t="shared" si="9"/>
         <v>44</v>
       </c>
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="91"/>
+      <c r="C56" s="90"/>
       <c r="D56" s="85">
         <v>0.82</v>
       </c>
@@ -6061,38 +6087,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I56" s="149">
+      <c r="I56" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J56" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J56" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K56" s="89"/>
-      <c r="L56" s="227"/>
-      <c r="M56" s="90">
+      <c r="K56" s="145"/>
+      <c r="L56" s="175"/>
+      <c r="M56" s="89">
         <f t="shared" si="5"/>
-        <v>123612.44</v>
-      </c>
-      <c r="N56" s="165">
+        <v>128563.44</v>
+      </c>
+      <c r="N56" s="161">
         <f t="shared" si="8"/>
-        <v>127320.44</v>
+        <v>132420.44</v>
       </c>
       <c r="O56" s="53">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="154">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="150">
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
-      <c r="B57" s="92" t="s">
+      <c r="B57" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="91"/>
+      <c r="C57" s="90"/>
       <c r="D57" s="85">
         <v>1.34</v>
       </c>
@@ -6111,38 +6137,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I57" s="149">
+      <c r="I57" s="145">
         <f t="shared" si="10"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J57" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J57" s="145">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K57" s="89"/>
-      <c r="L57" s="227"/>
-      <c r="M57" s="90">
+      <c r="K57" s="145"/>
+      <c r="L57" s="175"/>
+      <c r="M57" s="89">
         <f t="shared" si="5"/>
-        <v>202000.45</v>
-      </c>
-      <c r="N57" s="165">
+        <v>210090.45</v>
+      </c>
+      <c r="N57" s="161">
         <f t="shared" si="8"/>
-        <v>208060.45</v>
+        <v>216393.45</v>
       </c>
       <c r="O57" s="53">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="156">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="152">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="B58" s="128" t="s">
+      <c r="B58" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="91"/>
+      <c r="C58" s="90"/>
       <c r="D58" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -6160,23 +6186,23 @@
         <f t="shared" si="4"/>
         <v>639.97379999999976</v>
       </c>
-      <c r="I58" s="149">
+      <c r="I58" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J58" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J58" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K58" s="89"/>
-      <c r="L58" s="227"/>
-      <c r="M58" s="90">
+      <c r="K58" s="145"/>
+      <c r="L58" s="175"/>
+      <c r="M58" s="89">
         <f t="shared" si="5"/>
-        <v>190808.46</v>
-      </c>
-      <c r="N58" s="165">
+        <v>197570.46</v>
+      </c>
+      <c r="N58" s="161">
         <f t="shared" si="8"/>
-        <v>196532.46</v>
+        <v>203497.46</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="7"/>
@@ -6186,49 +6212,49 @@
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="157">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="153">
         <f t="shared" si="9"/>
         <v>47</v>
       </c>
-      <c r="B59" s="134" t="s">
+      <c r="B59" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="135"/>
-      <c r="D59" s="136">
+      <c r="C59" s="132"/>
+      <c r="D59" s="133">
         <v>1.17</v>
       </c>
-      <c r="E59" s="137">
+      <c r="E59" s="134">
         <v>173374.17</v>
       </c>
-      <c r="F59" s="137">
+      <c r="F59" s="134">
         <f>E59</f>
         <v>173374.17</v>
       </c>
-      <c r="G59" s="138">
+      <c r="G59" s="135">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H59" s="138"/>
-      <c r="I59" s="153">
+      <c r="H59" s="135"/>
+      <c r="I59" s="149">
         <f t="shared" si="10"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J59" s="153">
+        <v>148336.768125</v>
+      </c>
+      <c r="J59" s="149">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
-      <c r="K59" s="139"/>
-      <c r="L59" s="230">
+      <c r="K59" s="149"/>
+      <c r="L59" s="178">
         <v>135000</v>
       </c>
-      <c r="M59" s="140">
+      <c r="M59" s="136">
         <f t="shared" si="5"/>
-        <v>311373.46999999997</v>
-      </c>
-      <c r="N59" s="168">
+        <v>318437.46999999997</v>
+      </c>
+      <c r="N59" s="164">
         <f t="shared" si="8"/>
-        <v>320714.46999999997</v>
+        <v>327990.46999999997</v>
       </c>
       <c r="O59" s="53">
         <f t="shared" si="7"/>
@@ -6238,16 +6264,16 @@
         <v>239</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="156">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="152">
         <f t="shared" si="9"/>
         <v>48</v>
       </c>
-      <c r="B60" s="128" t="s">
+      <c r="B60" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="C60" s="127"/>
-      <c r="D60" s="123">
+      <c r="C60" s="124"/>
+      <c r="D60" s="121">
         <v>1.35</v>
       </c>
       <c r="E60" s="87">
@@ -6257,31 +6283,31 @@
         <f>E60</f>
         <v>209612.48</v>
       </c>
-      <c r="G60" s="124">
+      <c r="G60" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H60" s="124">
+      <c r="H60" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I60" s="151">
+      <c r="I60" s="147">
         <f t="shared" si="10"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J60" s="151">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J60" s="147">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K60" s="125"/>
-      <c r="L60" s="229"/>
-      <c r="M60" s="90">
+      <c r="K60" s="147"/>
+      <c r="L60" s="177"/>
+      <c r="M60" s="89">
         <f t="shared" si="5"/>
-        <v>203507.48</v>
-      </c>
-      <c r="N60" s="167">
+        <v>211658.48</v>
+      </c>
+      <c r="N60" s="163">
         <f t="shared" si="8"/>
-        <v>209612.48</v>
+        <v>218008.48</v>
       </c>
       <c r="O60" s="53">
         <f t="shared" si="7"/>
@@ -6291,16 +6317,16 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="156">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="152">
         <f t="shared" si="9"/>
         <v>49</v>
       </c>
-      <c r="B61" s="128" t="s">
+      <c r="B61" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="C61" s="127"/>
-      <c r="D61" s="123">
+      <c r="C61" s="124"/>
+      <c r="D61" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E61" s="86">
@@ -6317,39 +6343,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I61" s="149">
+      <c r="I61" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J61" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J61" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K61" s="89"/>
-      <c r="L61" s="227"/>
-      <c r="M61" s="90">
+      <c r="K61" s="145"/>
+      <c r="L61" s="175"/>
+      <c r="M61" s="89">
         <f t="shared" si="5"/>
-        <v>163918.49</v>
-      </c>
-      <c r="N61" s="165">
+        <v>170680.49</v>
+      </c>
+      <c r="N61" s="161">
         <f t="shared" si="8"/>
-        <v>168836.49</v>
+        <v>175800.49</v>
       </c>
       <c r="O61" s="53">
         <f t="shared" si="7"/>
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="156">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="152">
         <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="B62" s="128" t="s">
+      <c r="B62" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="C62" s="127"/>
-      <c r="D62" s="123">
+      <c r="C62" s="124"/>
+      <c r="D62" s="121">
         <v>0.82</v>
       </c>
       <c r="E62" s="86">
@@ -6364,39 +6390,39 @@
         <f t="shared" si="4"/>
         <v>3708.375</v>
       </c>
-      <c r="I62" s="149">
+      <c r="I62" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J62" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J62" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K62" s="89"/>
-      <c r="L62" s="227"/>
-      <c r="M62" s="90">
+      <c r="K62" s="145"/>
+      <c r="L62" s="175"/>
+      <c r="M62" s="89">
         <f t="shared" si="5"/>
-        <v>250933.5</v>
-      </c>
-      <c r="N62" s="165">
+        <v>255883.5</v>
+      </c>
+      <c r="N62" s="161">
         <f t="shared" si="8"/>
-        <v>258461.5</v>
+        <v>263560.5</v>
       </c>
       <c r="O62" s="53">
         <f t="shared" si="7"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="156">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="152">
         <f t="shared" si="9"/>
         <v>51</v>
       </c>
-      <c r="B63" s="128" t="s">
+      <c r="B63" s="125" t="s">
         <v>51</v>
       </c>
-      <c r="C63" s="127"/>
-      <c r="D63" s="123">
+      <c r="C63" s="124"/>
+      <c r="D63" s="121">
         <v>0.82</v>
       </c>
       <c r="E63" s="86">
@@ -6414,39 +6440,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I63" s="149">
+      <c r="I63" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J63" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J63" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K63" s="89"/>
-      <c r="L63" s="227"/>
-      <c r="M63" s="90">
+      <c r="K63" s="145"/>
+      <c r="L63" s="175"/>
+      <c r="M63" s="89">
         <f t="shared" si="5"/>
-        <v>123612.51</v>
-      </c>
-      <c r="N63" s="165">
+        <v>128563.51</v>
+      </c>
+      <c r="N63" s="161">
         <f t="shared" si="8"/>
-        <v>127320.51</v>
+        <v>132420.51</v>
       </c>
       <c r="O63" s="53">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="156">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="152">
         <f t="shared" si="9"/>
         <v>52</v>
       </c>
-      <c r="B64" s="128" t="s">
+      <c r="B64" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="127"/>
-      <c r="D64" s="123">
+      <c r="C64" s="124"/>
+      <c r="D64" s="121">
         <v>1.34</v>
       </c>
       <c r="E64" s="86">
@@ -6464,39 +6490,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I64" s="149">
+      <c r="I64" s="145">
         <f t="shared" si="10"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J64" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J64" s="145">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K64" s="89"/>
-      <c r="L64" s="227"/>
-      <c r="M64" s="90">
+      <c r="K64" s="145"/>
+      <c r="L64" s="175"/>
+      <c r="M64" s="89">
         <f t="shared" si="5"/>
-        <v>202000.52</v>
-      </c>
-      <c r="N64" s="165">
+        <v>210090.52</v>
+      </c>
+      <c r="N64" s="161">
         <f t="shared" si="8"/>
-        <v>208060.52</v>
+        <v>216393.52</v>
       </c>
       <c r="O64" s="53">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="156">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="152">
         <f t="shared" si="9"/>
         <v>53</v>
       </c>
-      <c r="B65" s="128" t="s">
+      <c r="B65" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="C65" s="127"/>
-      <c r="D65" s="123">
+      <c r="C65" s="124"/>
+      <c r="D65" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E65" s="87">
@@ -6514,39 +6540,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I65" s="149">
+      <c r="I65" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J65" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J65" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K65" s="89"/>
-      <c r="L65" s="227"/>
-      <c r="M65" s="90">
+      <c r="K65" s="145"/>
+      <c r="L65" s="175"/>
+      <c r="M65" s="89">
         <f t="shared" si="5"/>
-        <v>162770.53</v>
-      </c>
-      <c r="N65" s="165">
+        <v>169532.53</v>
+      </c>
+      <c r="N65" s="161">
         <f t="shared" si="8"/>
-        <v>167653.53</v>
+        <v>174618.53</v>
       </c>
       <c r="O65" s="53">
         <f t="shared" si="7"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="156">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="152">
         <f t="shared" si="9"/>
         <v>54</v>
       </c>
-      <c r="B66" s="128" t="s">
+      <c r="B66" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="127"/>
-      <c r="D66" s="123">
+      <c r="C66" s="124"/>
+      <c r="D66" s="121">
         <v>1.17</v>
       </c>
       <c r="E66" s="86">
@@ -6564,39 +6590,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I66" s="149">
+      <c r="I66" s="145">
         <f t="shared" si="10"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J66" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J66" s="145">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
-      <c r="K66" s="89"/>
-      <c r="L66" s="227"/>
-      <c r="M66" s="90">
+      <c r="K66" s="145"/>
+      <c r="L66" s="175"/>
+      <c r="M66" s="89">
         <f t="shared" si="5"/>
-        <v>176373.54</v>
-      </c>
-      <c r="N66" s="165">
+        <v>183437.54</v>
+      </c>
+      <c r="N66" s="161">
         <f t="shared" si="8"/>
-        <v>181664.54</v>
+        <v>188940.54</v>
       </c>
       <c r="O66" s="53">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="156">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="152">
         <f t="shared" si="9"/>
         <v>55</v>
       </c>
-      <c r="B67" s="128" t="s">
+      <c r="B67" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="127"/>
-      <c r="D67" s="123">
+      <c r="C67" s="124"/>
+      <c r="D67" s="121">
         <v>1.35</v>
       </c>
       <c r="E67" s="86">
@@ -6613,39 +6639,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I67" s="149">
+      <c r="I67" s="145">
         <f t="shared" si="10"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J67" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J67" s="145">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K67" s="89"/>
-      <c r="L67" s="227"/>
-      <c r="M67" s="90">
+      <c r="K67" s="145"/>
+      <c r="L67" s="175"/>
+      <c r="M67" s="89">
         <f t="shared" si="5"/>
-        <v>197579.55</v>
-      </c>
-      <c r="N67" s="165">
+        <v>205730.55</v>
+      </c>
+      <c r="N67" s="161">
         <f t="shared" si="8"/>
-        <v>203506.55</v>
+        <v>211902.55</v>
       </c>
       <c r="O67" s="53">
         <f t="shared" si="7"/>
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="156">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="152">
         <f t="shared" si="9"/>
         <v>56</v>
       </c>
-      <c r="B68" s="128" t="s">
+      <c r="B68" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C68" s="127"/>
-      <c r="D68" s="123">
+      <c r="C68" s="124"/>
+      <c r="D68" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E68" s="86">
@@ -6663,39 +6689,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I68" s="149">
+      <c r="I68" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J68" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J68" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K68" s="89"/>
-      <c r="L68" s="227"/>
-      <c r="M68" s="90">
+      <c r="K68" s="145"/>
+      <c r="L68" s="175"/>
+      <c r="M68" s="89">
         <f t="shared" si="5"/>
-        <v>168836.56</v>
-      </c>
-      <c r="N68" s="165">
+        <v>175598.56</v>
+      </c>
+      <c r="N68" s="161">
         <f t="shared" si="8"/>
-        <v>173901.56</v>
+        <v>180866.56</v>
       </c>
       <c r="O68" s="53">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="156">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" s="152">
         <f t="shared" si="9"/>
         <v>57</v>
       </c>
-      <c r="B69" s="128" t="s">
+      <c r="B69" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C69" s="127"/>
-      <c r="D69" s="123">
+      <c r="C69" s="124"/>
+      <c r="D69" s="121">
         <v>0.82</v>
       </c>
       <c r="E69" s="86">
@@ -6712,39 +6738,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I69" s="149">
+      <c r="I69" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J69" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J69" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K69" s="89"/>
-      <c r="L69" s="227"/>
-      <c r="M69" s="90">
+      <c r="K69" s="145"/>
+      <c r="L69" s="175"/>
+      <c r="M69" s="89">
         <f t="shared" si="5"/>
-        <v>123602.57</v>
-      </c>
-      <c r="N69" s="165">
+        <v>128553.57</v>
+      </c>
+      <c r="N69" s="161">
         <f t="shared" si="8"/>
-        <v>127310.57</v>
+        <v>132410.57</v>
       </c>
       <c r="O69" s="53">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="156">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="152">
         <f t="shared" si="9"/>
         <v>58</v>
       </c>
-      <c r="B70" s="128" t="s">
+      <c r="B70" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="127"/>
-      <c r="D70" s="123">
+      <c r="C70" s="124"/>
+      <c r="D70" s="121">
         <v>0.82</v>
       </c>
       <c r="E70" s="86">
@@ -6762,39 +6788,39 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I70" s="149">
+      <c r="I70" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J70" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J70" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K70" s="89"/>
-      <c r="L70" s="227"/>
-      <c r="M70" s="90">
+      <c r="K70" s="145"/>
+      <c r="L70" s="175"/>
+      <c r="M70" s="89">
         <f t="shared" si="5"/>
-        <v>123612.58</v>
-      </c>
-      <c r="N70" s="165">
+        <v>128563.58</v>
+      </c>
+      <c r="N70" s="161">
         <f t="shared" si="8"/>
-        <v>127320.58</v>
+        <v>132420.58000000002</v>
       </c>
       <c r="O70" s="53">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="156">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="152">
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
-      <c r="B71" s="128" t="s">
+      <c r="B71" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="127"/>
-      <c r="D71" s="123">
+      <c r="C71" s="124"/>
+      <c r="D71" s="121">
         <v>1.34</v>
       </c>
       <c r="E71" s="87">
@@ -6803,47 +6829,47 @@
       <c r="F71" s="87">
         <v>208060.59</v>
       </c>
-      <c r="G71" s="124">
+      <c r="G71" s="122">
         <f t="shared" si="0"/>
         <v>-6060</v>
       </c>
-      <c r="H71" s="124">
+      <c r="H71" s="122">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I71" s="151">
+      <c r="I71" s="147">
         <f t="shared" si="10"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J71" s="151">
+        <v>169889.97375</v>
+      </c>
+      <c r="J71" s="147">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K71" s="125"/>
-      <c r="L71" s="229"/>
-      <c r="M71" s="90">
+      <c r="K71" s="147"/>
+      <c r="L71" s="177"/>
+      <c r="M71" s="89">
         <f t="shared" si="5"/>
-        <v>195940.59</v>
-      </c>
-      <c r="N71" s="167">
+        <v>204030.59</v>
+      </c>
+      <c r="N71" s="163">
         <f t="shared" si="8"/>
-        <v>201818.59</v>
+        <v>210151.59</v>
       </c>
       <c r="O71" s="53">
         <f t="shared" si="7"/>
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="156">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" s="152">
         <f t="shared" si="9"/>
         <v>60</v>
       </c>
-      <c r="B72" s="128" t="s">
+      <c r="B72" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C72" s="127"/>
-      <c r="D72" s="123">
+      <c r="C72" s="124"/>
+      <c r="D72" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E72" s="86">
@@ -6860,38 +6886,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I72" s="149">
+      <c r="I72" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J72" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J72" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K72" s="89"/>
-      <c r="L72" s="227"/>
-      <c r="M72" s="90">
+      <c r="K72" s="145"/>
+      <c r="L72" s="175"/>
+      <c r="M72" s="89">
         <f t="shared" si="5"/>
-        <v>163918.6</v>
-      </c>
-      <c r="N72" s="165">
+        <v>170680.6</v>
+      </c>
+      <c r="N72" s="161">
         <f t="shared" si="8"/>
-        <v>168836.6</v>
+        <v>175800.6</v>
       </c>
       <c r="O72" s="53">
         <f t="shared" si="7"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="154">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="150">
         <f t="shared" si="9"/>
         <v>61</v>
       </c>
-      <c r="B73" s="92" t="s">
+      <c r="B73" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="C73" s="91"/>
+      <c r="C73" s="90"/>
       <c r="D73" s="85">
         <v>1.17</v>
       </c>
@@ -6910,38 +6936,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I73" s="149">
+      <c r="I73" s="145">
         <f t="shared" si="10"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J73" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J73" s="145">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
-      <c r="K73" s="89"/>
-      <c r="L73" s="227"/>
-      <c r="M73" s="90">
+      <c r="K73" s="145"/>
+      <c r="L73" s="175"/>
+      <c r="M73" s="89">
         <f t="shared" si="5"/>
-        <v>176373.61</v>
-      </c>
-      <c r="N73" s="165">
+        <v>183437.61</v>
+      </c>
+      <c r="N73" s="161">
         <f t="shared" si="8"/>
-        <v>181664.61</v>
+        <v>188940.61</v>
       </c>
       <c r="O73" s="53">
         <f t="shared" si="7"/>
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="154">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="150">
         <f t="shared" si="9"/>
         <v>62</v>
       </c>
-      <c r="B74" s="92" t="s">
+      <c r="B74" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="C74" s="91"/>
+      <c r="C74" s="90"/>
       <c r="D74" s="85">
         <v>1.35</v>
       </c>
@@ -6959,38 +6985,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I74" s="149">
+      <c r="I74" s="145">
         <f t="shared" si="10"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J74" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J74" s="145">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K74" s="89"/>
-      <c r="L74" s="227"/>
-      <c r="M74" s="90">
+      <c r="K74" s="145"/>
+      <c r="L74" s="175"/>
+      <c r="M74" s="89">
         <f t="shared" si="5"/>
-        <v>197579.62</v>
-      </c>
-      <c r="N74" s="165">
+        <v>205730.62</v>
+      </c>
+      <c r="N74" s="161">
         <f t="shared" si="8"/>
-        <v>203506.62</v>
+        <v>211902.62</v>
       </c>
       <c r="O74" s="53">
         <f t="shared" si="7"/>
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="154">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" s="150">
         <f t="shared" si="9"/>
         <v>63</v>
       </c>
-      <c r="B75" s="92" t="s">
+      <c r="B75" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C75" s="91"/>
+      <c r="C75" s="90"/>
       <c r="D75" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -7009,38 +7035,38 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I75" s="149">
+      <c r="I75" s="145">
         <f t="shared" si="10"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J75" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J75" s="145">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K75" s="89"/>
-      <c r="L75" s="227"/>
-      <c r="M75" s="90">
+      <c r="K75" s="145"/>
+      <c r="L75" s="175"/>
+      <c r="M75" s="89">
         <f t="shared" si="5"/>
-        <v>168836.63</v>
-      </c>
-      <c r="N75" s="165">
+        <v>175598.63</v>
+      </c>
+      <c r="N75" s="161">
         <f t="shared" si="8"/>
-        <v>173901.63</v>
+        <v>180866.63</v>
       </c>
       <c r="O75" s="53">
         <f t="shared" si="7"/>
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="154">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="150">
         <f t="shared" si="9"/>
         <v>64</v>
       </c>
-      <c r="B76" s="92" t="s">
+      <c r="B76" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="C76" s="91"/>
+      <c r="C76" s="90"/>
       <c r="D76" s="85">
         <v>0.82</v>
       </c>
@@ -7059,74 +7085,74 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I76" s="149">
+      <c r="I76" s="145">
         <f t="shared" si="10"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J76" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J76" s="145">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
-      <c r="K76" s="89">
+      <c r="K76" s="145">
         <v>50000</v>
       </c>
-      <c r="L76" s="227"/>
-      <c r="M76" s="90">
+      <c r="L76" s="175"/>
+      <c r="M76" s="89">
         <f t="shared" si="5"/>
-        <v>173612.64</v>
-      </c>
-      <c r="N76" s="165">
+        <v>178563.64</v>
+      </c>
+      <c r="N76" s="161">
         <f t="shared" si="8"/>
-        <v>178820.64</v>
+        <v>183920.64000000001</v>
       </c>
       <c r="O76" s="53">
         <f t="shared" si="7"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="156">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" s="152">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="B77" s="128" t="s">
+      <c r="B77" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="C77" s="127"/>
-      <c r="D77" s="123">
+      <c r="C77" s="124"/>
+      <c r="D77" s="121">
         <v>0.82</v>
       </c>
       <c r="E77" s="87">
         <v>928411.65</v>
       </c>
-      <c r="F77" s="234">
+      <c r="F77" s="180">
         <v>99012.65</v>
       </c>
-      <c r="G77" s="124">
+      <c r="G77" s="122">
         <f t="shared" ref="G77:G115" si="14">E77-F77</f>
         <v>829399</v>
       </c>
-      <c r="H77" s="124">
+      <c r="H77" s="122">
         <f t="shared" si="4"/>
         <v>24881.969999999998</v>
       </c>
-      <c r="I77" s="151">
+      <c r="I77" s="147">
         <f t="shared" ref="I77:I108" si="15">J$2*D77/100</f>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J77" s="151">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J77" s="147">
         <f t="shared" ref="J77:J108" si="16">E$2*D77/100</f>
         <v>24600</v>
       </c>
-      <c r="K77" s="125"/>
-      <c r="L77" s="229"/>
-      <c r="M77" s="90">
+      <c r="K77" s="147"/>
+      <c r="L77" s="177"/>
+      <c r="M77" s="89">
         <f t="shared" si="5"/>
-        <v>977893.65</v>
-      </c>
-      <c r="N77" s="167">
+        <v>982843.65</v>
+      </c>
+      <c r="N77" s="163">
         <f t="shared" si="8"/>
-        <v>1007230.65</v>
+        <v>1012328.65</v>
       </c>
       <c r="O77" s="53">
         <f t="shared" si="7"/>
@@ -7136,15 +7162,15 @@
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="154">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" s="150">
         <f t="shared" si="9"/>
         <v>66</v>
       </c>
-      <c r="B78" s="92" t="s">
+      <c r="B78" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="C78" s="91"/>
+      <c r="C78" s="90"/>
       <c r="D78" s="85">
         <v>1.34</v>
       </c>
@@ -7162,38 +7188,38 @@
         <f t="shared" ref="H78:H115" si="17">IF(G78&gt;0,G78*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I78" s="149">
+      <c r="I78" s="145">
         <f t="shared" si="15"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J78" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J78" s="145">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K78" s="89"/>
-      <c r="L78" s="227"/>
-      <c r="M78" s="90">
+      <c r="K78" s="145"/>
+      <c r="L78" s="175"/>
+      <c r="M78" s="89">
         <f t="shared" si="5"/>
-        <v>196304.66</v>
-      </c>
-      <c r="N78" s="165">
+        <v>204394.66</v>
+      </c>
+      <c r="N78" s="161">
         <f t="shared" si="8"/>
-        <v>202193.66</v>
+        <v>210526.66</v>
       </c>
       <c r="O78" s="53">
         <f t="shared" si="7"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="154">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" s="150">
         <f t="shared" si="9"/>
         <v>67</v>
       </c>
-      <c r="B79" s="92" t="s">
+      <c r="B79" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="C79" s="91"/>
+      <c r="C79" s="90"/>
       <c r="D79" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -7211,38 +7237,38 @@
         <f t="shared" si="17"/>
         <v>5189.7899999999991</v>
       </c>
-      <c r="I79" s="149">
+      <c r="I79" s="145">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J79" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J79" s="145">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K79" s="89"/>
-      <c r="L79" s="227"/>
-      <c r="M79" s="90">
+      <c r="K79" s="145"/>
+      <c r="L79" s="175"/>
+      <c r="M79" s="89">
         <f t="shared" ref="M79:M115" si="18">ROUND(SUM(G79:L79),0) + O79</f>
-        <v>347019.67</v>
-      </c>
-      <c r="N79" s="165">
+        <v>353780.67</v>
+      </c>
+      <c r="N79" s="161">
         <f t="shared" si="8"/>
-        <v>357430.67</v>
+        <v>364393.67</v>
       </c>
       <c r="O79" s="53">
         <f t="shared" si="7"/>
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="154">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="150">
         <f t="shared" si="9"/>
         <v>68</v>
       </c>
-      <c r="B80" s="92" t="s">
+      <c r="B80" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C80" s="91"/>
+      <c r="C80" s="90"/>
       <c r="D80" s="85">
         <v>1.17</v>
       </c>
@@ -7260,38 +7286,38 @@
         <f t="shared" si="17"/>
         <v>171257.6004</v>
       </c>
-      <c r="I80" s="149">
+      <c r="I80" s="145">
         <f t="shared" si="15"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J80" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J80" s="145">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
-      <c r="K80" s="89"/>
-      <c r="L80" s="227"/>
-      <c r="M80" s="90">
+      <c r="K80" s="145"/>
+      <c r="L80" s="175"/>
+      <c r="M80" s="89">
         <f t="shared" si="18"/>
-        <v>6056217.6799999997</v>
-      </c>
-      <c r="N80" s="165">
+        <v>6063281.6799999997</v>
+      </c>
+      <c r="N80" s="161">
         <f t="shared" si="8"/>
-        <v>6237904.6799999997</v>
+        <v>6245179.6799999997</v>
       </c>
       <c r="O80" s="53">
         <f t="shared" si="7"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="154">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" s="150">
         <f t="shared" si="9"/>
         <v>69</v>
       </c>
-      <c r="B81" s="92" t="s">
+      <c r="B81" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="C81" s="91"/>
+      <c r="C81" s="90"/>
       <c r="D81" s="85">
         <v>1.35</v>
       </c>
@@ -7310,39 +7336,39 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I81" s="149">
+      <c r="I81" s="145">
         <f t="shared" si="15"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J81" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J81" s="145">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K81" s="89"/>
-      <c r="L81" s="227"/>
-      <c r="M81" s="90">
+      <c r="K81" s="145"/>
+      <c r="L81" s="175"/>
+      <c r="M81" s="89">
         <f t="shared" si="18"/>
-        <v>203507.69</v>
-      </c>
-      <c r="N81" s="165">
+        <v>211658.69</v>
+      </c>
+      <c r="N81" s="161">
         <f t="shared" si="8"/>
-        <v>209612.69</v>
+        <v>218008.69</v>
       </c>
       <c r="O81" s="53">
         <f t="shared" si="7"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="156">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" s="152">
         <f t="shared" si="9"/>
         <v>70</v>
       </c>
-      <c r="B82" s="128" t="s">
+      <c r="B82" s="125" t="s">
         <v>70</v>
       </c>
-      <c r="C82" s="127"/>
-      <c r="D82" s="123">
+      <c r="C82" s="124"/>
+      <c r="D82" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E82" s="87">
@@ -7352,31 +7378,31 @@
         <f>142087.7+173836.7</f>
         <v>315924.40000000002</v>
       </c>
-      <c r="G82" s="124">
+      <c r="G82" s="122">
         <f t="shared" si="14"/>
         <v>0.29999999998835847</v>
       </c>
-      <c r="H82" s="124">
+      <c r="H82" s="122">
         <f t="shared" si="17"/>
         <v>8.9999999996507544E-3</v>
       </c>
-      <c r="I82" s="151">
+      <c r="I82" s="147">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J82" s="151">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J82" s="147">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K82" s="125"/>
-      <c r="L82" s="229"/>
-      <c r="M82" s="90">
+      <c r="K82" s="147"/>
+      <c r="L82" s="177"/>
+      <c r="M82" s="89">
         <f t="shared" si="18"/>
-        <v>168836.7</v>
-      </c>
-      <c r="N82" s="167">
+        <v>175598.7</v>
+      </c>
+      <c r="N82" s="163">
         <f t="shared" si="8"/>
-        <v>173901.7</v>
+        <v>180866.7</v>
       </c>
       <c r="O82" s="53">
         <f t="shared" si="7"/>
@@ -7386,15 +7412,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="156">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83" s="152">
         <f t="shared" si="9"/>
         <v>71</v>
       </c>
-      <c r="B83" s="128" t="s">
+      <c r="B83" s="125" t="s">
         <v>71</v>
       </c>
-      <c r="C83" s="91"/>
+      <c r="C83" s="90"/>
       <c r="D83" s="85">
         <v>0.82</v>
       </c>
@@ -7413,38 +7439,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I83" s="149">
+      <c r="I83" s="145">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J83" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J83" s="145">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K83" s="89"/>
-      <c r="L83" s="227"/>
-      <c r="M83" s="90">
+      <c r="K83" s="145"/>
+      <c r="L83" s="175"/>
+      <c r="M83" s="89">
         <f t="shared" si="18"/>
-        <v>123612.71</v>
-      </c>
-      <c r="N83" s="165">
+        <v>128563.71</v>
+      </c>
+      <c r="N83" s="161">
         <f t="shared" si="8"/>
-        <v>127320.71</v>
+        <v>132420.71000000002</v>
       </c>
       <c r="O83" s="53">
         <f t="shared" si="7"/>
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A84" s="154">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84" s="150">
         <f t="shared" si="9"/>
         <v>72</v>
       </c>
-      <c r="B84" s="92" t="s">
+      <c r="B84" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="C84" s="91"/>
+      <c r="C84" s="90"/>
       <c r="D84" s="85">
         <v>0.82</v>
       </c>
@@ -7463,38 +7489,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I84" s="149">
+      <c r="I84" s="145">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J84" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J84" s="145">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K84" s="89"/>
-      <c r="L84" s="227"/>
-      <c r="M84" s="90">
+      <c r="K84" s="145"/>
+      <c r="L84" s="175"/>
+      <c r="M84" s="89">
         <f t="shared" si="18"/>
-        <v>123612.72</v>
-      </c>
-      <c r="N84" s="165">
+        <v>128563.72</v>
+      </c>
+      <c r="N84" s="161">
         <f t="shared" si="8"/>
-        <v>127320.72</v>
+        <v>132420.72</v>
       </c>
       <c r="O84" s="53">
         <f t="shared" si="7"/>
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="154">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85" s="150">
         <f t="shared" si="9"/>
         <v>73</v>
       </c>
-      <c r="B85" s="92" t="s">
+      <c r="B85" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="C85" s="91"/>
+      <c r="C85" s="90"/>
       <c r="D85" s="85">
         <v>1.34</v>
       </c>
@@ -7512,38 +7538,38 @@
         <f t="shared" si="17"/>
         <v>5999.9999999999991</v>
       </c>
-      <c r="I85" s="149">
+      <c r="I85" s="145">
         <f t="shared" si="15"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J85" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J85" s="145">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K85" s="89"/>
-      <c r="L85" s="227"/>
-      <c r="M85" s="90">
+      <c r="K85" s="145"/>
+      <c r="L85" s="175"/>
+      <c r="M85" s="89">
         <f t="shared" si="18"/>
-        <v>408000.73</v>
-      </c>
-      <c r="N85" s="165">
+        <v>416090.73</v>
+      </c>
+      <c r="N85" s="161">
         <f t="shared" si="8"/>
-        <v>420240.73</v>
+        <v>428573.73</v>
       </c>
       <c r="O85" s="53">
         <f t="shared" si="7"/>
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="154">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" s="150">
         <f t="shared" si="9"/>
         <v>74</v>
       </c>
-      <c r="B86" s="92" t="s">
+      <c r="B86" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="C86" s="91"/>
+      <c r="C86" s="90"/>
       <c r="D86" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -7559,38 +7585,38 @@
         <f t="shared" si="17"/>
         <v>9805.5522000000001</v>
       </c>
-      <c r="I86" s="149">
+      <c r="I86" s="145">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J86" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J86" s="145">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K86" s="89"/>
-      <c r="L86" s="227"/>
-      <c r="M86" s="90">
+      <c r="K86" s="145"/>
+      <c r="L86" s="175"/>
+      <c r="M86" s="89">
         <f t="shared" si="18"/>
-        <v>505493.74</v>
-      </c>
-      <c r="N86" s="165">
+        <v>512255.74</v>
+      </c>
+      <c r="N86" s="161">
         <f t="shared" si="8"/>
-        <v>520658.74</v>
+        <v>527623.74</v>
       </c>
       <c r="O86" s="53">
         <f t="shared" si="7"/>
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A87" s="154">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87" s="150">
         <f t="shared" si="9"/>
         <v>75</v>
       </c>
-      <c r="B87" s="92" t="s">
+      <c r="B87" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="C87" s="91"/>
+      <c r="C87" s="90"/>
       <c r="D87" s="85">
         <v>1.17</v>
       </c>
@@ -7609,38 +7635,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I87" s="149">
+      <c r="I87" s="145">
         <f t="shared" si="15"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J87" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J87" s="145">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
-      <c r="K87" s="89"/>
-      <c r="L87" s="227"/>
-      <c r="M87" s="90">
+      <c r="K87" s="145"/>
+      <c r="L87" s="175"/>
+      <c r="M87" s="89">
         <f t="shared" si="18"/>
-        <v>176373.75</v>
-      </c>
-      <c r="N87" s="165">
+        <v>183437.75</v>
+      </c>
+      <c r="N87" s="161">
         <f t="shared" si="8"/>
-        <v>181664.75</v>
+        <v>188940.75</v>
       </c>
       <c r="O87" s="53">
         <f t="shared" si="7"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="154">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88" s="150">
         <f t="shared" si="9"/>
         <v>76</v>
       </c>
-      <c r="B88" s="92" t="s">
+      <c r="B88" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="C88" s="91"/>
+      <c r="C88" s="90"/>
       <c r="D88" s="85">
         <v>1.35</v>
       </c>
@@ -7659,38 +7685,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I88" s="149">
+      <c r="I88" s="145">
         <f t="shared" si="15"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J88" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J88" s="145">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K88" s="89"/>
-      <c r="L88" s="227"/>
-      <c r="M88" s="90">
+      <c r="K88" s="145"/>
+      <c r="L88" s="175"/>
+      <c r="M88" s="89">
         <f t="shared" si="18"/>
-        <v>203507.76</v>
-      </c>
-      <c r="N88" s="165">
+        <v>211658.76</v>
+      </c>
+      <c r="N88" s="161">
         <f t="shared" si="8"/>
-        <v>209612.76</v>
+        <v>218008.76</v>
       </c>
       <c r="O88" s="53">
         <f t="shared" si="7"/>
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A89" s="154">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" s="150">
         <f t="shared" si="9"/>
         <v>77</v>
       </c>
-      <c r="B89" s="92" t="s">
+      <c r="B89" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="C89" s="91"/>
+      <c r="C89" s="90"/>
       <c r="D89" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -7708,69 +7734,69 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I89" s="149">
+      <c r="I89" s="145">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J89" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J89" s="145">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K89" s="89"/>
-      <c r="L89" s="227"/>
-      <c r="M89" s="90">
+      <c r="K89" s="145"/>
+      <c r="L89" s="175"/>
+      <c r="M89" s="89">
         <f t="shared" si="18"/>
-        <v>164075.76999999999</v>
-      </c>
-      <c r="N89" s="165">
+        <v>170837.77</v>
+      </c>
+      <c r="N89" s="161">
         <f t="shared" si="8"/>
-        <v>168997.77</v>
+        <v>175962.77</v>
       </c>
       <c r="O89" s="53">
         <f t="shared" si="7"/>
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A90" s="157">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90" s="153">
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="B90" s="134" t="s">
+      <c r="B90" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="C90" s="135"/>
-      <c r="D90" s="136">
+      <c r="C90" s="132"/>
+      <c r="D90" s="133">
         <v>0.82</v>
       </c>
-      <c r="E90" s="137">
+      <c r="E90" s="134">
         <v>250932.78</v>
       </c>
-      <c r="F90" s="137"/>
-      <c r="G90" s="138">
+      <c r="F90" s="134"/>
+      <c r="G90" s="135">
         <f t="shared" si="14"/>
         <v>250932.78</v>
       </c>
-      <c r="H90" s="138"/>
-      <c r="I90" s="153">
+      <c r="H90" s="135"/>
+      <c r="I90" s="149">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J90" s="153">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J90" s="149">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K90" s="139"/>
-      <c r="L90" s="230">
+      <c r="K90" s="149"/>
+      <c r="L90" s="178">
         <v>250000</v>
       </c>
-      <c r="M90" s="140">
+      <c r="M90" s="136">
         <f t="shared" si="18"/>
-        <v>624545.78</v>
-      </c>
-      <c r="N90" s="168">
+        <v>629495.78</v>
+      </c>
+      <c r="N90" s="164">
         <f t="shared" si="8"/>
-        <v>643281.78</v>
+        <v>648380.78</v>
       </c>
       <c r="O90" s="53">
         <f t="shared" si="7"/>
@@ -7780,15 +7806,15 @@
         <v>238</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A91" s="154">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" s="150">
         <f t="shared" si="9"/>
         <v>79</v>
       </c>
-      <c r="B91" s="92" t="s">
+      <c r="B91" s="91" t="s">
         <v>79</v>
       </c>
-      <c r="C91" s="91"/>
+      <c r="C91" s="90"/>
       <c r="D91" s="85">
         <v>0.82</v>
       </c>
@@ -7807,38 +7833,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I91" s="149">
+      <c r="I91" s="145">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J91" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J91" s="145">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K91" s="89"/>
-      <c r="L91" s="227"/>
-      <c r="M91" s="90">
+      <c r="K91" s="145"/>
+      <c r="L91" s="175"/>
+      <c r="M91" s="89">
         <f t="shared" si="18"/>
-        <v>123612.79</v>
-      </c>
-      <c r="N91" s="165">
+        <v>128563.79</v>
+      </c>
+      <c r="N91" s="161">
         <f t="shared" si="8"/>
-        <v>127320.79</v>
+        <v>132420.78999999998</v>
       </c>
       <c r="O91" s="53">
         <f t="shared" si="7"/>
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A92" s="154">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92" s="150">
         <f t="shared" si="9"/>
         <v>80</v>
       </c>
-      <c r="B92" s="92" t="s">
+      <c r="B92" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="C92" s="91"/>
+      <c r="C92" s="90"/>
       <c r="D92" s="85">
         <v>1.34</v>
       </c>
@@ -7854,70 +7880,70 @@
         <f t="shared" si="17"/>
         <v>11920.554</v>
       </c>
-      <c r="I92" s="149">
+      <c r="I92" s="145">
         <f t="shared" si="15"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J92" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J92" s="145">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K92" s="89"/>
-      <c r="L92" s="227"/>
-      <c r="M92" s="90">
+      <c r="K92" s="145"/>
+      <c r="L92" s="175"/>
+      <c r="M92" s="89">
         <f t="shared" si="18"/>
-        <v>611272.80000000005</v>
-      </c>
-      <c r="N92" s="165">
+        <v>619362.80000000005</v>
+      </c>
+      <c r="N92" s="161">
         <f t="shared" si="8"/>
-        <v>629610.80000000005</v>
+        <v>637943.80000000005</v>
       </c>
       <c r="O92" s="53">
         <f t="shared" si="7"/>
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="155">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" s="151">
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
-      <c r="B93" s="102" t="s">
+      <c r="B93" s="100" t="s">
         <v>81</v>
       </c>
-      <c r="C93" s="103"/>
-      <c r="D93" s="98">
+      <c r="C93" s="101"/>
+      <c r="D93" s="96">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E93" s="99">
+      <c r="E93" s="97">
         <v>569223.81000000006</v>
       </c>
-      <c r="F93" s="99"/>
-      <c r="G93" s="100">
+      <c r="F93" s="97"/>
+      <c r="G93" s="98">
         <f t="shared" si="14"/>
         <v>569223.81000000006</v>
       </c>
-      <c r="H93" s="100">
+      <c r="H93" s="98">
         <f t="shared" si="17"/>
         <v>17076.7143</v>
       </c>
-      <c r="I93" s="150">
+      <c r="I93" s="146">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J93" s="150">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J93" s="146">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K93" s="97"/>
-      <c r="L93" s="228"/>
-      <c r="M93" s="101">
+      <c r="K93" s="146"/>
+      <c r="L93" s="176"/>
+      <c r="M93" s="99">
         <f t="shared" si="18"/>
-        <v>755136.81</v>
-      </c>
-      <c r="N93" s="166">
+        <v>761898.81</v>
+      </c>
+      <c r="N93" s="162">
         <f t="shared" si="8"/>
-        <v>777790.81</v>
+        <v>784755.81</v>
       </c>
       <c r="O93" s="53">
         <f t="shared" si="7"/>
@@ -7927,15 +7953,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A94" s="154">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" s="150">
         <f t="shared" si="9"/>
         <v>82</v>
       </c>
-      <c r="B94" s="92" t="s">
+      <c r="B94" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="91"/>
+      <c r="C94" s="90"/>
       <c r="D94" s="85">
         <v>1.17</v>
       </c>
@@ -7954,39 +7980,39 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I94" s="149">
+      <c r="I94" s="145">
         <f t="shared" si="15"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J94" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J94" s="145">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
-      <c r="K94" s="89"/>
-      <c r="L94" s="227"/>
-      <c r="M94" s="90">
+      <c r="K94" s="145"/>
+      <c r="L94" s="175"/>
+      <c r="M94" s="89">
         <f t="shared" si="18"/>
-        <v>176373.82</v>
-      </c>
-      <c r="N94" s="165">
+        <v>183437.82</v>
+      </c>
+      <c r="N94" s="161">
         <f t="shared" si="8"/>
-        <v>181664.82</v>
+        <v>188940.82</v>
       </c>
       <c r="O94" s="53">
         <f t="shared" si="7"/>
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A95" s="156">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95" s="152">
         <f t="shared" si="9"/>
         <v>83</v>
       </c>
-      <c r="B95" s="128" t="s">
+      <c r="B95" s="125" t="s">
         <v>83</v>
       </c>
-      <c r="C95" s="127"/>
-      <c r="D95" s="123">
+      <c r="C95" s="124"/>
+      <c r="D95" s="121">
         <v>1.35</v>
       </c>
       <c r="E95" s="87">
@@ -8001,39 +8027,39 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I95" s="149">
+      <c r="I95" s="145">
         <f t="shared" si="15"/>
-        <v>163007.43750000003</v>
-      </c>
-      <c r="J95" s="149">
+        <v>171157.80937500001</v>
+      </c>
+      <c r="J95" s="145">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K95" s="89"/>
-      <c r="L95" s="227"/>
-      <c r="M95" s="90">
+      <c r="K95" s="145"/>
+      <c r="L95" s="175"/>
+      <c r="M95" s="89">
         <f t="shared" si="18"/>
-        <v>129030.83</v>
-      </c>
-      <c r="N95" s="165">
+        <v>137181.82999999999</v>
+      </c>
+      <c r="N95" s="161">
         <f t="shared" si="8"/>
-        <v>132901.83000000002</v>
+        <v>141296.82999999999</v>
       </c>
       <c r="O95" s="53">
         <f t="shared" si="7"/>
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A96" s="156">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" s="152">
         <f t="shared" si="9"/>
         <v>84</v>
       </c>
-      <c r="B96" s="128" t="s">
+      <c r="B96" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="C96" s="127"/>
-      <c r="D96" s="123">
+      <c r="C96" s="124"/>
+      <c r="D96" s="121">
         <v>1.1200000000000001</v>
       </c>
       <c r="E96" s="87">
@@ -8051,38 +8077,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I96" s="149">
+      <c r="I96" s="145">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J96" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J96" s="145">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K96" s="89"/>
-      <c r="L96" s="227"/>
-      <c r="M96" s="90">
+      <c r="K96" s="145"/>
+      <c r="L96" s="175"/>
+      <c r="M96" s="89">
         <f t="shared" si="18"/>
-        <v>168836.84</v>
-      </c>
-      <c r="N96" s="165">
+        <v>175598.84</v>
+      </c>
+      <c r="N96" s="161">
         <f t="shared" si="8"/>
-        <v>173901.84</v>
+        <v>180866.84</v>
       </c>
       <c r="O96" s="53">
         <f t="shared" ref="O96:O115" si="19">O95+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A97" s="154">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97" s="150">
         <f t="shared" si="9"/>
         <v>85</v>
       </c>
-      <c r="B97" s="92" t="s">
+      <c r="B97" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="C97" s="91"/>
+      <c r="C97" s="90"/>
       <c r="D97" s="85">
         <v>0.82</v>
       </c>
@@ -8101,38 +8127,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I97" s="149">
+      <c r="I97" s="145">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J97" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J97" s="145">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K97" s="89"/>
-      <c r="L97" s="227"/>
-      <c r="M97" s="90">
+      <c r="K97" s="145"/>
+      <c r="L97" s="175"/>
+      <c r="M97" s="89">
         <f t="shared" si="18"/>
-        <v>123612.85</v>
-      </c>
-      <c r="N97" s="165">
+        <v>128563.85</v>
+      </c>
+      <c r="N97" s="161">
         <f t="shared" si="8"/>
-        <v>127320.85</v>
+        <v>132420.85</v>
       </c>
       <c r="O97" s="53">
         <f t="shared" si="19"/>
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A98" s="154">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98" s="150">
         <f t="shared" si="9"/>
         <v>86</v>
       </c>
-      <c r="B98" s="92" t="s">
+      <c r="B98" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="C98" s="91"/>
+      <c r="C98" s="90"/>
       <c r="D98" s="85">
         <v>0.82</v>
       </c>
@@ -8150,38 +8176,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I98" s="149">
+      <c r="I98" s="145">
         <f t="shared" si="15"/>
-        <v>99011.925000000003</v>
-      </c>
-      <c r="J98" s="149">
+        <v>103962.52125000001</v>
+      </c>
+      <c r="J98" s="145">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K98" s="89"/>
-      <c r="L98" s="227"/>
-      <c r="M98" s="90">
+      <c r="K98" s="145"/>
+      <c r="L98" s="175"/>
+      <c r="M98" s="89">
         <f t="shared" si="18"/>
-        <v>119837.86</v>
-      </c>
-      <c r="N98" s="165">
+        <v>124788.86</v>
+      </c>
+      <c r="N98" s="161">
         <f t="shared" ref="N98:N115" si="20">ROUND(M98*3%,0) + M98</f>
-        <v>123432.86</v>
+        <v>128532.86</v>
       </c>
       <c r="O98" s="53">
         <f t="shared" si="19"/>
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A99" s="154">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99" s="150">
         <f t="shared" ref="A99:A115" si="21">A98+1</f>
         <v>87</v>
       </c>
-      <c r="B99" s="92" t="s">
+      <c r="B99" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="C99" s="91"/>
+      <c r="C99" s="90"/>
       <c r="D99" s="85">
         <v>1.34</v>
       </c>
@@ -8200,38 +8226,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I99" s="149">
+      <c r="I99" s="145">
         <f t="shared" si="15"/>
-        <v>161799.97500000001</v>
-      </c>
-      <c r="J99" s="149">
+        <v>169889.97375</v>
+      </c>
+      <c r="J99" s="145">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K99" s="89"/>
-      <c r="L99" s="227"/>
-      <c r="M99" s="90">
+      <c r="K99" s="145"/>
+      <c r="L99" s="175"/>
+      <c r="M99" s="89">
         <f t="shared" si="18"/>
-        <v>202000.87</v>
-      </c>
-      <c r="N99" s="165">
+        <v>210090.87</v>
+      </c>
+      <c r="N99" s="161">
         <f t="shared" si="20"/>
-        <v>208060.87</v>
+        <v>216393.87</v>
       </c>
       <c r="O99" s="53">
         <f t="shared" si="19"/>
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="154">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100" s="150">
         <f t="shared" si="21"/>
         <v>88</v>
       </c>
-      <c r="B100" s="92" t="s">
+      <c r="B100" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="C100" s="91"/>
+      <c r="C100" s="90"/>
       <c r="D100" s="85">
         <v>1.1200000000000001</v>
       </c>
@@ -8250,38 +8276,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I100" s="149">
+      <c r="I100" s="145">
         <f t="shared" si="15"/>
-        <v>135235.80000000002</v>
-      </c>
-      <c r="J100" s="149">
+        <v>141997.59000000003</v>
+      </c>
+      <c r="J100" s="145">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K100" s="89"/>
-      <c r="L100" s="227"/>
-      <c r="M100" s="90">
+      <c r="K100" s="145"/>
+      <c r="L100" s="175"/>
+      <c r="M100" s="89">
         <f t="shared" si="18"/>
-        <v>168836.88</v>
-      </c>
-      <c r="N100" s="165">
+        <v>175598.88</v>
+      </c>
+      <c r="N100" s="161">
         <f t="shared" si="20"/>
-        <v>173901.88</v>
+        <v>180866.88</v>
       </c>
       <c r="O100" s="53">
         <f t="shared" si="19"/>
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A101" s="154">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101" s="150">
         <f t="shared" si="21"/>
         <v>89</v>
       </c>
-      <c r="B101" s="92" t="s">
+      <c r="B101" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="C101" s="91"/>
+      <c r="C101" s="90"/>
       <c r="D101" s="85">
         <v>1.17</v>
       </c>
@@ -8289,7 +8315,7 @@
         <v>176373.89</v>
       </c>
       <c r="F101" s="87">
-        <f t="shared" ref="F101:F112" si="22">E101</f>
+        <f t="shared" ref="F101:F109" si="22">E101</f>
         <v>176373.89</v>
       </c>
       <c r="G101" s="88">
@@ -8300,38 +8326,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I101" s="149">
+      <c r="I101" s="145">
         <f t="shared" si="15"/>
-        <v>141273.11249999999</v>
-      </c>
-      <c r="J101" s="149">
+        <v>148336.768125</v>
+      </c>
+      <c r="J101" s="145">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
-      <c r="K101" s="89"/>
-      <c r="L101" s="227"/>
-      <c r="M101" s="90">
+      <c r="K101" s="145"/>
+      <c r="L101" s="175"/>
+      <c r="M101" s="89">
         <f t="shared" si="18"/>
-        <v>176373.89</v>
-      </c>
-      <c r="N101" s="165">
+        <v>183437.89</v>
+      </c>
+      <c r="N101" s="161">
         <f t="shared" si="20"/>
-        <v>181664.89</v>
+        <v>188940.89</v>
       </c>
       <c r="O101" s="53">
         <f t="shared" si="19"/>
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A102" s="154">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102" s="150">
         <f t="shared" si="21"/>
         <v>90</v>
       </c>
-      <c r="B102" s="92" t="s">
+      <c r="B102" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="C102" s="91"/>
+      <c r="C102" s="90"/>
       <c r="D102" s="85">
         <v>0.1</v>
       </c>
@@ -8350,38 +8376,38 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I102" s="149">
+      <c r="I102" s="145">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J102" s="149">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J102" s="145">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K102" s="89"/>
-      <c r="L102" s="227"/>
-      <c r="M102" s="90">
+      <c r="K102" s="145"/>
+      <c r="L102" s="175"/>
+      <c r="M102" s="89">
         <f t="shared" si="18"/>
-        <v>15075.9</v>
-      </c>
-      <c r="N102" s="165">
+        <v>15678.9</v>
+      </c>
+      <c r="N102" s="161">
         <f t="shared" si="20"/>
-        <v>15527.9</v>
+        <v>16148.9</v>
       </c>
       <c r="O102" s="53">
         <f t="shared" si="19"/>
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A103" s="154">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103" s="150">
         <f t="shared" si="21"/>
         <v>91</v>
       </c>
-      <c r="B103" s="92" t="s">
+      <c r="B103" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="C103" s="91"/>
+      <c r="C103" s="90"/>
       <c r="D103" s="85">
         <v>0.1</v>
       </c>
@@ -8399,38 +8425,38 @@
         <f t="shared" si="17"/>
         <v>480.21</v>
       </c>
-      <c r="I103" s="149">
+      <c r="I103" s="145">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J103" s="149">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J103" s="145">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K103" s="89"/>
-      <c r="L103" s="227"/>
-      <c r="M103" s="90">
+      <c r="K103" s="145"/>
+      <c r="L103" s="175"/>
+      <c r="M103" s="89">
         <f t="shared" si="18"/>
-        <v>31562.91</v>
-      </c>
-      <c r="N103" s="165">
+        <v>32166.91</v>
+      </c>
+      <c r="N103" s="161">
         <f t="shared" si="20"/>
-        <v>32509.91</v>
+        <v>33131.910000000003</v>
       </c>
       <c r="O103" s="53">
         <f t="shared" si="19"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A104" s="154">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104" s="150">
         <f t="shared" si="21"/>
         <v>92</v>
       </c>
-      <c r="B104" s="92" t="s">
+      <c r="B104" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="91"/>
+      <c r="C104" s="90"/>
       <c r="D104" s="85">
         <v>0.1</v>
       </c>
@@ -8449,39 +8475,39 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I104" s="149">
+      <c r="I104" s="145">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J104" s="149">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J104" s="145">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K104" s="89"/>
-      <c r="L104" s="227"/>
-      <c r="M104" s="90">
+      <c r="K104" s="145"/>
+      <c r="L104" s="175"/>
+      <c r="M104" s="89">
         <f t="shared" si="18"/>
-        <v>15075.92</v>
-      </c>
-      <c r="N104" s="165">
+        <v>15678.92</v>
+      </c>
+      <c r="N104" s="161">
         <f t="shared" si="20"/>
-        <v>15527.92</v>
+        <v>16148.92</v>
       </c>
       <c r="O104" s="53">
         <f t="shared" si="19"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A105" s="156">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A105" s="152">
         <f t="shared" si="21"/>
         <v>93</v>
       </c>
-      <c r="B105" s="128" t="s">
+      <c r="B105" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="127"/>
-      <c r="D105" s="123">
+      <c r="C105" s="124"/>
+      <c r="D105" s="121">
         <v>0.1</v>
       </c>
       <c r="E105" s="87">
@@ -8490,47 +8516,47 @@
       <c r="F105" s="87">
         <v>15527.92</v>
       </c>
-      <c r="G105" s="124">
+      <c r="G105" s="122">
         <f t="shared" si="14"/>
         <v>-451.98999999999978</v>
       </c>
-      <c r="H105" s="124">
+      <c r="H105" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I105" s="151">
+      <c r="I105" s="147">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J105" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J105" s="147">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K105" s="125"/>
-      <c r="L105" s="229"/>
-      <c r="M105" s="90">
+      <c r="K105" s="147"/>
+      <c r="L105" s="177"/>
+      <c r="M105" s="89">
         <f t="shared" si="18"/>
-        <v>14623.93</v>
-      </c>
-      <c r="N105" s="167">
+        <v>15226.93</v>
+      </c>
+      <c r="N105" s="163">
         <f t="shared" si="20"/>
-        <v>15062.93</v>
+        <v>15683.93</v>
       </c>
       <c r="O105" s="53">
         <f t="shared" si="19"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A106" s="156">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A106" s="152">
         <f t="shared" si="21"/>
         <v>94</v>
       </c>
-      <c r="B106" s="128" t="s">
+      <c r="B106" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="C106" s="127"/>
-      <c r="D106" s="123">
+      <c r="C106" s="124"/>
+      <c r="D106" s="121">
         <v>0.1</v>
       </c>
       <c r="E106" s="87">
@@ -8540,47 +8566,47 @@
         <f>E106</f>
         <v>15075.94</v>
       </c>
-      <c r="G106" s="124">
+      <c r="G106" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H106" s="124">
+      <c r="H106" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I106" s="151">
+      <c r="I106" s="147">
         <f>J$2*D106/100</f>
-        <v>12074.625</v>
-      </c>
-      <c r="J106" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J106" s="147">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K106" s="125"/>
-      <c r="L106" s="229"/>
-      <c r="M106" s="90">
+      <c r="K106" s="147"/>
+      <c r="L106" s="177"/>
+      <c r="M106" s="89">
         <f t="shared" si="18"/>
-        <v>15075.94</v>
-      </c>
-      <c r="N106" s="167">
+        <v>15678.94</v>
+      </c>
+      <c r="N106" s="163">
         <f t="shared" si="20"/>
-        <v>15527.94</v>
+        <v>16148.94</v>
       </c>
       <c r="O106" s="53">
         <f t="shared" si="19"/>
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="156">
+    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="152">
         <f t="shared" si="21"/>
         <v>95</v>
       </c>
-      <c r="B107" s="128" t="s">
+      <c r="B107" s="125" t="s">
         <v>175</v>
       </c>
-      <c r="C107" s="127"/>
-      <c r="D107" s="123">
+      <c r="C107" s="124"/>
+      <c r="D107" s="121">
         <v>0.1</v>
       </c>
       <c r="E107" s="87">
@@ -8590,47 +8616,47 @@
         <f>E107</f>
         <v>14623.95</v>
       </c>
-      <c r="G107" s="124">
+      <c r="G107" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H107" s="124">
+      <c r="H107" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I107" s="151">
+      <c r="I107" s="147">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J107" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J107" s="147">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K107" s="125"/>
-      <c r="L107" s="229"/>
-      <c r="M107" s="90">
+      <c r="K107" s="147"/>
+      <c r="L107" s="177"/>
+      <c r="M107" s="89">
         <f t="shared" si="18"/>
-        <v>15075.95</v>
-      </c>
-      <c r="N107" s="167">
+        <v>15678.95</v>
+      </c>
+      <c r="N107" s="163">
         <f t="shared" si="20"/>
-        <v>15527.95</v>
+        <v>16148.95</v>
       </c>
       <c r="O107" s="53">
         <f t="shared" si="19"/>
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A108" s="156">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108" s="152">
         <f t="shared" si="21"/>
         <v>96</v>
       </c>
-      <c r="B108" s="128" t="s">
+      <c r="B108" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="C108" s="127"/>
-      <c r="D108" s="123">
+      <c r="C108" s="124"/>
+      <c r="D108" s="121">
         <v>0.1</v>
       </c>
       <c r="E108" s="87">
@@ -8640,31 +8666,31 @@
         <f t="shared" si="22"/>
         <v>15075.96</v>
       </c>
-      <c r="G108" s="124">
+      <c r="G108" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H108" s="124">
+      <c r="H108" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I108" s="151">
+      <c r="I108" s="147">
         <f t="shared" si="15"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J108" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J108" s="147">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="K108" s="125"/>
-      <c r="L108" s="229"/>
-      <c r="M108" s="90">
+      <c r="K108" s="147"/>
+      <c r="L108" s="177"/>
+      <c r="M108" s="89">
         <f t="shared" si="18"/>
-        <v>15075.96</v>
-      </c>
-      <c r="N108" s="167">
+        <v>15678.96</v>
+      </c>
+      <c r="N108" s="163">
         <f t="shared" si="20"/>
-        <v>15527.96</v>
+        <v>16148.96</v>
       </c>
       <c r="O108" s="53">
         <f t="shared" si="19"/>
@@ -8674,16 +8700,16 @@
         <v>161</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A109" s="156">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A109" s="152">
         <f t="shared" si="21"/>
         <v>97</v>
       </c>
-      <c r="B109" s="128" t="s">
+      <c r="B109" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="C109" s="127"/>
-      <c r="D109" s="123">
+      <c r="C109" s="124"/>
+      <c r="D109" s="121">
         <v>0.1</v>
       </c>
       <c r="E109" s="87">
@@ -8693,47 +8719,47 @@
         <f t="shared" si="22"/>
         <v>15075.97</v>
       </c>
-      <c r="G109" s="124">
+      <c r="G109" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H109" s="124">
+      <c r="H109" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I109" s="151">
+      <c r="I109" s="147">
         <f t="shared" ref="I109:I115" si="23">J$2*D109/100</f>
-        <v>12074.625</v>
-      </c>
-      <c r="J109" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J109" s="147">
         <f t="shared" ref="J109:J115" si="24">E$2*D109/100</f>
         <v>3000</v>
       </c>
-      <c r="K109" s="125"/>
-      <c r="L109" s="229"/>
-      <c r="M109" s="90">
+      <c r="K109" s="147"/>
+      <c r="L109" s="177"/>
+      <c r="M109" s="89">
         <f t="shared" si="18"/>
-        <v>15075.97</v>
-      </c>
-      <c r="N109" s="167">
+        <v>15678.97</v>
+      </c>
+      <c r="N109" s="163">
         <f t="shared" si="20"/>
-        <v>15527.97</v>
+        <v>16148.97</v>
       </c>
       <c r="O109" s="53">
         <f t="shared" si="19"/>
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A110" s="156">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A110" s="152">
         <f t="shared" si="21"/>
         <v>98</v>
       </c>
-      <c r="B110" s="128" t="s">
+      <c r="B110" s="125" t="s">
         <v>96</v>
       </c>
-      <c r="C110" s="127"/>
-      <c r="D110" s="123">
+      <c r="C110" s="124"/>
+      <c r="D110" s="121">
         <v>0.1</v>
       </c>
       <c r="E110" s="87">
@@ -8743,47 +8769,47 @@
         <f>E110</f>
         <v>15075.98</v>
       </c>
-      <c r="G110" s="124">
+      <c r="G110" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H110" s="124">
+      <c r="H110" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I110" s="151">
+      <c r="I110" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J110" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J110" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K110" s="125"/>
-      <c r="L110" s="229"/>
-      <c r="M110" s="90">
+      <c r="K110" s="147"/>
+      <c r="L110" s="177"/>
+      <c r="M110" s="89">
         <f t="shared" si="18"/>
-        <v>15075.98</v>
-      </c>
-      <c r="N110" s="167">
+        <v>15678.98</v>
+      </c>
+      <c r="N110" s="163">
         <f t="shared" si="20"/>
-        <v>15527.98</v>
+        <v>16148.98</v>
       </c>
       <c r="O110" s="53">
         <f t="shared" si="19"/>
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A111" s="156">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A111" s="152">
         <f t="shared" si="21"/>
         <v>99</v>
       </c>
-      <c r="B111" s="128" t="s">
+      <c r="B111" s="125" t="s">
         <v>97</v>
       </c>
-      <c r="C111" s="127"/>
-      <c r="D111" s="123">
+      <c r="C111" s="124"/>
+      <c r="D111" s="121">
         <v>0.1</v>
       </c>
       <c r="E111" s="87">
@@ -8792,94 +8818,94 @@
       <c r="F111" s="87">
         <v>15075.99</v>
       </c>
-      <c r="G111" s="124">
+      <c r="G111" s="122">
         <f t="shared" si="14"/>
         <v>-439</v>
       </c>
-      <c r="H111" s="124">
+      <c r="H111" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I111" s="151">
+      <c r="I111" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J111" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J111" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K111" s="125"/>
-      <c r="L111" s="229"/>
-      <c r="M111" s="90">
+      <c r="K111" s="147"/>
+      <c r="L111" s="177"/>
+      <c r="M111" s="89">
         <f t="shared" si="18"/>
-        <v>14636.99</v>
-      </c>
-      <c r="N111" s="167">
+        <v>15239.99</v>
+      </c>
+      <c r="N111" s="163">
         <f t="shared" si="20"/>
-        <v>15075.99</v>
+        <v>15696.99</v>
       </c>
       <c r="O111" s="53">
         <f t="shared" si="19"/>
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A112" s="156">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A112" s="152">
         <f t="shared" si="21"/>
         <v>100</v>
       </c>
-      <c r="B112" s="128" t="s">
+      <c r="B112" s="125" t="s">
         <v>98</v>
       </c>
-      <c r="C112" s="127"/>
-      <c r="D112" s="123">
+      <c r="C112" s="124"/>
+      <c r="D112" s="121">
         <v>0.1</v>
       </c>
       <c r="E112" s="87">
         <v>15076</v>
       </c>
       <c r="F112" s="87"/>
-      <c r="G112" s="124">
+      <c r="G112" s="122">
         <f t="shared" si="14"/>
         <v>15076</v>
       </c>
-      <c r="H112" s="124">
+      <c r="H112" s="122">
         <f t="shared" si="17"/>
         <v>452.28</v>
       </c>
-      <c r="I112" s="151">
+      <c r="I112" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J112" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J112" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K112" s="125"/>
-      <c r="L112" s="229"/>
-      <c r="M112" s="90">
+      <c r="K112" s="147"/>
+      <c r="L112" s="177"/>
+      <c r="M112" s="89">
         <f t="shared" si="18"/>
-        <v>30604</v>
-      </c>
-      <c r="N112" s="167">
+        <v>31208</v>
+      </c>
+      <c r="N112" s="163">
         <f t="shared" si="20"/>
-        <v>31522</v>
+        <v>32144</v>
       </c>
       <c r="O112" s="53">
         <f t="shared" si="19"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A113" s="156">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A113" s="152">
         <f t="shared" si="21"/>
         <v>101</v>
       </c>
-      <c r="B113" s="121" t="s">
+      <c r="B113" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="C113" s="127"/>
-      <c r="D113" s="123">
+      <c r="C113" s="124"/>
+      <c r="D113" s="121">
         <v>0.1</v>
       </c>
       <c r="E113" s="87">
@@ -8888,47 +8914,47 @@
       <c r="F113" s="87">
         <v>15528.01</v>
       </c>
-      <c r="G113" s="124">
+      <c r="G113" s="122">
         <f t="shared" si="14"/>
         <v>-452</v>
       </c>
-      <c r="H113" s="124">
+      <c r="H113" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I113" s="151">
+      <c r="I113" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J113" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J113" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K113" s="125"/>
-      <c r="L113" s="229"/>
-      <c r="M113" s="90">
+      <c r="K113" s="147"/>
+      <c r="L113" s="177"/>
+      <c r="M113" s="89">
         <f t="shared" si="18"/>
-        <v>14624.01</v>
-      </c>
-      <c r="N113" s="167">
+        <v>15227.01</v>
+      </c>
+      <c r="N113" s="163">
         <f t="shared" si="20"/>
-        <v>15063.01</v>
+        <v>15684.01</v>
       </c>
       <c r="O113" s="53">
         <f t="shared" si="19"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A114" s="156">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A114" s="152">
         <f t="shared" si="21"/>
         <v>102</v>
       </c>
-      <c r="B114" s="121" t="s">
+      <c r="B114" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="C114" s="127"/>
-      <c r="D114" s="123">
+      <c r="C114" s="124"/>
+      <c r="D114" s="121">
         <v>0.1</v>
       </c>
       <c r="E114" s="87">
@@ -8937,47 +8963,47 @@
       <c r="F114" s="87">
         <v>15076.02</v>
       </c>
-      <c r="G114" s="124">
+      <c r="G114" s="122">
         <f t="shared" si="14"/>
         <v>452</v>
       </c>
-      <c r="H114" s="124">
+      <c r="H114" s="122">
         <f t="shared" si="17"/>
         <v>13.559999999999999</v>
       </c>
-      <c r="I114" s="151">
+      <c r="I114" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J114" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J114" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K114" s="125"/>
-      <c r="L114" s="229"/>
-      <c r="M114" s="90">
+      <c r="K114" s="147"/>
+      <c r="L114" s="177"/>
+      <c r="M114" s="89">
         <f t="shared" si="18"/>
-        <v>15541.02</v>
-      </c>
-      <c r="N114" s="167">
+        <v>16145.02</v>
+      </c>
+      <c r="N114" s="163">
         <f t="shared" si="20"/>
-        <v>16007.02</v>
+        <v>16629.02</v>
       </c>
       <c r="O114" s="53">
         <f t="shared" si="19"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="156">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A115" s="152">
         <f t="shared" si="21"/>
         <v>103</v>
       </c>
-      <c r="B115" s="128" t="s">
+      <c r="B115" s="125" t="s">
         <v>175</v>
       </c>
-      <c r="C115" s="127"/>
-      <c r="D115" s="123">
+      <c r="C115" s="124"/>
+      <c r="D115" s="121">
         <v>0.1</v>
       </c>
       <c r="E115" s="87">
@@ -8987,195 +9013,190 @@
         <f>E115</f>
         <v>15076.03</v>
       </c>
-      <c r="G115" s="124">
+      <c r="G115" s="122">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H115" s="124">
+      <c r="H115" s="122">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I115" s="151">
+      <c r="I115" s="147">
         <f t="shared" si="23"/>
-        <v>12074.625</v>
-      </c>
-      <c r="J115" s="151">
+        <v>12678.356250000001</v>
+      </c>
+      <c r="J115" s="147">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="K115" s="125"/>
-      <c r="L115" s="229"/>
-      <c r="M115" s="90">
+      <c r="K115" s="147"/>
+      <c r="L115" s="177"/>
+      <c r="M115" s="89">
         <f t="shared" si="18"/>
-        <v>15076.03</v>
-      </c>
-      <c r="N115" s="167">
+        <v>15679.03</v>
+      </c>
+      <c r="N115" s="163">
         <f t="shared" si="20"/>
-        <v>15528.03</v>
+        <v>16149.03</v>
       </c>
       <c r="O115" s="53">
         <f t="shared" si="19"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A116" s="156"/>
-      <c r="B116" s="121"/>
-      <c r="C116" s="127"/>
-      <c r="D116" s="123"/>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A116" s="152"/>
+      <c r="B116" s="119"/>
+      <c r="C116" s="124"/>
+      <c r="D116" s="121"/>
       <c r="E116" s="87"/>
       <c r="F116" s="87"/>
-      <c r="G116" s="124"/>
-      <c r="H116" s="124"/>
-      <c r="I116" s="151"/>
-      <c r="J116" s="151"/>
-      <c r="K116" s="125"/>
-      <c r="L116" s="229"/>
-      <c r="M116" s="126"/>
-      <c r="N116" s="167"/>
+      <c r="G116" s="122"/>
+      <c r="H116" s="122"/>
+      <c r="I116" s="147"/>
+      <c r="J116" s="147"/>
+      <c r="K116" s="147"/>
+      <c r="L116" s="177"/>
+      <c r="M116" s="123"/>
+      <c r="N116" s="163"/>
       <c r="O116" s="53"/>
     </row>
-    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="158"/>
-      <c r="B117" s="159"/>
-      <c r="C117" s="159"/>
-      <c r="D117" s="160">
+    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="154"/>
+      <c r="B117" s="155"/>
+      <c r="C117" s="155"/>
+      <c r="D117" s="156">
         <f t="shared" ref="D117:N117" si="25">SUM(D13:D116)</f>
         <v>100.15999999999993</v>
       </c>
-      <c r="E117" s="161">
+      <c r="E117" s="157">
         <f t="shared" si="25"/>
-        <v>32861708.260000005</v>
-      </c>
-      <c r="F117" s="162">
+        <v>31126352.260000002</v>
+      </c>
+      <c r="F117" s="158">
         <f>SUM(F13:F116)</f>
-        <v>14068443.220000001</v>
-      </c>
-      <c r="G117" s="162">
+        <v>14192055.65</v>
+      </c>
+      <c r="G117" s="158">
         <f t="shared" si="25"/>
-        <v>18793265.039999999</v>
-      </c>
-      <c r="H117" s="162">
+        <v>16934296.609999999</v>
+      </c>
+      <c r="H117" s="158">
         <f t="shared" si="25"/>
-        <v>549869.22</v>
-      </c>
-      <c r="I117" s="163">
+        <v>494100.16710000002</v>
+      </c>
+      <c r="I117" s="159">
         <f t="shared" si="25"/>
-        <v>12093944.400000006</v>
-      </c>
-      <c r="J117" s="162">
+        <v>12698641.619999992</v>
+      </c>
+      <c r="J117" s="158">
         <f t="shared" si="25"/>
         <v>3004800</v>
       </c>
-      <c r="K117" s="164"/>
-      <c r="L117" s="231"/>
-      <c r="M117" s="172">
+      <c r="K117" s="160"/>
+      <c r="L117" s="179"/>
+      <c r="M117" s="168">
         <f t="shared" si="25"/>
-        <v>35170233.56000001</v>
-      </c>
-      <c r="N117" s="169">
+        <v>34243207.560000002</v>
+      </c>
+      <c r="N117" s="165">
         <f t="shared" si="25"/>
-        <v>36225328.560000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="93"/>
-      <c r="C118" s="93"/>
-    </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="196" t="s">
+        <v>35270505.56000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="92"/>
+      <c r="C118" s="92"/>
+    </row>
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="217" t="s">
         <v>105</v>
       </c>
-      <c r="C120" s="196"/>
-      <c r="D120" s="196"/>
-      <c r="E120" s="196"/>
-      <c r="F120" s="196"/>
-      <c r="G120" s="196"/>
-      <c r="H120" s="196"/>
-      <c r="I120" s="196"/>
-      <c r="J120" s="196"/>
-      <c r="K120" s="196"/>
-      <c r="L120" s="196"/>
-      <c r="M120" s="196"/>
-    </row>
-    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="196"/>
-      <c r="C121" s="196"/>
-      <c r="D121" s="196"/>
-      <c r="E121" s="196"/>
-      <c r="F121" s="196"/>
-      <c r="G121" s="196"/>
-      <c r="H121" s="196"/>
-      <c r="I121" s="196"/>
-      <c r="J121" s="196"/>
-      <c r="K121" s="196"/>
-      <c r="L121" s="196"/>
-      <c r="M121" s="196"/>
-    </row>
-    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="196"/>
-      <c r="C122" s="196"/>
-      <c r="D122" s="196"/>
-      <c r="E122" s="196"/>
-      <c r="F122" s="196"/>
-      <c r="G122" s="196"/>
-      <c r="H122" s="196"/>
-      <c r="I122" s="196"/>
-      <c r="J122" s="196"/>
-      <c r="K122" s="196"/>
-      <c r="L122" s="196"/>
-      <c r="M122" s="196"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="196"/>
-      <c r="C123" s="196"/>
-      <c r="D123" s="196"/>
-      <c r="E123" s="196"/>
-      <c r="F123" s="196"/>
-      <c r="G123" s="196"/>
-      <c r="H123" s="196"/>
-      <c r="I123" s="196"/>
-      <c r="J123" s="196"/>
-      <c r="K123" s="196"/>
-      <c r="L123" s="196"/>
-      <c r="M123" s="196"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="196"/>
-      <c r="C124" s="196"/>
-      <c r="D124" s="196"/>
-      <c r="E124" s="196"/>
-      <c r="F124" s="196"/>
-      <c r="G124" s="196"/>
-      <c r="H124" s="196"/>
-      <c r="I124" s="196"/>
-      <c r="J124" s="196"/>
-      <c r="K124" s="196"/>
-      <c r="L124" s="196"/>
-      <c r="M124" s="196"/>
-    </row>
-    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="196"/>
-      <c r="C125" s="196"/>
-      <c r="D125" s="196"/>
-      <c r="E125" s="196"/>
-      <c r="F125" s="196"/>
-      <c r="G125" s="196"/>
-      <c r="H125" s="196"/>
-      <c r="I125" s="196"/>
-      <c r="J125" s="196"/>
-      <c r="K125" s="196"/>
-      <c r="L125" s="196"/>
-      <c r="M125" s="196"/>
+      <c r="C120" s="217"/>
+      <c r="D120" s="217"/>
+      <c r="E120" s="217"/>
+      <c r="F120" s="217"/>
+      <c r="G120" s="217"/>
+      <c r="H120" s="217"/>
+      <c r="I120" s="217"/>
+      <c r="J120" s="217"/>
+      <c r="K120" s="217"/>
+      <c r="L120" s="217"/>
+      <c r="M120" s="217"/>
+    </row>
+    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="217"/>
+      <c r="C121" s="217"/>
+      <c r="D121" s="217"/>
+      <c r="E121" s="217"/>
+      <c r="F121" s="217"/>
+      <c r="G121" s="217"/>
+      <c r="H121" s="217"/>
+      <c r="I121" s="217"/>
+      <c r="J121" s="217"/>
+      <c r="K121" s="217"/>
+      <c r="L121" s="217"/>
+      <c r="M121" s="217"/>
+    </row>
+    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="217"/>
+      <c r="C122" s="217"/>
+      <c r="D122" s="217"/>
+      <c r="E122" s="217"/>
+      <c r="F122" s="217"/>
+      <c r="G122" s="217"/>
+      <c r="H122" s="217"/>
+      <c r="I122" s="217"/>
+      <c r="J122" s="217"/>
+      <c r="K122" s="217"/>
+      <c r="L122" s="217"/>
+      <c r="M122" s="217"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="217"/>
+      <c r="C123" s="217"/>
+      <c r="D123" s="217"/>
+      <c r="E123" s="217"/>
+      <c r="F123" s="217"/>
+      <c r="G123" s="217"/>
+      <c r="H123" s="217"/>
+      <c r="I123" s="217"/>
+      <c r="J123" s="217"/>
+      <c r="K123" s="217"/>
+      <c r="L123" s="217"/>
+      <c r="M123" s="217"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="217"/>
+      <c r="C124" s="217"/>
+      <c r="D124" s="217"/>
+      <c r="E124" s="217"/>
+      <c r="F124" s="217"/>
+      <c r="G124" s="217"/>
+      <c r="H124" s="217"/>
+      <c r="I124" s="217"/>
+      <c r="J124" s="217"/>
+      <c r="K124" s="217"/>
+      <c r="L124" s="217"/>
+      <c r="M124" s="217"/>
+    </row>
+    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="217"/>
+      <c r="C125" s="217"/>
+      <c r="D125" s="217"/>
+      <c r="E125" s="217"/>
+      <c r="F125" s="217"/>
+      <c r="G125" s="217"/>
+      <c r="H125" s="217"/>
+      <c r="I125" s="217"/>
+      <c r="J125" s="217"/>
+      <c r="K125" s="217"/>
+      <c r="L125" s="217"/>
+      <c r="M125" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="B120:M125"/>
     <mergeCell ref="D1:M1"/>
@@ -9190,55 +9211,60 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A10:N10"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:C25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" s="22"/>
     </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C4" s="22" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="22"/>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C6" s="22"/>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C7" s="22" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="175" t="s">
+    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="169" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/ITALIA/Marzo/Marzo ITALIA.xlsx
+++ b/2026/ITALIA/Marzo/Marzo ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CFCFEF-EE74-45D5-B649-A92DEB239590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760B7A71-1431-449C-BEB5-4B073B7CACCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="244">
   <si>
     <t>TOTAL</t>
   </si>
@@ -617,18 +617,6 @@
     <t>Seguro Sra. Gisela</t>
   </si>
   <si>
-    <t>Al 7F le hicimos su situacion detallada al pie de la letra debe abonar $371.016,53</t>
-  </si>
-  <si>
-    <t>Al 7D le debemos poner el deposito no identificado de enero de $110,000 este mes debe abonar $123.612,51</t>
-  </si>
-  <si>
-    <t>El 3C tiene nuevo propietario,  Marotta Pablo, agregarlo a la cadena de mails pabloeze.marotta@gmail.com</t>
-  </si>
-  <si>
-    <t>8C deposito $132.520 el 12/03</t>
-  </si>
-  <si>
     <t>3 C MAROTTA PABLO</t>
   </si>
   <si>
@@ -656,9 +644,6 @@
     <t>Transf 19/03</t>
   </si>
   <si>
-    <t>La UF 46 Deposito $190.000 el 25/03</t>
-  </si>
-  <si>
     <t>REEMPLAZOS</t>
   </si>
   <si>
@@ -777,6 +762,12 @@
   </si>
   <si>
     <t xml:space="preserve">Plan de pago de 6B: Consta de 24 cuotas de $33.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>La UF 19 el mes pasado quedo con dinero a favor y ese dinero a favor debia ir a la cochera 100</t>
+  </si>
+  <si>
+    <t>Transferencia no idenfiticada de 202060,8 de el del 06/01 debe abonar $390.640,8 pago $224.260,8</t>
   </si>
 </sst>
 </file>
@@ -958,7 +949,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,7 +1030,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1547,7 +1544,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1819,7 +1816,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="18" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1863,6 +1859,13 @@
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="19" fillId="13" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1902,106 +1905,114 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="13" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="19" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2390,12 +2401,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="201"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="205"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2408,12 +2419,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="202" t="s">
+      <c r="B3" s="206" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="203"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2431,7 +2442,7 @@
         <v>151</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2451,49 +2462,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="204" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="204"/>
+      <c r="B8" s="208" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="208"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="204"/>
-      <c r="C10" s="204"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="205" t="s">
+      <c r="A13" s="209" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="205"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="205"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="205"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
+      <c r="A14" s="209"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="205"/>
-      <c r="B15" s="205"/>
-      <c r="C15" s="205"/>
-      <c r="D15" s="205"/>
-      <c r="E15" s="205"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="205"/>
-      <c r="B16" s="205"/>
-      <c r="C16" s="205"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="205"/>
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2516,25 +2527,25 @@
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="129"/>
-      <c r="E21" s="181"/>
+      <c r="E21" s="180"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="196" t="s">
+      <c r="A22" s="200" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="197"/>
+      <c r="B22" s="201"/>
       <c r="C22" s="21"/>
       <c r="D22" s="139">
         <v>2109818.7799999998</v>
       </c>
-      <c r="E22" s="182"/>
+      <c r="E22" s="181"/>
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="196" t="s">
+      <c r="A23" s="200" t="s">
         <v>171</v>
       </c>
-      <c r="B23" s="197"/>
+      <c r="B23" s="201"/>
       <c r="C23" s="21"/>
       <c r="D23" s="139">
         <v>-458885.59</v>
@@ -2543,10 +2554,10 @@
       <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="196" t="s">
+      <c r="A24" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="197"/>
+      <c r="B24" s="201"/>
       <c r="C24" s="21"/>
       <c r="D24" s="140">
         <v>0.81</v>
@@ -2561,19 +2572,19 @@
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
       <c r="D25" s="25"/>
-      <c r="E25" s="183">
+      <c r="E25" s="182">
         <f>SUM(D22:D24)</f>
         <v>1650933.9999999998</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="184"/>
+      <c r="E26" s="183"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
@@ -2584,7 +2595,7 @@
       <c r="D27" s="38">
         <v>370000</v>
       </c>
-      <c r="E27" s="185"/>
+      <c r="E27" s="184"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
@@ -2595,7 +2606,7 @@
       <c r="D28" s="38">
         <v>5842.51</v>
       </c>
-      <c r="E28" s="186" t="s">
+      <c r="E28" s="185" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2606,7 +2617,7 @@
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
       <c r="D29" s="118"/>
-      <c r="E29" s="187">
+      <c r="E29" s="186">
         <f>D27+D28</f>
         <v>375842.51</v>
       </c>
@@ -2618,16 +2629,16 @@
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
       <c r="D30" s="25"/>
-      <c r="E30" s="184"/>
+      <c r="E30" s="183"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B31" s="94"/>
       <c r="C31" s="94"/>
       <c r="D31" s="38"/>
-      <c r="E31" s="186"/>
+      <c r="E31" s="185"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
@@ -2638,8 +2649,8 @@
       <c r="D32" s="38">
         <v>960321.67</v>
       </c>
-      <c r="E32" s="186" t="s">
-        <v>214</v>
+      <c r="E32" s="185" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2651,8 +2662,8 @@
       <c r="D33" s="38">
         <v>166275.49</v>
       </c>
-      <c r="E33" s="186" t="s">
-        <v>212</v>
+      <c r="E33" s="185" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2664,7 +2675,7 @@
       <c r="D34" s="38">
         <v>86923.04</v>
       </c>
-      <c r="E34" s="186" t="str">
+      <c r="E34" s="185" t="str">
         <f>E33</f>
         <v>Debito 12/03</v>
       </c>
@@ -2678,7 +2689,7 @@
       <c r="D35" s="38">
         <v>9658.1200000000008</v>
       </c>
-      <c r="E35" s="186" t="str">
+      <c r="E35" s="185" t="str">
         <f>E33</f>
         <v>Debito 12/03</v>
       </c>
@@ -2690,7 +2701,7 @@
       <c r="B36" s="94"/>
       <c r="C36" s="94"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="186"/>
+      <c r="E36" s="185"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
@@ -2711,19 +2722,19 @@
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
       <c r="D38" s="26"/>
-      <c r="E38" s="187"/>
+      <c r="E38" s="186"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="206" t="s">
+      <c r="A39" s="210" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="207"/>
+      <c r="B39" s="211"/>
       <c r="C39" s="29"/>
       <c r="D39" s="141">
         <v>214164</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2745,7 +2756,7 @@
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
       <c r="D41" s="31"/>
-      <c r="E41" s="188"/>
+      <c r="E41" s="187"/>
     </row>
     <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="32" t="s">
@@ -2775,7 +2786,7 @@
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B44" s="32" t="s">
         <v>181</v>
@@ -2785,12 +2796,12 @@
         <v>43276.24</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="32"/>
@@ -2798,20 +2809,20 @@
         <v>9529.66</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="206" t="s">
+      <c r="A46" s="210" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="207"/>
+      <c r="B46" s="211"/>
       <c r="C46" s="32"/>
       <c r="D46" s="33">
         <v>4890986.6399999997</v>
       </c>
       <c r="E46" s="130" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2830,7 +2841,7 @@
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
       <c r="D48" s="36"/>
-      <c r="E48" s="189">
+      <c r="E48" s="188">
         <f>SUM(D42:D47)</f>
         <v>4943792.54</v>
       </c>
@@ -2840,64 +2851,64 @@
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
       <c r="D49" s="25"/>
-      <c r="E49" s="190"/>
+      <c r="E49" s="189"/>
     </row>
     <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="196" t="s">
+      <c r="A50" s="200" t="s">
         <v>173</v>
       </c>
-      <c r="B50" s="197"/>
+      <c r="B50" s="201"/>
       <c r="C50" s="32"/>
       <c r="D50" s="33">
         <v>285000</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="196" t="s">
-        <v>240</v>
-      </c>
-      <c r="B51" s="197"/>
+      <c r="A51" s="200" t="s">
+        <v>235</v>
+      </c>
+      <c r="B51" s="201"/>
       <c r="C51" s="32"/>
       <c r="D51" s="33">
         <v>1300000</v>
       </c>
       <c r="E51" s="127" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="196" t="s">
-        <v>241</v>
-      </c>
-      <c r="B52" s="197"/>
+      <c r="A52" s="200" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" s="201"/>
       <c r="C52" s="32"/>
       <c r="D52" s="33">
         <v>380000</v>
       </c>
       <c r="E52" s="127" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="196" t="s">
-        <v>204</v>
-      </c>
-      <c r="B53" s="197"/>
+      <c r="A53" s="200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="201"/>
       <c r="C53" s="32"/>
       <c r="D53" s="33">
         <v>170000</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F53" s="53"/>
     </row>
     <row r="54" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="103" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="32"/>
@@ -2905,21 +2916,21 @@
         <v>910000</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F54" s="53"/>
     </row>
     <row r="55" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="196" t="s">
+      <c r="A55" s="200" t="s">
         <v>189</v>
       </c>
-      <c r="B55" s="197"/>
+      <c r="B55" s="201"/>
       <c r="C55" s="32"/>
       <c r="D55" s="33">
         <v>1400000</v>
       </c>
-      <c r="E55" s="182" t="s">
-        <v>205</v>
+      <c r="E55" s="181" t="s">
+        <v>201</v>
       </c>
       <c r="F55" s="53"/>
     </row>
@@ -2947,49 +2958,49 @@
         <v>289750</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F57" s="53"/>
     </row>
     <row r="58" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="196" t="s">
-        <v>227</v>
-      </c>
-      <c r="B58" s="197"/>
+      <c r="A58" s="200" t="s">
+        <v>222</v>
+      </c>
+      <c r="B58" s="201"/>
       <c r="C58" s="32"/>
       <c r="D58" s="33">
         <v>2550520.2599999998</v>
       </c>
-      <c r="E58" s="182" t="s">
-        <v>213</v>
+      <c r="E58" s="181" t="s">
+        <v>208</v>
       </c>
       <c r="F58" s="53"/>
     </row>
     <row r="59" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="103" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="32"/>
       <c r="D59" s="33">
         <v>137300</v>
       </c>
-      <c r="E59" s="182" t="s">
-        <v>202</v>
+      <c r="E59" s="181" t="s">
+        <v>198</v>
       </c>
       <c r="F59" s="53"/>
     </row>
     <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="196" t="s">
-        <v>211</v>
-      </c>
-      <c r="B60" s="197"/>
+      <c r="A60" s="200" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" s="201"/>
       <c r="C60" s="32"/>
       <c r="D60" s="33">
         <v>105602.65</v>
       </c>
-      <c r="E60" s="182" t="s">
-        <v>202</v>
+      <c r="E60" s="181" t="s">
+        <v>198</v>
       </c>
       <c r="F60" s="53"/>
     </row>
@@ -3012,28 +3023,28 @@
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
       <c r="D62" s="18"/>
-      <c r="E62" s="181"/>
+      <c r="E62" s="180"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="196" t="s">
-        <v>208</v>
-      </c>
-      <c r="B63" s="197"/>
+      <c r="A63" s="200" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" s="201"/>
       <c r="C63" s="21"/>
       <c r="D63" s="142"/>
-      <c r="E63" s="182"/>
+      <c r="E63" s="181"/>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="21"/>
       <c r="D64" s="143">
         <v>100000</v>
       </c>
-      <c r="E64" s="182" t="s">
-        <v>205</v>
+      <c r="E64" s="181" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3045,21 +3056,21 @@
       <c r="D65" s="143">
         <v>125000</v>
       </c>
-      <c r="E65" s="182" t="s">
-        <v>210</v>
+      <c r="E65" s="181" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="103" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="21"/>
       <c r="D66" s="143">
         <v>45000</v>
       </c>
-      <c r="E66" s="182" t="s">
-        <v>203</v>
+      <c r="E66" s="181" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -3069,7 +3080,7 @@
       <c r="B67" s="24"/>
       <c r="C67" s="24"/>
       <c r="D67" s="25"/>
-      <c r="E67" s="183">
+      <c r="E67" s="182">
         <f>SUM(D63:D66)</f>
         <v>270000</v>
       </c>
@@ -3092,7 +3103,7 @@
       <c r="D69" s="144">
         <v>52000</v>
       </c>
-      <c r="E69" s="191"/>
+      <c r="E69" s="190"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
@@ -3103,7 +3114,7 @@
       <c r="D70" s="144">
         <v>227782.42</v>
       </c>
-      <c r="E70" s="191"/>
+      <c r="E70" s="190"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="42" t="s">
@@ -3179,8 +3190,8 @@
       <c r="E79" s="63"/>
     </row>
     <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="196"/>
-      <c r="B80" s="197"/>
+      <c r="A80" s="200"/>
+      <c r="B80" s="201"/>
       <c r="C80" s="32"/>
       <c r="D80" s="38"/>
       <c r="E80" s="63"/>
@@ -3203,7 +3214,7 @@
       <c r="B83" s="66"/>
       <c r="C83" s="66"/>
       <c r="D83" s="128"/>
-      <c r="E83" s="192">
+      <c r="E83" s="191">
         <f>SUM(D79:D82)</f>
         <v>0</v>
       </c>
@@ -3223,7 +3234,7 @@
       <c r="B86" s="47"/>
       <c r="C86" s="47"/>
       <c r="D86" s="48"/>
-      <c r="E86" s="241">
+      <c r="E86" s="195">
         <v>3000000</v>
       </c>
     </row>
@@ -3300,22 +3311,22 @@
       <c r="E95" s="51"/>
     </row>
     <row r="96" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="195" t="s">
+      <c r="A96" s="199" t="s">
         <v>185</v>
       </c>
-      <c r="B96" s="195"/>
+      <c r="B96" s="199"/>
       <c r="D96" s="51"/>
       <c r="E96" s="51"/>
     </row>
     <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="195"/>
-      <c r="B97" s="195"/>
+      <c r="A97" s="199"/>
+      <c r="B97" s="199"/>
       <c r="D97" s="51"/>
       <c r="E97" s="51"/>
     </row>
     <row r="98" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="195"/>
-      <c r="B98" s="195"/>
+      <c r="A98" s="199"/>
+      <c r="B98" s="199"/>
       <c r="D98" s="51"/>
       <c r="E98" s="51"/>
     </row>
@@ -3324,22 +3335,22 @@
       <c r="E99" s="51"/>
     </row>
     <row r="100" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="195" t="s">
+      <c r="A100" s="199" t="s">
         <v>186</v>
       </c>
-      <c r="B100" s="195"/>
+      <c r="B100" s="199"/>
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
     </row>
     <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="195"/>
-      <c r="B101" s="195"/>
+      <c r="A101" s="199"/>
+      <c r="B101" s="199"/>
       <c r="D101" s="51"/>
       <c r="E101" s="51"/>
     </row>
     <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="195"/>
-      <c r="B102" s="195"/>
+      <c r="A102" s="199"/>
+      <c r="B102" s="199"/>
       <c r="D102" s="51"/>
       <c r="E102" s="51"/>
     </row>
@@ -3348,22 +3359,22 @@
       <c r="E103" s="51"/>
     </row>
     <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="195" t="s">
-        <v>233</v>
-      </c>
-      <c r="B104" s="195"/>
+      <c r="A104" s="199" t="s">
+        <v>228</v>
+      </c>
+      <c r="B104" s="199"/>
       <c r="D104" s="51"/>
       <c r="E104" s="51"/>
     </row>
     <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="195"/>
-      <c r="B105" s="195"/>
+      <c r="A105" s="199"/>
+      <c r="B105" s="199"/>
       <c r="D105" s="51"/>
       <c r="E105" s="51"/>
     </row>
     <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="195"/>
-      <c r="B106" s="195"/>
+      <c r="A106" s="199"/>
+      <c r="B106" s="199"/>
       <c r="D106" s="51"/>
       <c r="E106" s="51"/>
     </row>
@@ -3372,22 +3383,22 @@
       <c r="E107" s="51"/>
     </row>
     <row r="108" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="195" t="s">
-        <v>246</v>
-      </c>
-      <c r="B108" s="195"/>
+      <c r="A108" s="199" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="199"/>
       <c r="D108" s="51"/>
       <c r="E108" s="51"/>
     </row>
     <row r="109" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="195"/>
-      <c r="B109" s="195"/>
+      <c r="A109" s="199"/>
+      <c r="B109" s="199"/>
       <c r="D109" s="51"/>
       <c r="E109" s="51"/>
     </row>
     <row r="110" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="195"/>
-      <c r="B110" s="195"/>
+      <c r="A110" s="199"/>
+      <c r="B110" s="199"/>
       <c r="D110" s="51"/>
       <c r="E110" s="51"/>
     </row>
@@ -3396,22 +3407,22 @@
       <c r="E111" s="51"/>
     </row>
     <row r="112" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="195" t="s">
-        <v>242</v>
-      </c>
-      <c r="B112" s="195"/>
+      <c r="A112" s="199" t="s">
+        <v>237</v>
+      </c>
+      <c r="B112" s="199"/>
       <c r="D112" s="51"/>
       <c r="E112" s="51"/>
     </row>
     <row r="113" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="195"/>
-      <c r="B113" s="195"/>
+      <c r="A113" s="199"/>
+      <c r="B113" s="199"/>
       <c r="D113" s="51"/>
       <c r="E113" s="51"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="195"/>
-      <c r="B114" s="195"/>
+      <c r="A114" s="199"/>
+      <c r="B114" s="199"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
     </row>
@@ -3420,16 +3431,16 @@
       <c r="E115" s="51"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="199" t="s">
+      <c r="A116" s="203" t="s">
         <v>191</v>
       </c>
-      <c r="B116" s="199"/>
+      <c r="B116" s="203"/>
       <c r="D116" s="51"/>
       <c r="E116" s="51"/>
     </row>
     <row r="117" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="199"/>
-      <c r="B117" s="199"/>
+      <c r="A117" s="203"/>
+      <c r="B117" s="203"/>
       <c r="D117" s="51"/>
       <c r="E117" s="51"/>
     </row>
@@ -3437,8 +3448,8 @@
       <c r="A118"/>
       <c r="B118" s="69"/>
       <c r="C118" s="70"/>
-      <c r="D118" s="193"/>
-      <c r="E118" s="193"/>
+      <c r="D118" s="192"/>
+      <c r="E118" s="192"/>
     </row>
     <row r="119" spans="1:6" s="71" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="102" t="s">
@@ -3448,8 +3459,8 @@
         <v>1066133.5837450363</v>
       </c>
       <c r="C119" s="70"/>
-      <c r="D119" s="194"/>
-      <c r="E119" s="194"/>
+      <c r="D119" s="193"/>
+      <c r="E119" s="193"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="29" t="s">
@@ -3480,7 +3491,7 @@
       </c>
       <c r="B122" s="74">
         <f>PRORRATEO!F117</f>
-        <v>14192055.65</v>
+        <v>14414116.450000001</v>
       </c>
       <c r="D122" s="51"/>
       <c r="E122" s="51"/>
@@ -3488,9 +3499,9 @@
     </row>
     <row r="123" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="B123" s="170">
+        <v>216</v>
+      </c>
+      <c r="B123" s="169">
         <v>-110000</v>
       </c>
       <c r="D123" s="51"/>
@@ -3499,9 +3510,9 @@
     </row>
     <row r="124" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B124" s="170">
+        <v>224</v>
+      </c>
+      <c r="B124" s="169">
         <v>-6066</v>
       </c>
       <c r="D124" s="51"/>
@@ -3510,9 +3521,9 @@
     </row>
     <row r="125" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="B125" s="170">
+        <v>225</v>
+      </c>
+      <c r="B125" s="169">
         <v>-20610</v>
       </c>
       <c r="D125" s="51"/>
@@ -3521,9 +3532,9 @@
     </row>
     <row r="126" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="B126" s="170">
+        <v>221</v>
+      </c>
+      <c r="B126" s="169">
         <v>-50000</v>
       </c>
       <c r="D126" s="51"/>
@@ -3531,10 +3542,10 @@
       <c r="F126" s="69"/>
     </row>
     <row r="127" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="171" t="s">
-        <v>235</v>
-      </c>
-      <c r="B127" s="174">
+      <c r="A127" s="170" t="s">
+        <v>230</v>
+      </c>
+      <c r="B127" s="173">
         <f>300000+B128-123612</f>
         <v>44388</v>
       </c>
@@ -3543,8 +3554,8 @@
       <c r="F127" s="69"/>
     </row>
     <row r="128" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="171" t="s">
-        <v>225</v>
+      <c r="A128" s="170" t="s">
+        <v>220</v>
       </c>
       <c r="B128" s="137">
         <v>-132000</v>
@@ -3554,10 +3565,10 @@
       <c r="F128" s="69"/>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="171" t="s">
-        <v>232</v>
-      </c>
-      <c r="B129" s="172">
+      <c r="A129" s="170" t="s">
+        <v>227</v>
+      </c>
+      <c r="B129" s="171">
         <f>150000+B128</f>
         <v>18000</v>
       </c>
@@ -3566,8 +3577,8 @@
       <c r="F129" s="69"/>
     </row>
     <row r="130" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A130" s="171" t="s">
-        <v>228</v>
+      <c r="A130" s="170" t="s">
+        <v>223</v>
       </c>
       <c r="B130" s="137">
         <v>-132000</v>
@@ -3580,7 +3591,7 @@
       </c>
       <c r="B131" s="76">
         <f>SUM(B119:C130)</f>
-        <v>-1256883.5662549641</v>
+        <v>-1034822.7662549634</v>
       </c>
       <c r="D131" s="69"/>
       <c r="E131" s="53"/>
@@ -3588,20 +3599,20 @@
     </row>
     <row r="132" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A133" s="198" t="s">
+      <c r="A133" s="202" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="198"/>
-      <c r="C133" s="198"/>
+      <c r="B133" s="202"/>
+      <c r="C133" s="202"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A134" s="198"/>
-      <c r="B134" s="198"/>
-      <c r="C134" s="198"/>
+      <c r="A134" s="202"/>
+      <c r="B134" s="202"/>
+      <c r="C134" s="202"/>
     </row>
     <row r="135" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="77" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B135" s="126">
         <v>195940.3</v>
@@ -3610,8 +3621,8 @@
       <c r="D135" s="59"/>
     </row>
     <row r="136" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="173" t="s">
-        <v>234</v>
+      <c r="A136" s="172" t="s">
+        <v>229</v>
       </c>
       <c r="B136" s="126">
         <v>168841.60000000001</v>
@@ -3693,16 +3704,16 @@
       <c r="A1" s="104"/>
       <c r="B1" s="105"/>
       <c r="C1" s="105"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
-      <c r="F1" s="218"/>
-      <c r="G1" s="218"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
-      <c r="M1" s="218"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="106"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3712,10 +3723,10 @@
       <c r="D2" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="208">
+      <c r="E2" s="243">
         <v>3000000</v>
       </c>
-      <c r="F2" s="208"/>
+      <c r="F2" s="243"/>
       <c r="G2" s="109"/>
       <c r="H2" s="109"/>
       <c r="I2" s="109" t="s">
@@ -3749,189 +3760,189 @@
       <c r="O3" s="83"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="222" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="221"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="224"/>
       <c r="O4" s="83"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="222"/>
-      <c r="B5" s="223"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="224"/>
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="227"/>
       <c r="O5" s="83"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="222"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="224"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="227"/>
       <c r="O6" s="83"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="224"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="227"/>
       <c r="O7" s="83"/>
     </row>
     <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="225"/>
-      <c r="B8" s="226"/>
-      <c r="C8" s="226"/>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
-      <c r="G8" s="226"/>
-      <c r="H8" s="226"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226"/>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226"/>
-      <c r="M8" s="226"/>
-      <c r="N8" s="227"/>
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="230"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="237" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="236"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="238"/>
+      <c r="D9" s="238"/>
+      <c r="E9" s="238"/>
+      <c r="F9" s="238"/>
+      <c r="G9" s="238"/>
+      <c r="H9" s="238"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="238"/>
+      <c r="K9" s="238"/>
+      <c r="L9" s="238"/>
+      <c r="M9" s="238"/>
+      <c r="N9" s="239"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="237" t="s">
+      <c r="A10" s="240" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="238"/>
-      <c r="M10" s="238"/>
-      <c r="N10" s="239"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
+      <c r="N10" s="242"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="228" t="s">
+      <c r="A11" s="231" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="230" t="s">
+      <c r="B11" s="233" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="230" t="s">
+      <c r="C11" s="233" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="230" t="s">
+      <c r="D11" s="233" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="209" t="s">
+      <c r="E11" s="216" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="230" t="s">
+      <c r="F11" s="233" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="232" t="s">
+      <c r="G11" s="235" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="209" t="s">
+      <c r="H11" s="216" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="209" t="s">
+      <c r="I11" s="216" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="209" t="s">
+      <c r="J11" s="216" t="s">
         <v>128</v>
       </c>
-      <c r="K11" s="211" t="s">
+      <c r="K11" s="212" t="s">
         <v>188</v>
       </c>
-      <c r="L11" s="213" t="s">
-        <v>236</v>
+      <c r="L11" s="214" t="s">
+        <v>231</v>
       </c>
       <c r="M11" s="166" t="s">
         <v>138</v>
       </c>
-      <c r="N11" s="215" t="s">
+      <c r="N11" s="218" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="229"/>
-      <c r="B12" s="231"/>
-      <c r="C12" s="231"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="210"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="210"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="210"/>
-      <c r="K12" s="212"/>
-      <c r="L12" s="214"/>
+      <c r="A12" s="232"/>
+      <c r="B12" s="234"/>
+      <c r="C12" s="234"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="234"/>
+      <c r="G12" s="236"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="213"/>
+      <c r="L12" s="215"/>
       <c r="M12" s="167" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="N12" s="216"/>
+      <c r="N12" s="219"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="150">
@@ -3968,7 +3979,7 @@
         <v>41100.000000000007</v>
       </c>
       <c r="K13" s="145"/>
-      <c r="L13" s="175"/>
+      <c r="L13" s="174"/>
       <c r="M13" s="89">
         <f>ROUND(SUM(G13:L13),0) + O13</f>
         <v>214793.01</v>
@@ -4016,7 +4027,7 @@
         <v>35400</v>
       </c>
       <c r="K14" s="146"/>
-      <c r="L14" s="176"/>
+      <c r="L14" s="175"/>
       <c r="M14" s="99">
         <f>ROUND(SUM(G14:L14),0) + O14</f>
         <v>2972428.02</v>
@@ -4068,7 +4079,7 @@
         <v>22200</v>
       </c>
       <c r="K15" s="145"/>
-      <c r="L15" s="175"/>
+      <c r="L15" s="174"/>
       <c r="M15" s="89">
         <f t="shared" ref="M15:M78" si="5">ROUND(SUM(G15:L15),0) + O15</f>
         <v>116020.03</v>
@@ -4117,7 +4128,7 @@
         <v>44100</v>
       </c>
       <c r="K16" s="147"/>
-      <c r="L16" s="177"/>
+      <c r="L16" s="176"/>
       <c r="M16" s="89">
         <f t="shared" si="5"/>
         <v>230472.04</v>
@@ -4166,7 +4177,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K17" s="145"/>
-      <c r="L17" s="175"/>
+      <c r="L17" s="174"/>
       <c r="M17" s="89">
         <f t="shared" si="5"/>
         <v>175598.05</v>
@@ -4214,7 +4225,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K18" s="145"/>
-      <c r="L18" s="175"/>
+      <c r="L18" s="174"/>
       <c r="M18" s="89">
         <f t="shared" si="5"/>
         <v>205165.06</v>
@@ -4263,7 +4274,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K19" s="145"/>
-      <c r="L19" s="175"/>
+      <c r="L19" s="174"/>
       <c r="M19" s="89">
         <f t="shared" si="5"/>
         <v>175598.07</v>
@@ -4312,7 +4323,7 @@
         <v>24600</v>
       </c>
       <c r="K20" s="145"/>
-      <c r="L20" s="175"/>
+      <c r="L20" s="174"/>
       <c r="M20" s="89">
         <f t="shared" si="5"/>
         <v>128563.08</v>
@@ -4360,7 +4371,7 @@
         <v>24600</v>
       </c>
       <c r="K21" s="145"/>
-      <c r="L21" s="175"/>
+      <c r="L21" s="174"/>
       <c r="M21" s="89">
         <f t="shared" si="5"/>
         <v>124963.09</v>
@@ -4408,7 +4419,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K22" s="145"/>
-      <c r="L22" s="175"/>
+      <c r="L22" s="174"/>
       <c r="M22" s="89">
         <f t="shared" si="5"/>
         <v>216332.1</v>
@@ -4457,7 +4468,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K23" s="145"/>
-      <c r="L23" s="175"/>
+      <c r="L23" s="174"/>
       <c r="M23" s="89">
         <f t="shared" si="5"/>
         <v>175598.11</v>
@@ -4505,7 +4516,7 @@
         <v>35100</v>
       </c>
       <c r="K24" s="145"/>
-      <c r="L24" s="175"/>
+      <c r="L24" s="174"/>
       <c r="M24" s="89">
         <f t="shared" si="5"/>
         <v>3844889.12</v>
@@ -4554,7 +4565,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K25" s="145"/>
-      <c r="L25" s="175"/>
+      <c r="L25" s="174"/>
       <c r="M25" s="89">
         <f t="shared" si="5"/>
         <v>211658.13</v>
@@ -4600,7 +4611,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K26" s="145"/>
-      <c r="L26" s="175"/>
+      <c r="L26" s="174"/>
       <c r="M26" s="89">
         <f t="shared" si="5"/>
         <v>349499.14</v>
@@ -4649,7 +4660,7 @@
         <v>24600</v>
       </c>
       <c r="K27" s="145"/>
-      <c r="L27" s="175"/>
+      <c r="L27" s="174"/>
       <c r="M27" s="89">
         <f t="shared" si="5"/>
         <v>128563.15</v>
@@ -4697,7 +4708,7 @@
         <v>24600</v>
       </c>
       <c r="K28" s="145"/>
-      <c r="L28" s="175"/>
+      <c r="L28" s="174"/>
       <c r="M28" s="89">
         <f t="shared" si="5"/>
         <v>347847.16</v>
@@ -4746,7 +4757,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K29" s="145"/>
-      <c r="L29" s="175"/>
+      <c r="L29" s="174"/>
       <c r="M29" s="89">
         <f t="shared" si="5"/>
         <v>210090.17</v>
@@ -4795,7 +4806,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K30" s="147"/>
-      <c r="L30" s="177"/>
+      <c r="L30" s="176"/>
       <c r="M30" s="89">
         <f t="shared" si="5"/>
         <v>175598.18</v>
@@ -4810,10 +4821,10 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="150">
+      <c r="A31" s="196">
         <v>19</v>
       </c>
-      <c r="B31" s="84" t="s">
+      <c r="B31" s="197" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="90"/>
@@ -4843,7 +4854,7 @@
         <v>35100</v>
       </c>
       <c r="K31" s="145"/>
-      <c r="L31" s="175"/>
+      <c r="L31" s="174"/>
       <c r="M31" s="89">
         <f t="shared" si="5"/>
         <v>168363.19</v>
@@ -4889,7 +4900,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K32" s="149"/>
-      <c r="L32" s="178">
+      <c r="L32" s="177">
         <v>123300</v>
       </c>
       <c r="M32" s="136">
@@ -4905,7 +4916,7 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="P32" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -4943,7 +4954,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K33" s="147"/>
-      <c r="L33" s="177"/>
+      <c r="L33" s="176"/>
       <c r="M33" s="89">
         <f t="shared" si="5"/>
         <v>175598.21</v>
@@ -4963,7 +4974,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="125" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C34" s="90"/>
       <c r="D34" s="85">
@@ -4992,7 +5003,7 @@
         <v>24600</v>
       </c>
       <c r="K34" s="145"/>
-      <c r="L34" s="175"/>
+      <c r="L34" s="174"/>
       <c r="M34" s="89">
         <f t="shared" si="5"/>
         <v>124966.22</v>
@@ -5041,7 +5052,7 @@
         <v>24600</v>
       </c>
       <c r="K35" s="145"/>
-      <c r="L35" s="175"/>
+      <c r="L35" s="174"/>
       <c r="M35" s="89">
         <f t="shared" si="5"/>
         <v>124855.23</v>
@@ -5091,7 +5102,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K36" s="145"/>
-      <c r="L36" s="175"/>
+      <c r="L36" s="174"/>
       <c r="M36" s="89">
         <f t="shared" si="5"/>
         <v>210090.23999999999</v>
@@ -5138,7 +5149,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K37" s="145"/>
-      <c r="L37" s="175"/>
+      <c r="L37" s="174"/>
       <c r="M37" s="89">
         <f t="shared" si="5"/>
         <v>509323.25</v>
@@ -5187,7 +5198,7 @@
         <v>35100</v>
       </c>
       <c r="K38" s="145"/>
-      <c r="L38" s="175"/>
+      <c r="L38" s="174"/>
       <c r="M38" s="89">
         <f t="shared" si="5"/>
         <v>178146.26</v>
@@ -5239,7 +5250,7 @@
       <c r="K39" s="145">
         <v>50000</v>
       </c>
-      <c r="L39" s="175"/>
+      <c r="L39" s="174"/>
       <c r="M39" s="89">
         <f t="shared" si="5"/>
         <v>261658.27</v>
@@ -5288,7 +5299,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K40" s="145"/>
-      <c r="L40" s="175"/>
+      <c r="L40" s="174"/>
       <c r="M40" s="89">
         <f t="shared" si="5"/>
         <v>170680.28</v>
@@ -5338,7 +5349,7 @@
         <v>24600</v>
       </c>
       <c r="K41" s="147"/>
-      <c r="L41" s="177"/>
+      <c r="L41" s="176"/>
       <c r="M41" s="89">
         <f t="shared" si="5"/>
         <v>128563.29</v>
@@ -5390,7 +5401,7 @@
         <v>24600</v>
       </c>
       <c r="K42" s="145"/>
-      <c r="L42" s="175"/>
+      <c r="L42" s="174"/>
       <c r="M42" s="89">
         <f t="shared" si="5"/>
         <v>128431.3</v>
@@ -5440,7 +5451,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K43" s="145"/>
-      <c r="L43" s="175"/>
+      <c r="L43" s="174"/>
       <c r="M43" s="89">
         <f t="shared" si="5"/>
         <v>210090.31</v>
@@ -5489,7 +5500,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K44" s="145"/>
-      <c r="L44" s="175"/>
+      <c r="L44" s="174"/>
       <c r="M44" s="89">
         <f t="shared" si="5"/>
         <v>347920.32</v>
@@ -5536,7 +5547,7 @@
         <v>35100</v>
       </c>
       <c r="K45" s="149"/>
-      <c r="L45" s="178">
+      <c r="L45" s="177">
         <v>170000</v>
       </c>
       <c r="M45" s="136">
@@ -5552,7 +5563,7 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P45" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
@@ -5591,7 +5602,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K46" s="145"/>
-      <c r="L46" s="175"/>
+      <c r="L46" s="174"/>
       <c r="M46" s="89">
         <f t="shared" si="5"/>
         <v>211658.34</v>
@@ -5640,7 +5651,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K47" s="147"/>
-      <c r="L47" s="177"/>
+      <c r="L47" s="176"/>
       <c r="M47" s="89">
         <f t="shared" si="5"/>
         <v>148450.35</v>
@@ -5693,7 +5704,7 @@
         <v>24600</v>
       </c>
       <c r="K48" s="145"/>
-      <c r="L48" s="175"/>
+      <c r="L48" s="174"/>
       <c r="M48" s="89">
         <f t="shared" si="5"/>
         <v>128563.36</v>
@@ -5746,7 +5757,7 @@
         <v>24600</v>
       </c>
       <c r="K49" s="145"/>
-      <c r="L49" s="175"/>
+      <c r="L49" s="174"/>
       <c r="M49" s="89">
         <f t="shared" si="5"/>
         <v>128563.37</v>
@@ -5793,7 +5804,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K50" s="145"/>
-      <c r="L50" s="175"/>
+      <c r="L50" s="174"/>
       <c r="M50" s="89">
         <f t="shared" si="5"/>
         <v>626024.38</v>
@@ -5843,7 +5854,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K51" s="145"/>
-      <c r="L51" s="175"/>
+      <c r="L51" s="174"/>
       <c r="M51" s="89">
         <f t="shared" si="5"/>
         <v>175598.39</v>
@@ -5890,7 +5901,7 @@
         <v>35100</v>
       </c>
       <c r="K52" s="145"/>
-      <c r="L52" s="175"/>
+      <c r="L52" s="174"/>
       <c r="M52" s="89">
         <f t="shared" si="5"/>
         <v>744945.4</v>
@@ -5939,7 +5950,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K53" s="145"/>
-      <c r="L53" s="175"/>
+      <c r="L53" s="174"/>
       <c r="M53" s="89">
         <f t="shared" si="5"/>
         <v>205736.41</v>
@@ -5986,7 +5997,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K54" s="149"/>
-      <c r="L54" s="178">
+      <c r="L54" s="177">
         <v>33000</v>
       </c>
       <c r="M54" s="136">
@@ -6002,7 +6013,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P54" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
@@ -6017,7 +6028,7 @@
       <c r="D55" s="133">
         <v>0.82</v>
       </c>
-      <c r="E55" s="240">
+      <c r="E55" s="194">
         <v>123612.43</v>
       </c>
       <c r="F55" s="134">
@@ -6041,7 +6052,7 @@
         <v>24600</v>
       </c>
       <c r="K55" s="149"/>
-      <c r="L55" s="178">
+      <c r="L55" s="177">
         <v>300000</v>
       </c>
       <c r="M55" s="136">
@@ -6057,7 +6068,7 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P55" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
@@ -6096,7 +6107,7 @@
         <v>24600</v>
       </c>
       <c r="K56" s="145"/>
-      <c r="L56" s="175"/>
+      <c r="L56" s="174"/>
       <c r="M56" s="89">
         <f t="shared" si="5"/>
         <v>128563.44</v>
@@ -6146,7 +6157,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K57" s="145"/>
-      <c r="L57" s="175"/>
+      <c r="L57" s="174"/>
       <c r="M57" s="89">
         <f t="shared" si="5"/>
         <v>210090.45</v>
@@ -6195,7 +6206,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K58" s="145"/>
-      <c r="L58" s="175"/>
+      <c r="L58" s="174"/>
       <c r="M58" s="89">
         <f t="shared" si="5"/>
         <v>197570.46</v>
@@ -6245,7 +6256,7 @@
         <v>35100</v>
       </c>
       <c r="K59" s="149"/>
-      <c r="L59" s="178">
+      <c r="L59" s="177">
         <v>135000</v>
       </c>
       <c r="M59" s="136">
@@ -6261,7 +6272,7 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
@@ -6300,7 +6311,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K60" s="147"/>
-      <c r="L60" s="177"/>
+      <c r="L60" s="176"/>
       <c r="M60" s="89">
         <f t="shared" si="5"/>
         <v>211658.48</v>
@@ -6352,7 +6363,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K61" s="145"/>
-      <c r="L61" s="175"/>
+      <c r="L61" s="174"/>
       <c r="M61" s="89">
         <f t="shared" si="5"/>
         <v>170680.49</v>
@@ -6399,7 +6410,7 @@
         <v>24600</v>
       </c>
       <c r="K62" s="145"/>
-      <c r="L62" s="175"/>
+      <c r="L62" s="174"/>
       <c r="M62" s="89">
         <f t="shared" si="5"/>
         <v>255883.5</v>
@@ -6449,7 +6460,7 @@
         <v>24600</v>
       </c>
       <c r="K63" s="145"/>
-      <c r="L63" s="175"/>
+      <c r="L63" s="174"/>
       <c r="M63" s="89">
         <f t="shared" si="5"/>
         <v>128563.51</v>
@@ -6499,7 +6510,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K64" s="145"/>
-      <c r="L64" s="175"/>
+      <c r="L64" s="174"/>
       <c r="M64" s="89">
         <f t="shared" si="5"/>
         <v>210090.52</v>
@@ -6549,7 +6560,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K65" s="145"/>
-      <c r="L65" s="175"/>
+      <c r="L65" s="174"/>
       <c r="M65" s="89">
         <f t="shared" si="5"/>
         <v>169532.53</v>
@@ -6599,7 +6610,7 @@
         <v>35100</v>
       </c>
       <c r="K66" s="145"/>
-      <c r="L66" s="175"/>
+      <c r="L66" s="174"/>
       <c r="M66" s="89">
         <f t="shared" si="5"/>
         <v>183437.54</v>
@@ -6648,7 +6659,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K67" s="145"/>
-      <c r="L67" s="175"/>
+      <c r="L67" s="174"/>
       <c r="M67" s="89">
         <f t="shared" si="5"/>
         <v>205730.55</v>
@@ -6698,7 +6709,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K68" s="145"/>
-      <c r="L68" s="175"/>
+      <c r="L68" s="174"/>
       <c r="M68" s="89">
         <f t="shared" si="5"/>
         <v>175598.56</v>
@@ -6747,7 +6758,7 @@
         <v>24600</v>
       </c>
       <c r="K69" s="145"/>
-      <c r="L69" s="175"/>
+      <c r="L69" s="174"/>
       <c r="M69" s="89">
         <f t="shared" si="5"/>
         <v>128553.57</v>
@@ -6797,7 +6808,7 @@
         <v>24600</v>
       </c>
       <c r="K70" s="145"/>
-      <c r="L70" s="175"/>
+      <c r="L70" s="174"/>
       <c r="M70" s="89">
         <f t="shared" si="5"/>
         <v>128563.58</v>
@@ -6846,7 +6857,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K71" s="147"/>
-      <c r="L71" s="177"/>
+      <c r="L71" s="176"/>
       <c r="M71" s="89">
         <f t="shared" si="5"/>
         <v>204030.59</v>
@@ -6895,7 +6906,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K72" s="145"/>
-      <c r="L72" s="175"/>
+      <c r="L72" s="174"/>
       <c r="M72" s="89">
         <f t="shared" si="5"/>
         <v>170680.6</v>
@@ -6945,7 +6956,7 @@
         <v>35100</v>
       </c>
       <c r="K73" s="145"/>
-      <c r="L73" s="175"/>
+      <c r="L73" s="174"/>
       <c r="M73" s="89">
         <f t="shared" si="5"/>
         <v>183437.61</v>
@@ -6994,7 +7005,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K74" s="145"/>
-      <c r="L74" s="175"/>
+      <c r="L74" s="174"/>
       <c r="M74" s="89">
         <f t="shared" si="5"/>
         <v>205730.62</v>
@@ -7044,7 +7055,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K75" s="145"/>
-      <c r="L75" s="175"/>
+      <c r="L75" s="174"/>
       <c r="M75" s="89">
         <f t="shared" si="5"/>
         <v>175598.63</v>
@@ -7096,7 +7107,7 @@
       <c r="K76" s="145">
         <v>50000</v>
       </c>
-      <c r="L76" s="175"/>
+      <c r="L76" s="174"/>
       <c r="M76" s="89">
         <f t="shared" si="5"/>
         <v>178563.64</v>
@@ -7125,7 +7136,7 @@
       <c r="E77" s="87">
         <v>928411.65</v>
       </c>
-      <c r="F77" s="180">
+      <c r="F77" s="179">
         <v>99012.65</v>
       </c>
       <c r="G77" s="122">
@@ -7145,7 +7156,7 @@
         <v>24600</v>
       </c>
       <c r="K77" s="147"/>
-      <c r="L77" s="177"/>
+      <c r="L77" s="176"/>
       <c r="M77" s="89">
         <f t="shared" si="5"/>
         <v>982843.65</v>
@@ -7197,7 +7208,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K78" s="145"/>
-      <c r="L78" s="175"/>
+      <c r="L78" s="174"/>
       <c r="M78" s="89">
         <f t="shared" si="5"/>
         <v>204394.66</v>
@@ -7246,7 +7257,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K79" s="145"/>
-      <c r="L79" s="175"/>
+      <c r="L79" s="174"/>
       <c r="M79" s="89">
         <f t="shared" ref="M79:M115" si="18">ROUND(SUM(G79:L79),0) + O79</f>
         <v>353780.67</v>
@@ -7295,7 +7306,7 @@
         <v>35100</v>
       </c>
       <c r="K80" s="145"/>
-      <c r="L80" s="175"/>
+      <c r="L80" s="174"/>
       <c r="M80" s="89">
         <f t="shared" si="18"/>
         <v>6063281.6799999997</v>
@@ -7345,7 +7356,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K81" s="145"/>
-      <c r="L81" s="175"/>
+      <c r="L81" s="174"/>
       <c r="M81" s="89">
         <f t="shared" si="18"/>
         <v>211658.69</v>
@@ -7395,7 +7406,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K82" s="147"/>
-      <c r="L82" s="177"/>
+      <c r="L82" s="176"/>
       <c r="M82" s="89">
         <f t="shared" si="18"/>
         <v>175598.7</v>
@@ -7448,7 +7459,7 @@
         <v>24600</v>
       </c>
       <c r="K83" s="145"/>
-      <c r="L83" s="175"/>
+      <c r="L83" s="174"/>
       <c r="M83" s="89">
         <f t="shared" si="18"/>
         <v>128563.71</v>
@@ -7498,7 +7509,7 @@
         <v>24600</v>
       </c>
       <c r="K84" s="145"/>
-      <c r="L84" s="175"/>
+      <c r="L84" s="174"/>
       <c r="M84" s="89">
         <f t="shared" si="18"/>
         <v>128563.72</v>
@@ -7547,7 +7558,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K85" s="145"/>
-      <c r="L85" s="175"/>
+      <c r="L85" s="174"/>
       <c r="M85" s="89">
         <f t="shared" si="18"/>
         <v>416090.73</v>
@@ -7594,7 +7605,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K86" s="145"/>
-      <c r="L86" s="175"/>
+      <c r="L86" s="174"/>
       <c r="M86" s="89">
         <f t="shared" si="18"/>
         <v>512255.74</v>
@@ -7644,7 +7655,7 @@
         <v>35100</v>
       </c>
       <c r="K87" s="145"/>
-      <c r="L87" s="175"/>
+      <c r="L87" s="174"/>
       <c r="M87" s="89">
         <f t="shared" si="18"/>
         <v>183437.75</v>
@@ -7694,7 +7705,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K88" s="145"/>
-      <c r="L88" s="175"/>
+      <c r="L88" s="174"/>
       <c r="M88" s="89">
         <f t="shared" si="18"/>
         <v>211658.76</v>
@@ -7743,7 +7754,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K89" s="145"/>
-      <c r="L89" s="175"/>
+      <c r="L89" s="174"/>
       <c r="M89" s="89">
         <f t="shared" si="18"/>
         <v>170837.77</v>
@@ -7787,7 +7798,7 @@
         <v>24600</v>
       </c>
       <c r="K90" s="149"/>
-      <c r="L90" s="178">
+      <c r="L90" s="177">
         <v>250000</v>
       </c>
       <c r="M90" s="136">
@@ -7803,7 +7814,7 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="P90" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -7842,7 +7853,7 @@
         <v>24600</v>
       </c>
       <c r="K91" s="145"/>
-      <c r="L91" s="175"/>
+      <c r="L91" s="174"/>
       <c r="M91" s="89">
         <f t="shared" si="18"/>
         <v>128563.79</v>
@@ -7857,28 +7868,30 @@
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92" s="150">
+      <c r="A92" s="244">
         <f t="shared" si="9"/>
         <v>80</v>
       </c>
-      <c r="B92" s="91" t="s">
+      <c r="B92" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="C92" s="90"/>
-      <c r="D92" s="85">
+      <c r="C92" s="246"/>
+      <c r="D92" s="247">
         <v>1.34</v>
       </c>
-      <c r="E92" s="86">
+      <c r="E92" s="248">
         <v>397351.8</v>
       </c>
-      <c r="F92" s="87"/>
+      <c r="F92" s="87">
+        <v>222060.79999999999</v>
+      </c>
       <c r="G92" s="88">
-        <f t="shared" si="14"/>
-        <v>397351.8</v>
+        <f>E92-F92</f>
+        <v>175291</v>
       </c>
       <c r="H92" s="88">
         <f t="shared" si="17"/>
-        <v>11920.554</v>
+        <v>5258.73</v>
       </c>
       <c r="I92" s="145">
         <f t="shared" si="15"/>
@@ -7889,14 +7902,14 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K92" s="145"/>
-      <c r="L92" s="175"/>
+      <c r="L92" s="174"/>
       <c r="M92" s="89">
         <f t="shared" si="18"/>
-        <v>619362.80000000005</v>
+        <v>390640.8</v>
       </c>
       <c r="N92" s="161">
         <f t="shared" si="8"/>
-        <v>637943.80000000005</v>
+        <v>402359.8</v>
       </c>
       <c r="O92" s="53">
         <f t="shared" si="7"/>
@@ -7936,7 +7949,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K93" s="146"/>
-      <c r="L93" s="176"/>
+      <c r="L93" s="175"/>
       <c r="M93" s="99">
         <f t="shared" si="18"/>
         <v>761898.81</v>
@@ -7989,7 +8002,7 @@
         <v>35100</v>
       </c>
       <c r="K94" s="145"/>
-      <c r="L94" s="175"/>
+      <c r="L94" s="174"/>
       <c r="M94" s="89">
         <f t="shared" si="18"/>
         <v>183437.82</v>
@@ -8036,7 +8049,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K95" s="145"/>
-      <c r="L95" s="175"/>
+      <c r="L95" s="174"/>
       <c r="M95" s="89">
         <f t="shared" si="18"/>
         <v>137181.82999999999</v>
@@ -8086,7 +8099,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K96" s="145"/>
-      <c r="L96" s="175"/>
+      <c r="L96" s="174"/>
       <c r="M96" s="89">
         <f t="shared" si="18"/>
         <v>175598.84</v>
@@ -8136,7 +8149,7 @@
         <v>24600</v>
       </c>
       <c r="K97" s="145"/>
-      <c r="L97" s="175"/>
+      <c r="L97" s="174"/>
       <c r="M97" s="89">
         <f t="shared" si="18"/>
         <v>128563.85</v>
@@ -8185,7 +8198,7 @@
         <v>24600</v>
       </c>
       <c r="K98" s="145"/>
-      <c r="L98" s="175"/>
+      <c r="L98" s="174"/>
       <c r="M98" s="89">
         <f t="shared" si="18"/>
         <v>124788.86</v>
@@ -8235,7 +8248,7 @@
         <v>40200.000000000007</v>
       </c>
       <c r="K99" s="145"/>
-      <c r="L99" s="175"/>
+      <c r="L99" s="174"/>
       <c r="M99" s="89">
         <f t="shared" si="18"/>
         <v>210090.87</v>
@@ -8285,7 +8298,7 @@
         <v>33600.000000000007</v>
       </c>
       <c r="K100" s="145"/>
-      <c r="L100" s="175"/>
+      <c r="L100" s="174"/>
       <c r="M100" s="89">
         <f t="shared" si="18"/>
         <v>175598.88</v>
@@ -8335,7 +8348,7 @@
         <v>35100</v>
       </c>
       <c r="K101" s="145"/>
-      <c r="L101" s="175"/>
+      <c r="L101" s="174"/>
       <c r="M101" s="89">
         <f t="shared" si="18"/>
         <v>183437.89</v>
@@ -8385,7 +8398,7 @@
         <v>3000</v>
       </c>
       <c r="K102" s="145"/>
-      <c r="L102" s="175"/>
+      <c r="L102" s="174"/>
       <c r="M102" s="89">
         <f t="shared" si="18"/>
         <v>15678.9</v>
@@ -8434,7 +8447,7 @@
         <v>3000</v>
       </c>
       <c r="K103" s="145"/>
-      <c r="L103" s="175"/>
+      <c r="L103" s="174"/>
       <c r="M103" s="89">
         <f t="shared" si="18"/>
         <v>32166.91</v>
@@ -8484,7 +8497,7 @@
         <v>3000</v>
       </c>
       <c r="K104" s="145"/>
-      <c r="L104" s="175"/>
+      <c r="L104" s="174"/>
       <c r="M104" s="89">
         <f t="shared" si="18"/>
         <v>15678.92</v>
@@ -8533,7 +8546,7 @@
         <v>3000</v>
       </c>
       <c r="K105" s="147"/>
-      <c r="L105" s="177"/>
+      <c r="L105" s="176"/>
       <c r="M105" s="89">
         <f t="shared" si="18"/>
         <v>15226.93</v>
@@ -8583,7 +8596,7 @@
         <v>3000</v>
       </c>
       <c r="K106" s="147"/>
-      <c r="L106" s="177"/>
+      <c r="L106" s="176"/>
       <c r="M106" s="89">
         <f t="shared" si="18"/>
         <v>15678.94</v>
@@ -8633,7 +8646,7 @@
         <v>3000</v>
       </c>
       <c r="K107" s="147"/>
-      <c r="L107" s="177"/>
+      <c r="L107" s="176"/>
       <c r="M107" s="89">
         <f t="shared" si="18"/>
         <v>15678.95</v>
@@ -8683,7 +8696,7 @@
         <v>3000</v>
       </c>
       <c r="K108" s="147"/>
-      <c r="L108" s="177"/>
+      <c r="L108" s="176"/>
       <c r="M108" s="89">
         <f t="shared" si="18"/>
         <v>15678.96</v>
@@ -8736,7 +8749,7 @@
         <v>3000</v>
       </c>
       <c r="K109" s="147"/>
-      <c r="L109" s="177"/>
+      <c r="L109" s="176"/>
       <c r="M109" s="89">
         <f t="shared" si="18"/>
         <v>15678.97</v>
@@ -8786,7 +8799,7 @@
         <v>3000</v>
       </c>
       <c r="K110" s="147"/>
-      <c r="L110" s="177"/>
+      <c r="L110" s="176"/>
       <c r="M110" s="89">
         <f t="shared" si="18"/>
         <v>15678.98</v>
@@ -8835,7 +8848,7 @@
         <v>3000</v>
       </c>
       <c r="K111" s="147"/>
-      <c r="L111" s="177"/>
+      <c r="L111" s="176"/>
       <c r="M111" s="89">
         <f t="shared" si="18"/>
         <v>15239.99</v>
@@ -8882,7 +8895,7 @@
         <v>3000</v>
       </c>
       <c r="K112" s="147"/>
-      <c r="L112" s="177"/>
+      <c r="L112" s="176"/>
       <c r="M112" s="89">
         <f t="shared" si="18"/>
         <v>31208</v>
@@ -8931,7 +8944,7 @@
         <v>3000</v>
       </c>
       <c r="K113" s="147"/>
-      <c r="L113" s="177"/>
+      <c r="L113" s="176"/>
       <c r="M113" s="89">
         <f t="shared" si="18"/>
         <v>15227.01</v>
@@ -8980,7 +8993,7 @@
         <v>3000</v>
       </c>
       <c r="K114" s="147"/>
-      <c r="L114" s="177"/>
+      <c r="L114" s="176"/>
       <c r="M114" s="89">
         <f t="shared" si="18"/>
         <v>16145.02</v>
@@ -9030,7 +9043,7 @@
         <v>3000</v>
       </c>
       <c r="K115" s="147"/>
-      <c r="L115" s="177"/>
+      <c r="L115" s="176"/>
       <c r="M115" s="89">
         <f t="shared" si="18"/>
         <v>15679.03</v>
@@ -9056,7 +9069,7 @@
       <c r="I116" s="147"/>
       <c r="J116" s="147"/>
       <c r="K116" s="147"/>
-      <c r="L116" s="177"/>
+      <c r="L116" s="176"/>
       <c r="M116" s="123"/>
       <c r="N116" s="163"/>
       <c r="O116" s="53"/>
@@ -9075,15 +9088,15 @@
       </c>
       <c r="F117" s="158">
         <f>SUM(F13:F116)</f>
-        <v>14192055.65</v>
+        <v>14414116.450000001</v>
       </c>
       <c r="G117" s="158">
         <f t="shared" si="25"/>
-        <v>16934296.609999999</v>
+        <v>16712235.810000001</v>
       </c>
       <c r="H117" s="158">
         <f t="shared" si="25"/>
-        <v>494100.16710000002</v>
+        <v>487438.3431</v>
       </c>
       <c r="I117" s="159">
         <f t="shared" si="25"/>
@@ -9094,14 +9107,14 @@
         <v>3004800</v>
       </c>
       <c r="K117" s="160"/>
-      <c r="L117" s="179"/>
+      <c r="L117" s="178"/>
       <c r="M117" s="168">
         <f t="shared" si="25"/>
-        <v>34243207.560000002</v>
+        <v>34014485.560000002</v>
       </c>
       <c r="N117" s="165">
         <f t="shared" si="25"/>
-        <v>35270505.56000001</v>
+        <v>35034921.560000002</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9110,95 +9123,93 @@
     </row>
     <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="217" t="s">
+      <c r="B120" s="220" t="s">
         <v>105</v>
       </c>
-      <c r="C120" s="217"/>
-      <c r="D120" s="217"/>
-      <c r="E120" s="217"/>
-      <c r="F120" s="217"/>
-      <c r="G120" s="217"/>
-      <c r="H120" s="217"/>
-      <c r="I120" s="217"/>
-      <c r="J120" s="217"/>
-      <c r="K120" s="217"/>
-      <c r="L120" s="217"/>
-      <c r="M120" s="217"/>
+      <c r="C120" s="220"/>
+      <c r="D120" s="220"/>
+      <c r="E120" s="220"/>
+      <c r="F120" s="220"/>
+      <c r="G120" s="220"/>
+      <c r="H120" s="220"/>
+      <c r="I120" s="220"/>
+      <c r="J120" s="220"/>
+      <c r="K120" s="220"/>
+      <c r="L120" s="220"/>
+      <c r="M120" s="220"/>
     </row>
     <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="217"/>
-      <c r="C121" s="217"/>
-      <c r="D121" s="217"/>
-      <c r="E121" s="217"/>
-      <c r="F121" s="217"/>
-      <c r="G121" s="217"/>
-      <c r="H121" s="217"/>
-      <c r="I121" s="217"/>
-      <c r="J121" s="217"/>
-      <c r="K121" s="217"/>
-      <c r="L121" s="217"/>
-      <c r="M121" s="217"/>
+      <c r="B121" s="220"/>
+      <c r="C121" s="220"/>
+      <c r="D121" s="220"/>
+      <c r="E121" s="220"/>
+      <c r="F121" s="220"/>
+      <c r="G121" s="220"/>
+      <c r="H121" s="220"/>
+      <c r="I121" s="220"/>
+      <c r="J121" s="220"/>
+      <c r="K121" s="220"/>
+      <c r="L121" s="220"/>
+      <c r="M121" s="220"/>
     </row>
     <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="217"/>
-      <c r="C122" s="217"/>
-      <c r="D122" s="217"/>
-      <c r="E122" s="217"/>
-      <c r="F122" s="217"/>
-      <c r="G122" s="217"/>
-      <c r="H122" s="217"/>
-      <c r="I122" s="217"/>
-      <c r="J122" s="217"/>
-      <c r="K122" s="217"/>
-      <c r="L122" s="217"/>
-      <c r="M122" s="217"/>
+      <c r="B122" s="220"/>
+      <c r="C122" s="220"/>
+      <c r="D122" s="220"/>
+      <c r="E122" s="220"/>
+      <c r="F122" s="220"/>
+      <c r="G122" s="220"/>
+      <c r="H122" s="220"/>
+      <c r="I122" s="220"/>
+      <c r="J122" s="220"/>
+      <c r="K122" s="220"/>
+      <c r="L122" s="220"/>
+      <c r="M122" s="220"/>
     </row>
     <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="217"/>
-      <c r="C123" s="217"/>
-      <c r="D123" s="217"/>
-      <c r="E123" s="217"/>
-      <c r="F123" s="217"/>
-      <c r="G123" s="217"/>
-      <c r="H123" s="217"/>
-      <c r="I123" s="217"/>
-      <c r="J123" s="217"/>
-      <c r="K123" s="217"/>
-      <c r="L123" s="217"/>
-      <c r="M123" s="217"/>
+      <c r="B123" s="220"/>
+      <c r="C123" s="220"/>
+      <c r="D123" s="220"/>
+      <c r="E123" s="220"/>
+      <c r="F123" s="220"/>
+      <c r="G123" s="220"/>
+      <c r="H123" s="220"/>
+      <c r="I123" s="220"/>
+      <c r="J123" s="220"/>
+      <c r="K123" s="220"/>
+      <c r="L123" s="220"/>
+      <c r="M123" s="220"/>
     </row>
     <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="217"/>
-      <c r="C124" s="217"/>
-      <c r="D124" s="217"/>
-      <c r="E124" s="217"/>
-      <c r="F124" s="217"/>
-      <c r="G124" s="217"/>
-      <c r="H124" s="217"/>
-      <c r="I124" s="217"/>
-      <c r="J124" s="217"/>
-      <c r="K124" s="217"/>
-      <c r="L124" s="217"/>
-      <c r="M124" s="217"/>
+      <c r="B124" s="220"/>
+      <c r="C124" s="220"/>
+      <c r="D124" s="220"/>
+      <c r="E124" s="220"/>
+      <c r="F124" s="220"/>
+      <c r="G124" s="220"/>
+      <c r="H124" s="220"/>
+      <c r="I124" s="220"/>
+      <c r="J124" s="220"/>
+      <c r="K124" s="220"/>
+      <c r="L124" s="220"/>
+      <c r="M124" s="220"/>
     </row>
     <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="217"/>
-      <c r="C125" s="217"/>
-      <c r="D125" s="217"/>
-      <c r="E125" s="217"/>
-      <c r="F125" s="217"/>
-      <c r="G125" s="217"/>
-      <c r="H125" s="217"/>
-      <c r="I125" s="217"/>
-      <c r="J125" s="217"/>
-      <c r="K125" s="217"/>
-      <c r="L125" s="217"/>
-      <c r="M125" s="217"/>
+      <c r="B125" s="220"/>
+      <c r="C125" s="220"/>
+      <c r="D125" s="220"/>
+      <c r="E125" s="220"/>
+      <c r="F125" s="220"/>
+      <c r="G125" s="220"/>
+      <c r="H125" s="220"/>
+      <c r="I125" s="220"/>
+      <c r="J125" s="220"/>
+      <c r="K125" s="220"/>
+      <c r="L125" s="220"/>
+      <c r="M125" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="B120:M125"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="A4:N8"/>
     <mergeCell ref="A11:A12"/>
@@ -9216,6 +9227,8 @@
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="J11:J12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="B120:M125"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9234,9 +9247,7 @@
       <c r="C3" s="22"/>
     </row>
     <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="22" t="s">
-        <v>193</v>
-      </c>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="22"/>
@@ -9245,24 +9256,20 @@
       <c r="C6" s="22"/>
     </row>
     <row r="7" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C7" s="22" t="s">
-        <v>194</v>
+      <c r="C7" s="198" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C10" s="169" t="s">
-        <v>195</v>
+      <c r="C10" s="249" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C12" s="22" t="s">
-        <v>196</v>
-      </c>
+      <c r="C12" s="22"/>
     </row>
     <row r="14" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C14" s="22" t="s">
-        <v>206</v>
-      </c>
+      <c r="C14" s="22"/>
     </row>
     <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
